--- a/environment/runtimefiles/AllCPU-AllOS/zcadelectrotech/data/preload/xlsxtemplates/modelinxlsx/+++EMO_NEWMETHOD_LAST.xlsx
+++ b/environment/runtimefiles/AllCPU-AllOS/zcadelectrotech/data/preload/xlsxtemplates/modelinxlsx/+++EMO_NEWMETHOD_LAST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21425"/>
   <workbookPr codeName="ЭтаКнига" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\zcad\zcadMASTER\environment\runtimefiles\AllCPU-AllOS\zcadelectrotech\data\preload\xlsxtemplates\modelinxlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\zcad\zcadMaster\environment\runtimefiles\AllCPU-AllOS\zcadelectrotech\data\preload\xlsxtemplates\modelinxlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B166C352-9727-4865-8AAB-4D1697C4BE8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44607A5F-266B-4ADC-AC13-CCBA7FA7DB19}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" tabRatio="643" activeTab="12" xr2:uid="{456AB35E-0355-4F16-B1D8-5CF582B696FE}"/>
+    <workbookView xWindow="4350" yWindow="6615" windowWidth="21705" windowHeight="14025" tabRatio="643" firstSheet="11" activeTab="12" xr2:uid="{456AB35E-0355-4F16-B1D8-5CF582B696FE}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="4" r:id="rId1"/>
@@ -36,17 +36,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -782,14 +771,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -4789,6 +4778,81 @@
     <xf numFmtId="0" fontId="0" fillId="67" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4848,9 +4912,6 @@
     <xf numFmtId="0" fontId="0" fillId="46" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4941,78 +5002,6 @@
     <xf numFmtId="0" fontId="14" fillId="45" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5422,9 +5411,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5462,7 +5451,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5568,7 +5557,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5710,7 +5699,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5732,87 +5721,87 @@
   <sheetData>
     <row r="2" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:79" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="268" t="s">
+      <c r="A3" s="222" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="269"/>
-      <c r="C3" s="270"/>
-      <c r="F3" s="271" t="s">
+      <c r="B3" s="223"/>
+      <c r="C3" s="224"/>
+      <c r="F3" s="225" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="272"/>
-      <c r="H3" s="273"/>
-      <c r="K3" s="266" t="s">
+      <c r="G3" s="226"/>
+      <c r="H3" s="227"/>
+      <c r="K3" s="220" t="s">
         <v>73</v>
       </c>
-      <c r="L3" s="267"/>
-      <c r="M3" s="267"/>
-      <c r="N3" s="267"/>
-      <c r="O3" s="267"/>
-      <c r="P3" s="267"/>
-      <c r="Q3" s="267"/>
-      <c r="R3" s="267"/>
-      <c r="S3" s="267"/>
-      <c r="T3" s="267"/>
-      <c r="U3" s="267"/>
-      <c r="V3" s="267"/>
-      <c r="W3" s="267"/>
-      <c r="X3" s="267"/>
-      <c r="Y3" s="267"/>
-      <c r="Z3" s="267"/>
-      <c r="AA3" s="267"/>
-      <c r="AB3" s="267"/>
-      <c r="AC3" s="267"/>
-      <c r="AD3" s="267"/>
-      <c r="AE3" s="267"/>
-      <c r="AF3" s="267"/>
-      <c r="AG3" s="267"/>
-      <c r="AH3" s="267"/>
-      <c r="AI3" s="267"/>
-      <c r="AJ3" s="267"/>
-      <c r="AK3" s="267"/>
-      <c r="AL3" s="267"/>
-      <c r="AM3" s="267"/>
-      <c r="AN3" s="267"/>
-      <c r="AO3" s="267"/>
-      <c r="AP3" s="267"/>
-      <c r="AQ3" s="267"/>
-      <c r="AR3" s="267"/>
-      <c r="AS3" s="267"/>
-      <c r="AT3" s="267"/>
-      <c r="AU3" s="267"/>
-      <c r="AV3" s="267"/>
-      <c r="AW3" s="267"/>
-      <c r="AX3" s="267"/>
-      <c r="AY3" s="267"/>
-      <c r="AZ3" s="267"/>
-      <c r="BA3" s="267"/>
-      <c r="BB3" s="267"/>
-      <c r="BC3" s="267"/>
-      <c r="BD3" s="267"/>
-      <c r="BE3" s="267"/>
-      <c r="BF3" s="267"/>
-      <c r="BG3" s="267"/>
-      <c r="BH3" s="267"/>
-      <c r="BI3" s="267"/>
-      <c r="BJ3" s="267"/>
-      <c r="BK3" s="267"/>
-      <c r="BL3" s="267"/>
-      <c r="BM3" s="267"/>
-      <c r="BN3" s="267"/>
-      <c r="BO3" s="267"/>
-      <c r="BP3" s="267"/>
-      <c r="BQ3" s="267"/>
-      <c r="BR3" s="267"/>
-      <c r="BS3" s="267"/>
-      <c r="BT3" s="267"/>
-      <c r="BU3" s="267"/>
-      <c r="BV3" s="267"/>
-      <c r="BW3" s="267"/>
-      <c r="BX3" s="267"/>
-      <c r="BY3" s="267"/>
-      <c r="BZ3" s="267"/>
-      <c r="CA3" s="267"/>
+      <c r="L3" s="221"/>
+      <c r="M3" s="221"/>
+      <c r="N3" s="221"/>
+      <c r="O3" s="221"/>
+      <c r="P3" s="221"/>
+      <c r="Q3" s="221"/>
+      <c r="R3" s="221"/>
+      <c r="S3" s="221"/>
+      <c r="T3" s="221"/>
+      <c r="U3" s="221"/>
+      <c r="V3" s="221"/>
+      <c r="W3" s="221"/>
+      <c r="X3" s="221"/>
+      <c r="Y3" s="221"/>
+      <c r="Z3" s="221"/>
+      <c r="AA3" s="221"/>
+      <c r="AB3" s="221"/>
+      <c r="AC3" s="221"/>
+      <c r="AD3" s="221"/>
+      <c r="AE3" s="221"/>
+      <c r="AF3" s="221"/>
+      <c r="AG3" s="221"/>
+      <c r="AH3" s="221"/>
+      <c r="AI3" s="221"/>
+      <c r="AJ3" s="221"/>
+      <c r="AK3" s="221"/>
+      <c r="AL3" s="221"/>
+      <c r="AM3" s="221"/>
+      <c r="AN3" s="221"/>
+      <c r="AO3" s="221"/>
+      <c r="AP3" s="221"/>
+      <c r="AQ3" s="221"/>
+      <c r="AR3" s="221"/>
+      <c r="AS3" s="221"/>
+      <c r="AT3" s="221"/>
+      <c r="AU3" s="221"/>
+      <c r="AV3" s="221"/>
+      <c r="AW3" s="221"/>
+      <c r="AX3" s="221"/>
+      <c r="AY3" s="221"/>
+      <c r="AZ3" s="221"/>
+      <c r="BA3" s="221"/>
+      <c r="BB3" s="221"/>
+      <c r="BC3" s="221"/>
+      <c r="BD3" s="221"/>
+      <c r="BE3" s="221"/>
+      <c r="BF3" s="221"/>
+      <c r="BG3" s="221"/>
+      <c r="BH3" s="221"/>
+      <c r="BI3" s="221"/>
+      <c r="BJ3" s="221"/>
+      <c r="BK3" s="221"/>
+      <c r="BL3" s="221"/>
+      <c r="BM3" s="221"/>
+      <c r="BN3" s="221"/>
+      <c r="BO3" s="221"/>
+      <c r="BP3" s="221"/>
+      <c r="BQ3" s="221"/>
+      <c r="BR3" s="221"/>
+      <c r="BS3" s="221"/>
+      <c r="BT3" s="221"/>
+      <c r="BU3" s="221"/>
+      <c r="BV3" s="221"/>
+      <c r="BW3" s="221"/>
+      <c r="BX3" s="221"/>
+      <c r="BY3" s="221"/>
+      <c r="BZ3" s="221"/>
+      <c r="CA3" s="221"/>
     </row>
     <row r="4" spans="1:79" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -6931,10 +6920,10 @@
       <c r="CA8" s="2"/>
     </row>
     <row r="9" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="274" t="s">
+      <c r="A9" s="228" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="275"/>
+      <c r="B9" s="229"/>
       <c r="F9" s="27">
         <v>2500</v>
       </c>
@@ -12067,15 +12056,15 @@
     </row>
     <row r="41" spans="6:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="42" spans="6:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F42" s="271" t="s">
+      <c r="F42" s="225" t="s">
         <v>71</v>
       </c>
-      <c r="G42" s="272"/>
-      <c r="H42" s="273"/>
-      <c r="K42" s="276" t="s">
+      <c r="G42" s="226"/>
+      <c r="H42" s="227"/>
+      <c r="K42" s="230" t="s">
         <v>508</v>
       </c>
-      <c r="L42" s="277"/>
+      <c r="L42" s="231"/>
     </row>
     <row r="43" spans="6:79" ht="31.5" x14ac:dyDescent="0.25">
       <c r="F43" s="36" t="s">
@@ -12168,10 +12157,10 @@
       <c r="H50" s="29"/>
     </row>
     <row r="56" spans="3:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C56" s="265" t="s">
+      <c r="C56" s="219" t="s">
         <v>618</v>
       </c>
-      <c r="D56" s="265"/>
+      <c r="D56" s="219"/>
     </row>
     <row r="57" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C57" s="2" t="s">
@@ -12731,20 +12720,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:45" x14ac:dyDescent="0.25">
-      <c r="C1" s="238" t="s">
+      <c r="C1" s="242" t="s">
         <v>436</v>
       </c>
-      <c r="D1" s="238"/>
-      <c r="L1" s="288" t="s">
+      <c r="D1" s="242"/>
+      <c r="L1" s="243" t="s">
         <v>474</v>
       </c>
-      <c r="M1" s="288"/>
-      <c r="N1" s="288"/>
-      <c r="O1" s="288"/>
-      <c r="P1" s="288"/>
-      <c r="Q1" s="288"/>
-      <c r="R1" s="288"/>
-      <c r="S1" s="288"/>
+      <c r="M1" s="243"/>
+      <c r="N1" s="243"/>
+      <c r="O1" s="243"/>
+      <c r="P1" s="243"/>
+      <c r="Q1" s="243"/>
+      <c r="R1" s="243"/>
+      <c r="S1" s="243"/>
     </row>
     <row r="2" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C2" s="99" t="s">
@@ -12980,10 +12969,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="C1" s="238" t="s">
+      <c r="C1" s="242" t="s">
         <v>436</v>
       </c>
-      <c r="D1" s="238"/>
+      <c r="D1" s="242"/>
     </row>
     <row r="2" spans="2:31" x14ac:dyDescent="0.25">
       <c r="C2" s="99" t="s">
@@ -13034,7 +13023,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="133">
-        <f>COUNT($C$7:C7)</f>
+        <f>COUNT($I$7:I7)</f>
         <v>1</v>
       </c>
       <c r="H7" s="133" t="str">
@@ -13069,11 +13058,11 @@
         <v>L=0м</v>
       </c>
       <c r="P7" s="137" t="e">
-        <f>IF(L7=G7,_xlfn.CONCAT(D7," ",O7),_xlfn.CONCAT(D7," ",O7,"\P"))</f>
+        <f>IF(L7=G7,D7&amp;" "&amp;O7,D7&amp;" "&amp;O7&amp;"\P")</f>
         <v>#N/A</v>
       </c>
-      <c r="Q7" s="138" t="e" cm="1">
-        <f t="array" aca="1" ref="Q7" ca="1">_xlfn.CONCAT(INDIRECT(INDEX($H$7:H7,K7)&amp;":"&amp;N7))</f>
+      <c r="Q7" s="138" t="e">
+        <f>IF(C7=INDEX($C$7:$C$777777,G7+1),P7&amp;INDEX($P$7:$P$777777,G7+1),P7)&amp;IF(C7=INDEX($C$7:$C$777777,G7+2),INDEX($P$7:$P$777777,G7+2),"")&amp;IF(C7=INDEX($C$7:$C$777777,G7+3),INDEX($P$7:$P$777777,G7+3),"")&amp;IF(C7=INDEX($C$7:$C$777777,G7+4),INDEX($P$7:$P$777777,G7+4),"")&amp;IF(C7=INDEX($C$7:$C$777777,G7+5),INDEX($P$7:$P$777777,G7+5),"")&amp;IF(C7=INDEX($C$7:$C$777777,G7+6),INDEX($P$7:$P$777777,G7+6),"")</f>
         <v>#N/A</v>
       </c>
       <c r="R7" s="139"/>
@@ -13436,31 +13425,31 @@
       </c>
     </row>
     <row r="4" spans="4:57" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="223" t="s">
+      <c r="D4" s="248" t="s">
         <v>313</v>
       </c>
-      <c r="E4" s="223"/>
-      <c r="F4" s="223"/>
-      <c r="G4" s="223"/>
-      <c r="H4" s="223"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
       <c r="I4" s="62" t="s">
         <v>312</v>
       </c>
       <c r="J4" s="91"/>
       <c r="K4" s="91"/>
       <c r="P4" s="62"/>
-      <c r="Q4" s="223" t="s">
+      <c r="Q4" s="248" t="s">
         <v>311</v>
       </c>
-      <c r="R4" s="223"/>
-      <c r="S4" s="223"/>
-      <c r="T4" s="223"/>
-      <c r="U4" s="223"/>
-      <c r="V4" s="223"/>
-      <c r="Z4" s="238" t="s">
+      <c r="R4" s="248"/>
+      <c r="S4" s="248"/>
+      <c r="T4" s="248"/>
+      <c r="U4" s="248"/>
+      <c r="V4" s="248"/>
+      <c r="Z4" s="242" t="s">
         <v>436</v>
       </c>
-      <c r="AA4" s="238"/>
+      <c r="AA4" s="242"/>
       <c r="AU4" s="96" t="s">
         <v>403</v>
       </c>
@@ -13489,12 +13478,12 @@
       </c>
     </row>
     <row r="5" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D5" s="224" t="s">
+      <c r="D5" s="249" t="s">
         <v>310</v>
       </c>
-      <c r="E5" s="224"/>
-      <c r="F5" s="224"/>
-      <c r="G5" s="224"/>
+      <c r="E5" s="249"/>
+      <c r="F5" s="249"/>
+      <c r="G5" s="249"/>
       <c r="H5" s="100">
         <f>AU5</f>
         <v>0</v>
@@ -13507,17 +13496,17 @@
       <c r="P5" s="61" t="s">
         <v>308</v>
       </c>
-      <c r="Q5" s="225" t="s">
+      <c r="Q5" s="250" t="s">
         <v>307</v>
       </c>
-      <c r="R5" s="225"/>
-      <c r="S5" s="225"/>
-      <c r="T5" s="225"/>
-      <c r="U5" s="225">
+      <c r="R5" s="250"/>
+      <c r="S5" s="250"/>
+      <c r="T5" s="250"/>
+      <c r="U5" s="250">
         <f ca="1">ROUNDUP(SUM($AC$26:$AC$900000),2)</f>
         <v>0</v>
       </c>
-      <c r="V5" s="225"/>
+      <c r="V5" s="250"/>
       <c r="Z5" s="99" t="s">
         <v>424</v>
       </c>
@@ -13566,12 +13555,12 @@
       </c>
     </row>
     <row r="6" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D6" s="226" t="s">
+      <c r="D6" s="251" t="s">
         <v>306</v>
       </c>
-      <c r="E6" s="226"/>
-      <c r="F6" s="226"/>
-      <c r="G6" s="226"/>
+      <c r="E6" s="251"/>
+      <c r="F6" s="251"/>
+      <c r="G6" s="251"/>
       <c r="H6" s="90" t="s">
         <v>443</v>
       </c>
@@ -13583,17 +13572,17 @@
       <c r="P6" s="61">
         <v>63</v>
       </c>
-      <c r="Q6" s="225" t="s">
+      <c r="Q6" s="250" t="s">
         <v>304</v>
       </c>
-      <c r="R6" s="225"/>
-      <c r="S6" s="225"/>
-      <c r="T6" s="225"/>
-      <c r="U6" s="225">
+      <c r="R6" s="250"/>
+      <c r="S6" s="250"/>
+      <c r="T6" s="250"/>
+      <c r="U6" s="250">
         <f ca="1">ROUNDUP(U5*U11,2)</f>
         <v>0</v>
       </c>
-      <c r="V6" s="225"/>
+      <c r="V6" s="250"/>
       <c r="Z6" s="99" t="s">
         <v>425</v>
       </c>
@@ -13602,12 +13591,12 @@
       </c>
     </row>
     <row r="7" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D7" s="219" t="s">
+      <c r="D7" s="244" t="s">
         <v>303</v>
       </c>
-      <c r="E7" s="219"/>
-      <c r="F7" s="219"/>
-      <c r="G7" s="219"/>
+      <c r="E7" s="244"/>
+      <c r="F7" s="244"/>
+      <c r="G7" s="244"/>
       <c r="H7" s="58">
         <v>45399</v>
       </c>
@@ -13619,25 +13608,25 @@
       <c r="P7" s="61">
         <v>32</v>
       </c>
-      <c r="Q7" s="225" t="s">
+      <c r="Q7" s="250" t="s">
         <v>301</v>
       </c>
-      <c r="R7" s="225"/>
-      <c r="S7" s="225"/>
-      <c r="T7" s="225"/>
-      <c r="U7" s="225">
-        <f ca="1">ROUNDUP((U6*1000)/(VLOOKUP(H11,BD!$B$4:$C$5,2,FALSE)*U8),2)</f>
-        <v>0</v>
-      </c>
-      <c r="V7" s="225"/>
+      <c r="R7" s="250"/>
+      <c r="S7" s="250"/>
+      <c r="T7" s="250"/>
+      <c r="U7" s="250">
+        <f ca="1">ROUNDUP((U6*1000)/(INDEX(BD!C4:C5,MATCH(H11,BD!B4:B5,0))*U8),2)</f>
+        <v>0</v>
+      </c>
+      <c r="V7" s="250"/>
     </row>
     <row r="8" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D8" s="219" t="s">
+      <c r="D8" s="244" t="s">
         <v>300</v>
       </c>
-      <c r="E8" s="219"/>
-      <c r="F8" s="219"/>
-      <c r="G8" s="219"/>
+      <c r="E8" s="244"/>
+      <c r="F8" s="244"/>
+      <c r="G8" s="244"/>
       <c r="H8" s="58" t="s">
         <v>299</v>
       </c>
@@ -13649,24 +13638,24 @@
       <c r="P8" s="61">
         <v>6</v>
       </c>
-      <c r="Q8" s="227" t="s">
+      <c r="Q8" s="252" t="s">
         <v>297</v>
       </c>
-      <c r="R8" s="228"/>
-      <c r="S8" s="228"/>
-      <c r="T8" s="229"/>
-      <c r="U8" s="232">
+      <c r="R8" s="253"/>
+      <c r="S8" s="253"/>
+      <c r="T8" s="254"/>
+      <c r="U8" s="257">
         <v>0.92</v>
       </c>
-      <c r="V8" s="232"/>
+      <c r="V8" s="257"/>
     </row>
     <row r="9" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D9" s="219" t="s">
+      <c r="D9" s="244" t="s">
         <v>296</v>
       </c>
-      <c r="E9" s="219"/>
-      <c r="F9" s="219"/>
-      <c r="G9" s="219"/>
+      <c r="E9" s="244"/>
+      <c r="F9" s="244"/>
+      <c r="G9" s="244"/>
       <c r="H9" s="58" t="s">
         <v>295</v>
       </c>
@@ -13678,22 +13667,22 @@
       <c r="P9" s="61" t="s">
         <v>293</v>
       </c>
-      <c r="Q9" s="220" t="s">
+      <c r="Q9" s="245" t="s">
         <v>292</v>
       </c>
-      <c r="R9" s="220"/>
-      <c r="S9" s="220"/>
-      <c r="T9" s="220"/>
-      <c r="U9" s="221"/>
-      <c r="V9" s="221"/>
+      <c r="R9" s="245"/>
+      <c r="S9" s="245"/>
+      <c r="T9" s="245"/>
+      <c r="U9" s="246"/>
+      <c r="V9" s="246"/>
     </row>
     <row r="10" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D10" s="219" t="s">
+      <c r="D10" s="244" t="s">
         <v>291</v>
       </c>
-      <c r="E10" s="219"/>
-      <c r="F10" s="219"/>
-      <c r="G10" s="219"/>
+      <c r="E10" s="244"/>
+      <c r="F10" s="244"/>
+      <c r="G10" s="244"/>
       <c r="I10" s="61" t="s">
         <v>290</v>
       </c>
@@ -13702,20 +13691,20 @@
       <c r="P10" s="61">
         <v>4</v>
       </c>
-      <c r="Q10" s="220"/>
-      <c r="R10" s="220"/>
-      <c r="S10" s="220"/>
-      <c r="T10" s="220"/>
-      <c r="U10" s="221"/>
-      <c r="V10" s="221"/>
+      <c r="Q10" s="245"/>
+      <c r="R10" s="245"/>
+      <c r="S10" s="245"/>
+      <c r="T10" s="245"/>
+      <c r="U10" s="246"/>
+      <c r="V10" s="246"/>
     </row>
     <row r="11" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D11" s="219" t="s">
+      <c r="D11" s="244" t="s">
         <v>289</v>
       </c>
-      <c r="E11" s="219"/>
-      <c r="F11" s="219"/>
-      <c r="G11" s="219"/>
+      <c r="E11" s="244"/>
+      <c r="F11" s="244"/>
+      <c r="G11" s="244"/>
       <c r="H11" s="99">
         <v>380</v>
       </c>
@@ -13727,24 +13716,24 @@
       <c r="P11" s="61" t="s">
         <v>287</v>
       </c>
-      <c r="Q11" s="246" t="s">
+      <c r="Q11" s="270" t="s">
         <v>286</v>
       </c>
-      <c r="R11" s="247"/>
-      <c r="S11" s="247"/>
-      <c r="T11" s="248"/>
-      <c r="U11" s="249">
+      <c r="R11" s="271"/>
+      <c r="S11" s="271"/>
+      <c r="T11" s="272"/>
+      <c r="U11" s="273">
         <v>1</v>
       </c>
-      <c r="V11" s="250"/>
+      <c r="V11" s="274"/>
     </row>
     <row r="12" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D12" s="219" t="s">
+      <c r="D12" s="244" t="s">
         <v>285</v>
       </c>
-      <c r="E12" s="219"/>
-      <c r="F12" s="219"/>
-      <c r="G12" s="219"/>
+      <c r="E12" s="244"/>
+      <c r="F12" s="244"/>
+      <c r="G12" s="244"/>
       <c r="H12" s="58" t="s">
         <v>284</v>
       </c>
@@ -13756,99 +13745,99 @@
       <c r="P12" s="61" t="s">
         <v>283</v>
       </c>
-      <c r="Q12" s="222" t="s">
+      <c r="Q12" s="247" t="s">
         <v>282</v>
       </c>
-      <c r="R12" s="222"/>
-      <c r="S12" s="222"/>
-      <c r="T12" s="222"/>
-      <c r="U12" s="222">
+      <c r="R12" s="247"/>
+      <c r="S12" s="247"/>
+      <c r="T12" s="247"/>
+      <c r="U12" s="247">
         <v>44.5</v>
       </c>
-      <c r="V12" s="222"/>
+      <c r="V12" s="247"/>
     </row>
     <row r="13" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D13" s="219" t="s">
+      <c r="D13" s="244" t="s">
         <v>281</v>
       </c>
-      <c r="E13" s="219"/>
-      <c r="F13" s="219"/>
-      <c r="G13" s="219"/>
+      <c r="E13" s="244"/>
+      <c r="F13" s="244"/>
+      <c r="G13" s="244"/>
       <c r="H13" s="58" t="s">
         <v>280</v>
       </c>
       <c r="I13" s="59"/>
       <c r="P13" s="59"/>
-      <c r="Q13" s="222" t="s">
+      <c r="Q13" s="247" t="s">
         <v>279</v>
       </c>
-      <c r="R13" s="222"/>
-      <c r="S13" s="222"/>
-      <c r="T13" s="222"/>
-      <c r="U13" s="222">
+      <c r="R13" s="247"/>
+      <c r="S13" s="247"/>
+      <c r="T13" s="247"/>
+      <c r="U13" s="247">
         <v>44.5</v>
       </c>
-      <c r="V13" s="222"/>
+      <c r="V13" s="247"/>
     </row>
     <row r="14" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D14" s="219" t="s">
+      <c r="D14" s="244" t="s">
         <v>278</v>
       </c>
-      <c r="E14" s="219"/>
-      <c r="F14" s="219"/>
-      <c r="G14" s="219"/>
+      <c r="E14" s="244"/>
+      <c r="F14" s="244"/>
+      <c r="G14" s="244"/>
       <c r="H14" s="60" t="str">
         <f>'&lt;zlight&gt;'!G20&amp;"."&amp;'&lt;zlight&gt;'!H20</f>
         <v>.</v>
       </c>
       <c r="I14" s="59"/>
       <c r="P14" s="59"/>
-      <c r="Q14" s="222" t="s">
+      <c r="Q14" s="247" t="s">
         <v>277</v>
       </c>
-      <c r="R14" s="222"/>
-      <c r="S14" s="222"/>
-      <c r="T14" s="222"/>
-      <c r="U14" s="222">
+      <c r="R14" s="247"/>
+      <c r="S14" s="247"/>
+      <c r="T14" s="247"/>
+      <c r="U14" s="247">
         <v>44.5</v>
       </c>
-      <c r="V14" s="222"/>
+      <c r="V14" s="247"/>
     </row>
     <row r="15" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D15" s="219" t="s">
+      <c r="D15" s="244" t="s">
         <v>276</v>
       </c>
-      <c r="E15" s="219"/>
-      <c r="F15" s="219"/>
-      <c r="G15" s="219"/>
+      <c r="E15" s="244"/>
+      <c r="F15" s="244"/>
+      <c r="G15" s="244"/>
       <c r="H15" s="58">
         <v>77</v>
       </c>
       <c r="P15" s="59"/>
-      <c r="Q15" s="231" t="s">
+      <c r="Q15" s="256" t="s">
         <v>275</v>
       </c>
-      <c r="R15" s="231"/>
-      <c r="S15" s="231"/>
-      <c r="T15" s="231"/>
-      <c r="U15" s="232">
+      <c r="R15" s="256"/>
+      <c r="S15" s="256"/>
+      <c r="T15" s="256"/>
+      <c r="U15" s="257">
         <f ca="1">ROUNDUP((U6*1000)/(INDEX(BD!$C$4:$C$5,MATCH(H11,BD!$B$4:$B$5,0))*U8),2)</f>
         <v>0</v>
       </c>
-      <c r="V15" s="232"/>
+      <c r="V15" s="257"/>
     </row>
     <row r="16" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="Q16" s="235" t="s">
+      <c r="Q16" s="260" t="s">
         <v>406</v>
       </c>
-      <c r="R16" s="235"/>
-      <c r="S16" s="235"/>
-      <c r="T16" s="235"/>
-      <c r="U16" s="235" t="e">
+      <c r="R16" s="260"/>
+      <c r="S16" s="260"/>
+      <c r="T16" s="260"/>
+      <c r="U16" s="260" t="e">
         <f>INDEX(BB5:BB9,MATCH(1,BD5:BD9,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="V16" s="235"/>
+      <c r="V16" s="260"/>
     </row>
     <row r="22" spans="1:263" x14ac:dyDescent="0.25">
       <c r="L22" s="141" t="s">
@@ -14906,209 +14895,209 @@
       </c>
     </row>
     <row r="25" spans="1:263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BD25" s="240" t="s">
+      <c r="BD25" s="264" t="s">
         <v>514</v>
       </c>
-      <c r="BE25" s="241"/>
-      <c r="BF25" s="241"/>
-      <c r="BG25" s="241"/>
-      <c r="BH25" s="241"/>
-      <c r="BI25" s="241"/>
-      <c r="BJ25" s="241"/>
-      <c r="BK25" s="241"/>
-      <c r="BL25" s="241"/>
-      <c r="BM25" s="241"/>
-      <c r="BN25" s="241"/>
-      <c r="BO25" s="241"/>
-      <c r="BP25" s="241"/>
-      <c r="BQ25" s="241"/>
-      <c r="BR25" s="241"/>
-      <c r="BS25" s="241"/>
-      <c r="BT25" s="241"/>
-      <c r="BU25" s="241"/>
-      <c r="BV25" s="241"/>
-      <c r="BW25" s="241"/>
-      <c r="BX25" s="241"/>
-      <c r="BY25" s="241"/>
-      <c r="BZ25" s="241"/>
-      <c r="CA25" s="242"/>
-      <c r="CB25" s="240" t="s">
+      <c r="BE25" s="265"/>
+      <c r="BF25" s="265"/>
+      <c r="BG25" s="265"/>
+      <c r="BH25" s="265"/>
+      <c r="BI25" s="265"/>
+      <c r="BJ25" s="265"/>
+      <c r="BK25" s="265"/>
+      <c r="BL25" s="265"/>
+      <c r="BM25" s="265"/>
+      <c r="BN25" s="265"/>
+      <c r="BO25" s="265"/>
+      <c r="BP25" s="265"/>
+      <c r="BQ25" s="265"/>
+      <c r="BR25" s="265"/>
+      <c r="BS25" s="265"/>
+      <c r="BT25" s="265"/>
+      <c r="BU25" s="265"/>
+      <c r="BV25" s="265"/>
+      <c r="BW25" s="265"/>
+      <c r="BX25" s="265"/>
+      <c r="BY25" s="265"/>
+      <c r="BZ25" s="265"/>
+      <c r="CA25" s="266"/>
+      <c r="CB25" s="264" t="s">
         <v>517</v>
       </c>
-      <c r="CC25" s="241"/>
-      <c r="CD25" s="241"/>
-      <c r="CE25" s="241"/>
-      <c r="CF25" s="241"/>
-      <c r="CG25" s="241"/>
-      <c r="CH25" s="241"/>
-      <c r="CI25" s="241"/>
-      <c r="CJ25" s="241"/>
-      <c r="CK25" s="241"/>
-      <c r="CL25" s="241"/>
-      <c r="CM25" s="241"/>
-      <c r="CN25" s="241"/>
-      <c r="CO25" s="241"/>
-      <c r="CP25" s="241"/>
-      <c r="CQ25" s="241"/>
-      <c r="CR25" s="241"/>
-      <c r="CS25" s="241"/>
-      <c r="CT25" s="243" t="s">
+      <c r="CC25" s="265"/>
+      <c r="CD25" s="265"/>
+      <c r="CE25" s="265"/>
+      <c r="CF25" s="265"/>
+      <c r="CG25" s="265"/>
+      <c r="CH25" s="265"/>
+      <c r="CI25" s="265"/>
+      <c r="CJ25" s="265"/>
+      <c r="CK25" s="265"/>
+      <c r="CL25" s="265"/>
+      <c r="CM25" s="265"/>
+      <c r="CN25" s="265"/>
+      <c r="CO25" s="265"/>
+      <c r="CP25" s="265"/>
+      <c r="CQ25" s="265"/>
+      <c r="CR25" s="265"/>
+      <c r="CS25" s="265"/>
+      <c r="CT25" s="267" t="s">
         <v>266</v>
       </c>
-      <c r="CU25" s="244"/>
-      <c r="CV25" s="244"/>
-      <c r="CW25" s="244"/>
-      <c r="CX25" s="244"/>
-      <c r="CY25" s="244"/>
-      <c r="CZ25" s="244"/>
-      <c r="DA25" s="244"/>
-      <c r="DB25" s="244"/>
-      <c r="DC25" s="244"/>
-      <c r="DD25" s="244"/>
-      <c r="DE25" s="244"/>
-      <c r="DF25" s="244"/>
-      <c r="DG25" s="244"/>
-      <c r="DH25" s="244"/>
-      <c r="DI25" s="244"/>
-      <c r="DJ25" s="244"/>
-      <c r="DK25" s="244"/>
-      <c r="DL25" s="244"/>
-      <c r="DM25" s="244"/>
-      <c r="DN25" s="244"/>
-      <c r="DO25" s="244"/>
-      <c r="DP25" s="244"/>
-      <c r="DQ25" s="244"/>
-      <c r="DR25" s="244"/>
-      <c r="DS25" s="244"/>
-      <c r="DT25" s="244"/>
-      <c r="DU25" s="244"/>
-      <c r="DV25" s="244"/>
-      <c r="DW25" s="244"/>
-      <c r="DX25" s="244"/>
-      <c r="DY25" s="244"/>
-      <c r="DZ25" s="244"/>
-      <c r="EA25" s="244"/>
-      <c r="EB25" s="244"/>
-      <c r="EC25" s="244"/>
-      <c r="ED25" s="244"/>
-      <c r="EE25" s="244"/>
-      <c r="EF25" s="244"/>
-      <c r="EG25" s="244"/>
-      <c r="EH25" s="244"/>
-      <c r="EI25" s="244"/>
-      <c r="EJ25" s="244"/>
-      <c r="EK25" s="244"/>
-      <c r="EL25" s="244"/>
-      <c r="EM25" s="244"/>
-      <c r="EN25" s="244"/>
-      <c r="EO25" s="244"/>
-      <c r="EP25" s="244"/>
-      <c r="EQ25" s="244"/>
-      <c r="ER25" s="244"/>
-      <c r="ES25" s="244"/>
-      <c r="ET25" s="244"/>
-      <c r="EU25" s="244"/>
-      <c r="EV25" s="244"/>
-      <c r="EW25" s="244"/>
-      <c r="EX25" s="244"/>
-      <c r="EY25" s="244"/>
-      <c r="EZ25" s="244"/>
-      <c r="FA25" s="244"/>
-      <c r="FB25" s="244"/>
-      <c r="FC25" s="244"/>
-      <c r="FD25" s="244"/>
-      <c r="FE25" s="244"/>
-      <c r="FF25" s="244"/>
-      <c r="FG25" s="244"/>
-      <c r="FH25" s="244"/>
-      <c r="FI25" s="244"/>
-      <c r="FJ25" s="244"/>
-      <c r="FK25" s="244"/>
-      <c r="FL25" s="244"/>
-      <c r="FM25" s="244"/>
-      <c r="FN25" s="244"/>
-      <c r="FO25" s="244"/>
-      <c r="FP25" s="245"/>
+      <c r="CU25" s="268"/>
+      <c r="CV25" s="268"/>
+      <c r="CW25" s="268"/>
+      <c r="CX25" s="268"/>
+      <c r="CY25" s="268"/>
+      <c r="CZ25" s="268"/>
+      <c r="DA25" s="268"/>
+      <c r="DB25" s="268"/>
+      <c r="DC25" s="268"/>
+      <c r="DD25" s="268"/>
+      <c r="DE25" s="268"/>
+      <c r="DF25" s="268"/>
+      <c r="DG25" s="268"/>
+      <c r="DH25" s="268"/>
+      <c r="DI25" s="268"/>
+      <c r="DJ25" s="268"/>
+      <c r="DK25" s="268"/>
+      <c r="DL25" s="268"/>
+      <c r="DM25" s="268"/>
+      <c r="DN25" s="268"/>
+      <c r="DO25" s="268"/>
+      <c r="DP25" s="268"/>
+      <c r="DQ25" s="268"/>
+      <c r="DR25" s="268"/>
+      <c r="DS25" s="268"/>
+      <c r="DT25" s="268"/>
+      <c r="DU25" s="268"/>
+      <c r="DV25" s="268"/>
+      <c r="DW25" s="268"/>
+      <c r="DX25" s="268"/>
+      <c r="DY25" s="268"/>
+      <c r="DZ25" s="268"/>
+      <c r="EA25" s="268"/>
+      <c r="EB25" s="268"/>
+      <c r="EC25" s="268"/>
+      <c r="ED25" s="268"/>
+      <c r="EE25" s="268"/>
+      <c r="EF25" s="268"/>
+      <c r="EG25" s="268"/>
+      <c r="EH25" s="268"/>
+      <c r="EI25" s="268"/>
+      <c r="EJ25" s="268"/>
+      <c r="EK25" s="268"/>
+      <c r="EL25" s="268"/>
+      <c r="EM25" s="268"/>
+      <c r="EN25" s="268"/>
+      <c r="EO25" s="268"/>
+      <c r="EP25" s="268"/>
+      <c r="EQ25" s="268"/>
+      <c r="ER25" s="268"/>
+      <c r="ES25" s="268"/>
+      <c r="ET25" s="268"/>
+      <c r="EU25" s="268"/>
+      <c r="EV25" s="268"/>
+      <c r="EW25" s="268"/>
+      <c r="EX25" s="268"/>
+      <c r="EY25" s="268"/>
+      <c r="EZ25" s="268"/>
+      <c r="FA25" s="268"/>
+      <c r="FB25" s="268"/>
+      <c r="FC25" s="268"/>
+      <c r="FD25" s="268"/>
+      <c r="FE25" s="268"/>
+      <c r="FF25" s="268"/>
+      <c r="FG25" s="268"/>
+      <c r="FH25" s="268"/>
+      <c r="FI25" s="268"/>
+      <c r="FJ25" s="268"/>
+      <c r="FK25" s="268"/>
+      <c r="FL25" s="268"/>
+      <c r="FM25" s="268"/>
+      <c r="FN25" s="268"/>
+      <c r="FO25" s="268"/>
+      <c r="FP25" s="269"/>
     </row>
     <row r="26" spans="1:263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="233" t="s">
+      <c r="D26" s="258" t="s">
         <v>274</v>
       </c>
-      <c r="E26" s="230" t="s">
+      <c r="E26" s="255" t="s">
         <v>225</v>
       </c>
-      <c r="F26" s="230" t="s">
+      <c r="F26" s="255" t="s">
         <v>224</v>
       </c>
-      <c r="G26" s="230" t="s">
+      <c r="G26" s="255" t="s">
         <v>273</v>
       </c>
-      <c r="H26" s="230" t="s">
+      <c r="H26" s="255" t="s">
         <v>272</v>
       </c>
-      <c r="I26" s="230" t="s">
+      <c r="I26" s="255" t="s">
         <v>271</v>
       </c>
-      <c r="J26" s="255" t="s">
+      <c r="J26" s="279" t="s">
         <v>612</v>
       </c>
-      <c r="K26" s="234" t="s">
+      <c r="K26" s="259" t="s">
         <v>390</v>
       </c>
-      <c r="L26" s="258" t="s">
+      <c r="L26" s="282" t="s">
         <v>391</v>
       </c>
-      <c r="M26" s="258"/>
-      <c r="N26" s="258"/>
-      <c r="O26" s="230" t="s">
+      <c r="M26" s="282"/>
+      <c r="N26" s="282"/>
+      <c r="O26" s="255" t="s">
         <v>270</v>
       </c>
-      <c r="P26" s="259" t="s">
+      <c r="P26" s="283" t="s">
         <v>269</v>
       </c>
-      <c r="Q26" s="259"/>
-      <c r="R26" s="259"/>
-      <c r="S26" s="259"/>
-      <c r="T26" s="259"/>
-      <c r="U26" s="259"/>
-      <c r="V26" s="259"/>
-      <c r="W26" s="259"/>
-      <c r="X26" s="259"/>
-      <c r="Y26" s="259"/>
-      <c r="Z26" s="259"/>
-      <c r="AA26" s="259"/>
-      <c r="AB26" s="260" t="s">
+      <c r="Q26" s="283"/>
+      <c r="R26" s="283"/>
+      <c r="S26" s="283"/>
+      <c r="T26" s="283"/>
+      <c r="U26" s="283"/>
+      <c r="V26" s="283"/>
+      <c r="W26" s="283"/>
+      <c r="X26" s="283"/>
+      <c r="Y26" s="283"/>
+      <c r="Z26" s="283"/>
+      <c r="AA26" s="283"/>
+      <c r="AB26" s="284" t="s">
         <v>268</v>
       </c>
-      <c r="AC26" s="260"/>
-      <c r="AD26" s="260"/>
-      <c r="AE26" s="260"/>
-      <c r="AF26" s="260"/>
-      <c r="AG26" s="260"/>
-      <c r="AH26" s="260"/>
-      <c r="AI26" s="260"/>
-      <c r="AJ26" s="260"/>
-      <c r="AK26" s="260"/>
-      <c r="AL26" s="260"/>
-      <c r="AM26" s="260"/>
-      <c r="AN26" s="260" t="s">
+      <c r="AC26" s="284"/>
+      <c r="AD26" s="284"/>
+      <c r="AE26" s="284"/>
+      <c r="AF26" s="284"/>
+      <c r="AG26" s="284"/>
+      <c r="AH26" s="284"/>
+      <c r="AI26" s="284"/>
+      <c r="AJ26" s="284"/>
+      <c r="AK26" s="284"/>
+      <c r="AL26" s="284"/>
+      <c r="AM26" s="284"/>
+      <c r="AN26" s="284" t="s">
         <v>267</v>
       </c>
-      <c r="AO26" s="260"/>
-      <c r="AP26" s="260"/>
-      <c r="AQ26" s="260"/>
-      <c r="AR26" s="260"/>
-      <c r="AS26" s="260"/>
-      <c r="AT26" s="260"/>
-      <c r="AU26" s="260"/>
-      <c r="AV26" s="260"/>
-      <c r="AW26" s="260"/>
-      <c r="AX26" s="260"/>
-      <c r="AY26" s="260"/>
-      <c r="AZ26" s="260"/>
-      <c r="BA26" s="260"/>
-      <c r="BB26" s="260"/>
-      <c r="BC26" s="260"/>
+      <c r="AO26" s="284"/>
+      <c r="AP26" s="284"/>
+      <c r="AQ26" s="284"/>
+      <c r="AR26" s="284"/>
+      <c r="AS26" s="284"/>
+      <c r="AT26" s="284"/>
+      <c r="AU26" s="284"/>
+      <c r="AV26" s="284"/>
+      <c r="AW26" s="284"/>
+      <c r="AX26" s="284"/>
+      <c r="AY26" s="284"/>
+      <c r="AZ26" s="284"/>
+      <c r="BA26" s="284"/>
+      <c r="BB26" s="284"/>
+      <c r="BC26" s="284"/>
       <c r="BD26" s="59"/>
       <c r="BE26" s="59"/>
       <c r="BF26" s="59"/>
@@ -15117,26 +15106,26 @@
       <c r="BI26" s="59"/>
       <c r="BJ26" s="59"/>
       <c r="BK26" s="59"/>
-      <c r="BL26" s="262" t="s">
+      <c r="BL26" s="286" t="s">
         <v>503</v>
       </c>
-      <c r="BM26" s="262"/>
-      <c r="BN26" s="262"/>
-      <c r="BO26" s="262"/>
-      <c r="BP26" s="262"/>
-      <c r="BQ26" s="262"/>
-      <c r="BR26" s="262"/>
-      <c r="BS26" s="262"/>
+      <c r="BM26" s="286"/>
+      <c r="BN26" s="286"/>
+      <c r="BO26" s="286"/>
+      <c r="BP26" s="286"/>
+      <c r="BQ26" s="286"/>
+      <c r="BR26" s="286"/>
+      <c r="BS26" s="286"/>
       <c r="BT26" s="59"/>
       <c r="BU26" s="59"/>
       <c r="BV26" s="59"/>
-      <c r="BW26" s="263" t="s">
+      <c r="BW26" s="287" t="s">
         <v>516</v>
       </c>
-      <c r="BX26" s="263"/>
-      <c r="BY26" s="263"/>
-      <c r="BZ26" s="263"/>
-      <c r="CA26" s="263"/>
+      <c r="BX26" s="287"/>
+      <c r="BY26" s="287"/>
+      <c r="BZ26" s="287"/>
+      <c r="CA26" s="287"/>
       <c r="CB26" s="59"/>
       <c r="CC26" s="59"/>
       <c r="CD26" s="59"/>
@@ -15167,84 +15156,84 @@
       <c r="DC26" s="59"/>
       <c r="DD26" s="59"/>
       <c r="DE26" s="59"/>
-      <c r="DF26" s="252" t="s">
+      <c r="DF26" s="276" t="s">
         <v>535</v>
       </c>
-      <c r="DG26" s="252"/>
-      <c r="DH26" s="252"/>
-      <c r="DI26" s="252"/>
-      <c r="DJ26" s="252"/>
-      <c r="DK26" s="252"/>
-      <c r="DL26" s="252"/>
-      <c r="DM26" s="252"/>
-      <c r="DN26" s="252"/>
-      <c r="DO26" s="252"/>
-      <c r="DP26" s="252"/>
-      <c r="DQ26" s="252"/>
-      <c r="DR26" s="252"/>
-      <c r="DS26" s="252"/>
-      <c r="DT26" s="252"/>
-      <c r="DU26" s="252"/>
-      <c r="DV26" s="252"/>
-      <c r="DW26" s="252"/>
-      <c r="DX26" s="251" t="s">
+      <c r="DG26" s="276"/>
+      <c r="DH26" s="276"/>
+      <c r="DI26" s="276"/>
+      <c r="DJ26" s="276"/>
+      <c r="DK26" s="276"/>
+      <c r="DL26" s="276"/>
+      <c r="DM26" s="276"/>
+      <c r="DN26" s="276"/>
+      <c r="DO26" s="276"/>
+      <c r="DP26" s="276"/>
+      <c r="DQ26" s="276"/>
+      <c r="DR26" s="276"/>
+      <c r="DS26" s="276"/>
+      <c r="DT26" s="276"/>
+      <c r="DU26" s="276"/>
+      <c r="DV26" s="276"/>
+      <c r="DW26" s="276"/>
+      <c r="DX26" s="275" t="s">
         <v>206</v>
       </c>
-      <c r="DY26" s="251"/>
-      <c r="DZ26" s="251"/>
-      <c r="EA26" s="236" t="s">
+      <c r="DY26" s="275"/>
+      <c r="DZ26" s="275"/>
+      <c r="EA26" s="261" t="s">
         <v>205</v>
       </c>
-      <c r="EB26" s="237"/>
-      <c r="EC26" s="237"/>
-      <c r="ED26" s="237"/>
-      <c r="EE26" s="237"/>
-      <c r="EF26" s="237"/>
-      <c r="EG26" s="237"/>
-      <c r="EH26" s="237"/>
-      <c r="EI26" s="237"/>
-      <c r="EJ26" s="237"/>
-      <c r="EK26" s="237"/>
-      <c r="EL26" s="237"/>
-      <c r="EM26" s="237"/>
-      <c r="EN26" s="237"/>
-      <c r="EO26" s="237"/>
-      <c r="EP26" s="237"/>
-      <c r="EQ26" s="253" t="s">
+      <c r="EB26" s="262"/>
+      <c r="EC26" s="262"/>
+      <c r="ED26" s="262"/>
+      <c r="EE26" s="262"/>
+      <c r="EF26" s="262"/>
+      <c r="EG26" s="262"/>
+      <c r="EH26" s="262"/>
+      <c r="EI26" s="262"/>
+      <c r="EJ26" s="262"/>
+      <c r="EK26" s="262"/>
+      <c r="EL26" s="262"/>
+      <c r="EM26" s="262"/>
+      <c r="EN26" s="262"/>
+      <c r="EO26" s="262"/>
+      <c r="EP26" s="262"/>
+      <c r="EQ26" s="277" t="s">
         <v>204</v>
       </c>
-      <c r="ER26" s="253"/>
-      <c r="ES26" s="253"/>
-      <c r="ET26" s="253"/>
-      <c r="EU26" s="253"/>
-      <c r="EV26" s="253"/>
-      <c r="EW26" s="254" t="s">
+      <c r="ER26" s="277"/>
+      <c r="ES26" s="277"/>
+      <c r="ET26" s="277"/>
+      <c r="EU26" s="277"/>
+      <c r="EV26" s="277"/>
+      <c r="EW26" s="278" t="s">
         <v>203</v>
       </c>
-      <c r="EX26" s="254"/>
-      <c r="EY26" s="254"/>
-      <c r="EZ26" s="254"/>
-      <c r="FA26" s="254" t="s">
+      <c r="EX26" s="278"/>
+      <c r="EY26" s="278"/>
+      <c r="EZ26" s="278"/>
+      <c r="FA26" s="278" t="s">
         <v>202</v>
       </c>
-      <c r="FB26" s="254"/>
-      <c r="FC26" s="254"/>
-      <c r="FD26" s="254"/>
-      <c r="FE26" s="254" t="s">
+      <c r="FB26" s="278"/>
+      <c r="FC26" s="278"/>
+      <c r="FD26" s="278"/>
+      <c r="FE26" s="278" t="s">
         <v>201</v>
       </c>
-      <c r="FF26" s="254"/>
-      <c r="FG26" s="254"/>
-      <c r="FH26" s="254"/>
-      <c r="FI26" s="254"/>
-      <c r="FJ26" s="254"/>
-      <c r="FK26" s="254" t="s">
+      <c r="FF26" s="278"/>
+      <c r="FG26" s="278"/>
+      <c r="FH26" s="278"/>
+      <c r="FI26" s="278"/>
+      <c r="FJ26" s="278"/>
+      <c r="FK26" s="278" t="s">
         <v>200</v>
       </c>
-      <c r="FL26" s="254"/>
-      <c r="FM26" s="254"/>
-      <c r="FN26" s="254"/>
-      <c r="FO26" s="254"/>
+      <c r="FL26" s="278"/>
+      <c r="FM26" s="278"/>
+      <c r="FN26" s="278"/>
+      <c r="FO26" s="278"/>
       <c r="FP26" s="59"/>
       <c r="FQ26" s="83"/>
       <c r="FR26" s="83"/>
@@ -15327,14 +15316,14 @@
       </c>
     </row>
     <row r="27" spans="1:263" ht="103.5" x14ac:dyDescent="0.25">
-      <c r="D27" s="233"/>
-      <c r="E27" s="230"/>
-      <c r="F27" s="230"/>
-      <c r="G27" s="230"/>
-      <c r="H27" s="230"/>
-      <c r="I27" s="230"/>
-      <c r="J27" s="256"/>
-      <c r="K27" s="234"/>
+      <c r="D27" s="258"/>
+      <c r="E27" s="255"/>
+      <c r="F27" s="255"/>
+      <c r="G27" s="255"/>
+      <c r="H27" s="255"/>
+      <c r="I27" s="255"/>
+      <c r="J27" s="280"/>
+      <c r="K27" s="259"/>
       <c r="L27" s="93" t="s">
         <v>257</v>
       </c>
@@ -15344,7 +15333,7 @@
       <c r="N27" s="93" t="s">
         <v>255</v>
       </c>
-      <c r="O27" s="230"/>
+      <c r="O27" s="255"/>
       <c r="P27" s="163" t="s">
         <v>329</v>
       </c>
@@ -15810,10 +15799,10 @@
       <c r="FP27" s="195" t="s">
         <v>432</v>
       </c>
-      <c r="FQ27" s="264" t="s">
+      <c r="FQ27" s="288" t="s">
         <v>593</v>
       </c>
-      <c r="FR27" s="264"/>
+      <c r="FR27" s="288"/>
       <c r="FU27" s="115">
         <f>35*$AA$5</f>
         <v>35</v>
@@ -15839,40 +15828,40 @@
       <c r="GQ27" s="106"/>
       <c r="GR27" s="106"/>
       <c r="GS27" s="106"/>
-      <c r="HM27" s="261" t="s">
+      <c r="HM27" s="285" t="s">
         <v>421</v>
       </c>
-      <c r="HN27" s="261"/>
-      <c r="HO27" s="261"/>
-      <c r="HP27" s="261"/>
-      <c r="HQ27" s="261"/>
-      <c r="HR27" s="261"/>
-      <c r="HS27" s="261"/>
-      <c r="HT27" s="261"/>
-      <c r="HU27" s="239" t="s">
+      <c r="HN27" s="285"/>
+      <c r="HO27" s="285"/>
+      <c r="HP27" s="285"/>
+      <c r="HQ27" s="285"/>
+      <c r="HR27" s="285"/>
+      <c r="HS27" s="285"/>
+      <c r="HT27" s="285"/>
+      <c r="HU27" s="263" t="s">
         <v>211</v>
       </c>
-      <c r="HV27" s="239"/>
-      <c r="HW27" s="239"/>
-      <c r="HX27" s="239"/>
-      <c r="HY27" s="239"/>
-      <c r="HZ27" s="239"/>
-      <c r="IA27" s="239"/>
-      <c r="IB27" s="239"/>
-      <c r="IC27" s="239"/>
-      <c r="ID27" s="239"/>
-      <c r="IE27" s="257" t="s">
+      <c r="HV27" s="263"/>
+      <c r="HW27" s="263"/>
+      <c r="HX27" s="263"/>
+      <c r="HY27" s="263"/>
+      <c r="HZ27" s="263"/>
+      <c r="IA27" s="263"/>
+      <c r="IB27" s="263"/>
+      <c r="IC27" s="263"/>
+      <c r="ID27" s="263"/>
+      <c r="IE27" s="281" t="s">
         <v>210</v>
       </c>
-      <c r="IF27" s="257"/>
-      <c r="IG27" s="257"/>
-      <c r="IH27" s="257"/>
-      <c r="II27" s="257"/>
-      <c r="IJ27" s="257"/>
-      <c r="IK27" s="257"/>
-      <c r="IL27" s="257"/>
-      <c r="IM27" s="257"/>
-      <c r="IN27" s="257"/>
+      <c r="IF27" s="281"/>
+      <c r="IG27" s="281"/>
+      <c r="IH27" s="281"/>
+      <c r="II27" s="281"/>
+      <c r="IJ27" s="281"/>
+      <c r="IK27" s="281"/>
+      <c r="IL27" s="281"/>
+      <c r="IM27" s="281"/>
+      <c r="IN27" s="281"/>
       <c r="IO27" s="216" t="s">
         <v>237</v>
       </c>
@@ -17090,27 +17079,27 @@
     </row>
     <row r="3" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="C3" s="61"/>
-      <c r="D3" s="285" t="s">
+      <c r="D3" s="239" t="s">
         <v>331</v>
       </c>
-      <c r="E3" s="285"/>
-      <c r="F3" s="285"/>
-      <c r="G3" s="285" t="s">
+      <c r="E3" s="239"/>
+      <c r="F3" s="239"/>
+      <c r="G3" s="239" t="s">
         <v>332</v>
       </c>
-      <c r="H3" s="285"/>
-      <c r="I3" s="285"/>
+      <c r="H3" s="239"/>
+      <c r="I3" s="239"/>
       <c r="J3" s="71" t="s">
         <v>335</v>
       </c>
       <c r="K3" s="71" t="s">
         <v>333</v>
       </c>
-      <c r="L3" s="285" t="s">
+      <c r="L3" s="239" t="s">
         <v>334</v>
       </c>
-      <c r="M3" s="285"/>
-      <c r="N3" s="285"/>
+      <c r="M3" s="239"/>
+      <c r="N3" s="239"/>
       <c r="O3" s="289" t="s">
         <v>342</v>
       </c>
@@ -17241,41 +17230,41 @@
   <sheetData>
     <row r="1" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="266" t="s">
+      <c r="B2" s="220" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="267"/>
-      <c r="D2" s="267"/>
-      <c r="E2" s="267"/>
-      <c r="F2" s="267"/>
-      <c r="G2" s="267"/>
-      <c r="H2" s="267"/>
-      <c r="I2" s="267"/>
-      <c r="J2" s="267"/>
-      <c r="K2" s="267"/>
-      <c r="L2" s="267"/>
-      <c r="M2" s="267"/>
-      <c r="N2" s="267"/>
-      <c r="O2" s="267"/>
-      <c r="P2" s="267"/>
-      <c r="Q2" s="267"/>
-      <c r="R2" s="267"/>
-      <c r="S2" s="267"/>
-      <c r="T2" s="267"/>
-      <c r="U2" s="267"/>
-      <c r="V2" s="267"/>
-      <c r="W2" s="267"/>
-      <c r="X2" s="267"/>
-      <c r="Y2" s="267"/>
-      <c r="Z2" s="267"/>
-      <c r="AA2" s="267"/>
-      <c r="AB2" s="267"/>
-      <c r="AC2" s="267"/>
-      <c r="AD2" s="267"/>
-      <c r="AE2" s="267"/>
-      <c r="AF2" s="267"/>
-      <c r="AG2" s="267"/>
-      <c r="AH2" s="278"/>
+      <c r="C2" s="221"/>
+      <c r="D2" s="221"/>
+      <c r="E2" s="221"/>
+      <c r="F2" s="221"/>
+      <c r="G2" s="221"/>
+      <c r="H2" s="221"/>
+      <c r="I2" s="221"/>
+      <c r="J2" s="221"/>
+      <c r="K2" s="221"/>
+      <c r="L2" s="221"/>
+      <c r="M2" s="221"/>
+      <c r="N2" s="221"/>
+      <c r="O2" s="221"/>
+      <c r="P2" s="221"/>
+      <c r="Q2" s="221"/>
+      <c r="R2" s="221"/>
+      <c r="S2" s="221"/>
+      <c r="T2" s="221"/>
+      <c r="U2" s="221"/>
+      <c r="V2" s="221"/>
+      <c r="W2" s="221"/>
+      <c r="X2" s="221"/>
+      <c r="Y2" s="221"/>
+      <c r="Z2" s="221"/>
+      <c r="AA2" s="221"/>
+      <c r="AB2" s="221"/>
+      <c r="AC2" s="221"/>
+      <c r="AD2" s="221"/>
+      <c r="AE2" s="221"/>
+      <c r="AF2" s="221"/>
+      <c r="AG2" s="221"/>
+      <c r="AH2" s="232"/>
     </row>
     <row r="3" spans="2:34" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="44" t="s">
@@ -18698,49 +18687,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="279" t="s">
+      <c r="B1" s="233" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="279"/>
-      <c r="D1" s="279"/>
-      <c r="E1" s="279"/>
-      <c r="F1" s="279"/>
-      <c r="G1" s="279"/>
-      <c r="H1" s="279"/>
-      <c r="I1" s="279"/>
-      <c r="J1" s="279"/>
-      <c r="K1" s="279"/>
-      <c r="L1" s="279"/>
-      <c r="M1" s="279"/>
-      <c r="N1" s="279"/>
-      <c r="O1" s="279"/>
-      <c r="P1" s="279"/>
-      <c r="Q1" s="279"/>
-      <c r="R1" s="279"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="233"/>
+      <c r="L1" s="233"/>
+      <c r="M1" s="233"/>
+      <c r="N1" s="233"/>
+      <c r="O1" s="233"/>
+      <c r="P1" s="233"/>
+      <c r="Q1" s="233"/>
+      <c r="R1" s="233"/>
     </row>
     <row r="2" spans="1:18" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="24"/>
       <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="280" t="s">
+      <c r="C2" s="234" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="280"/>
-      <c r="E2" s="280"/>
-      <c r="F2" s="280"/>
-      <c r="G2" s="280"/>
-      <c r="H2" s="280"/>
-      <c r="I2" s="280"/>
-      <c r="J2" s="280"/>
-      <c r="K2" s="280"/>
-      <c r="L2" s="280"/>
-      <c r="M2" s="280"/>
-      <c r="N2" s="280"/>
-      <c r="O2" s="280"/>
-      <c r="P2" s="280"/>
-      <c r="Q2" s="280"/>
-      <c r="R2" s="281"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
+      <c r="G2" s="234"/>
+      <c r="H2" s="234"/>
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
+      <c r="K2" s="234"/>
+      <c r="L2" s="234"/>
+      <c r="M2" s="234"/>
+      <c r="N2" s="234"/>
+      <c r="O2" s="234"/>
+      <c r="P2" s="234"/>
+      <c r="Q2" s="234"/>
+      <c r="R2" s="235"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
@@ -19199,14 +19188,14 @@
   <sheetData>
     <row r="1" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="282" t="s">
+      <c r="C2" s="236" t="s">
         <v>422</v>
       </c>
-      <c r="D2" s="283"/>
-      <c r="E2" s="283"/>
-      <c r="F2" s="283"/>
-      <c r="G2" s="283"/>
-      <c r="H2" s="284"/>
+      <c r="D2" s="237"/>
+      <c r="E2" s="237"/>
+      <c r="F2" s="237"/>
+      <c r="G2" s="237"/>
+      <c r="H2" s="238"/>
     </row>
     <row r="3" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C3" s="110" t="s">
@@ -20552,11 +20541,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:68" x14ac:dyDescent="0.25">
-      <c r="D3" s="286" t="s">
+      <c r="D3" s="240" t="s">
         <v>316</v>
       </c>
-      <c r="E3" s="286"/>
-      <c r="F3" s="286"/>
+      <c r="E3" s="240"/>
+      <c r="F3" s="240"/>
     </row>
     <row r="4" spans="1:68" x14ac:dyDescent="0.25">
       <c r="D4" s="63" t="s">
@@ -20779,71 +20768,71 @@
     </row>
     <row r="8" spans="1:68" ht="135" x14ac:dyDescent="0.25">
       <c r="B8" s="211"/>
-      <c r="C8" s="285" t="s">
+      <c r="C8" s="239" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="285"/>
-      <c r="E8" s="285"/>
-      <c r="F8" s="287" t="s">
+      <c r="D8" s="239"/>
+      <c r="E8" s="239"/>
+      <c r="F8" s="241" t="s">
         <v>323</v>
       </c>
-      <c r="G8" s="287"/>
-      <c r="H8" s="287"/>
-      <c r="I8" s="285" t="s">
+      <c r="G8" s="241"/>
+      <c r="H8" s="241"/>
+      <c r="I8" s="239" t="s">
         <v>165</v>
       </c>
-      <c r="J8" s="285"/>
-      <c r="K8" s="285"/>
-      <c r="L8" s="285" t="s">
+      <c r="J8" s="239"/>
+      <c r="K8" s="239"/>
+      <c r="L8" s="239" t="s">
         <v>178</v>
       </c>
-      <c r="M8" s="285"/>
-      <c r="N8" s="285"/>
-      <c r="O8" s="285" t="s">
+      <c r="M8" s="239"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="239" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="285"/>
-      <c r="Q8" s="285"/>
-      <c r="R8" s="285" t="s">
+      <c r="P8" s="239"/>
+      <c r="Q8" s="239"/>
+      <c r="R8" s="239" t="s">
         <v>179</v>
       </c>
-      <c r="S8" s="285"/>
-      <c r="T8" s="285"/>
-      <c r="U8" s="285" t="s">
+      <c r="S8" s="239"/>
+      <c r="T8" s="239"/>
+      <c r="U8" s="239" t="s">
         <v>166</v>
       </c>
-      <c r="V8" s="285"/>
-      <c r="W8" s="285"/>
-      <c r="X8" s="285" t="s">
+      <c r="V8" s="239"/>
+      <c r="W8" s="239"/>
+      <c r="X8" s="239" t="s">
         <v>181</v>
       </c>
-      <c r="Y8" s="285"/>
-      <c r="Z8" s="285"/>
-      <c r="AA8" s="285" t="s">
+      <c r="Y8" s="239"/>
+      <c r="Z8" s="239"/>
+      <c r="AA8" s="239" t="s">
         <v>182</v>
       </c>
-      <c r="AB8" s="285"/>
-      <c r="AC8" s="285"/>
-      <c r="AD8" s="285" t="s">
+      <c r="AB8" s="239"/>
+      <c r="AC8" s="239"/>
+      <c r="AD8" s="239" t="s">
         <v>3</v>
       </c>
-      <c r="AE8" s="285"/>
-      <c r="AF8" s="285"/>
-      <c r="AG8" s="285" t="s">
+      <c r="AE8" s="239"/>
+      <c r="AF8" s="239"/>
+      <c r="AG8" s="239" t="s">
         <v>380</v>
       </c>
-      <c r="AH8" s="285"/>
-      <c r="AI8" s="285"/>
-      <c r="AJ8" s="285" t="s">
+      <c r="AH8" s="239"/>
+      <c r="AI8" s="239"/>
+      <c r="AJ8" s="239" t="s">
         <v>599</v>
       </c>
-      <c r="AK8" s="285"/>
-      <c r="AL8" s="285"/>
-      <c r="AM8" s="285" t="s">
+      <c r="AK8" s="239"/>
+      <c r="AL8" s="239"/>
+      <c r="AM8" s="239" t="s">
         <v>595</v>
       </c>
-      <c r="AN8" s="285"/>
-      <c r="AO8" s="285"/>
+      <c r="AN8" s="239"/>
+      <c r="AO8" s="239"/>
       <c r="AP8" s="101" t="s">
         <v>419</v>
       </c>

--- a/environment/runtimefiles/AllCPU-AllOS/zcadelectrotech/data/preload/xlsxtemplates/modelinxlsx/+++EMO_NEWMETHOD_LAST.xlsx
+++ b/environment/runtimefiles/AllCPU-AllOS/zcadelectrotech/data/preload/xlsxtemplates/modelinxlsx/+++EMO_NEWMETHOD_LAST.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ЭтаКнига" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\zcad\zcadMaster\environment\runtimefiles\AllCPU-AllOS\zcadelectrotech\data\preload\xlsxtemplates\modelinxlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\zcad\zcadMASTER\environment\runtimefiles\AllCPU-AllOS\zcadelectrotech\data\preload\xlsxtemplates\modelinxlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44607A5F-266B-4ADC-AC13-CCBA7FA7DB19}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911C70B1-2494-488E-86D5-952C10AF7F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4350" yWindow="6615" windowWidth="21705" windowHeight="14025" tabRatio="643" firstSheet="11" activeTab="12" xr2:uid="{456AB35E-0355-4F16-B1D8-5CF582B696FE}"/>
+    <workbookView xWindow="6630" yWindow="2445" windowWidth="40725" windowHeight="17940" tabRatio="643" activeTab="4" xr2:uid="{456AB35E-0355-4F16-B1D8-5CF582B696FE}"/>
   </bookViews>
   <sheets>
     <sheet name="BD" sheetId="4" r:id="rId1"/>
@@ -21,21 +21,33 @@
     <sheet name="&lt;workbook&gt;SET" sheetId="7" r:id="rId6"/>
     <sheet name="&lt;zalldev&gt;SET" sheetId="15" r:id="rId7"/>
     <sheet name="&lt;zalldev&gt;EXPORT" sheetId="11" r:id="rId8"/>
-    <sheet name="&lt;zalldev&gt;TEMPLATEKZ" sheetId="17" r:id="rId9"/>
-    <sheet name="&lt;zallcab&gt;SET" sheetId="23" r:id="rId10"/>
-    <sheet name="&lt;zallcab&gt;CALC" sheetId="24" r:id="rId11"/>
-    <sheet name="&lt;zallcab&gt;CabZhurnal" sheetId="29" r:id="rId12"/>
-    <sheet name="&lt;zallcab&gt;CabGroup" sheetId="28" r:id="rId13"/>
-    <sheet name="&lt;zlight&gt;SET" sheetId="18" r:id="rId14"/>
-    <sheet name="&lt;zlight&gt;TEMP" sheetId="21" r:id="rId15"/>
-    <sheet name="&lt;zlight&gt;TEMPGU" sheetId="22" r:id="rId16"/>
-    <sheet name="&lt;zlight&gt;" sheetId="20" r:id="rId17"/>
-    <sheet name="&lt;zallcab&gt;EXPORT" sheetId="14" r:id="rId18"/>
+    <sheet name="&lt;zalldev&gt;DevGroup" sheetId="30" r:id="rId9"/>
+    <sheet name="&lt;zalldev&gt;TEMPLATEKZ" sheetId="17" r:id="rId10"/>
+    <sheet name="&lt;zallcab&gt;SET" sheetId="23" r:id="rId11"/>
+    <sheet name="&lt;zallcab&gt;EXPORT" sheetId="14" r:id="rId12"/>
+    <sheet name="&lt;zallcab&gt;CALC" sheetId="24" r:id="rId13"/>
+    <sheet name="&lt;zallcab&gt;CabZhurnal" sheetId="29" r:id="rId14"/>
+    <sheet name="&lt;zallcab&gt;CabGroup" sheetId="28" r:id="rId15"/>
+    <sheet name="&lt;zlight&gt;SET" sheetId="18" r:id="rId16"/>
+    <sheet name="&lt;zlight&gt;TEMP" sheetId="21" r:id="rId17"/>
+    <sheet name="&lt;zlight&gt;TEMPGU" sheetId="22" r:id="rId18"/>
+    <sheet name="&lt;zlight&gt;" sheetId="20" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -771,14 +783,14 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -793,7 +805,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="650">
   <si>
     <t>&lt;zlight&gt;</t>
   </si>
@@ -1889,27 +1901,15 @@
     <t>Hidden~inPipe</t>
   </si>
   <si>
-    <t>Скрыто в метал.тр.</t>
-  </si>
-  <si>
     <t>Hidden~underPlaster</t>
   </si>
   <si>
-    <t>Скрыто под штукатур</t>
-  </si>
-  <si>
     <t>open~inMetalTray</t>
   </si>
   <si>
-    <t>в метал.лотке</t>
-  </si>
-  <si>
     <t>open~inCableChannel</t>
   </si>
   <si>
-    <t>в каб.канал</t>
-  </si>
-  <si>
     <t>open~inPipePVC</t>
   </si>
   <si>
@@ -1917,9 +1917,6 @@
   </si>
   <si>
     <t>open~inPip</t>
-  </si>
-  <si>
-    <t>откр. в мет.тр.</t>
   </si>
   <si>
     <t>Имя кабеля</t>
@@ -2611,12 +2608,6 @@
     <t>&lt;zdevsettings name=[ANALYSISEM_exporttoxlsx] type=[boolean]&gt;</t>
   </si>
   <si>
-    <t>&lt;zcopyrow targetsheet=[&lt;zalldev&gt;EXPORT] targetcodename=[zalldevimport] keynumcol=[56]&gt;</t>
-  </si>
-  <si>
-    <t>&lt;zcopyrow targetsheet=[&lt;zalldev&gt;EXPORT] targetcodename=[zalldevimport] keynumcol=[55]&gt;</t>
-  </si>
-  <si>
     <t>VEL_POWER_SHR05</t>
   </si>
   <si>
@@ -2714,6 +2705,69 @@
   </si>
   <si>
     <t>Метод</t>
+  </si>
+  <si>
+    <t>&lt;zcopyrow targetsheet=[&lt;zalldev&gt;EXPORT] targetcodename=[zalldevimport] keynumcol=[58]&gt;</t>
+  </si>
+  <si>
+    <t>&lt;zcopyrow targetsheet=[&lt;zalldev&gt;EXPORT] targetcodename=[zalldevimport] keynumcol=[59]&gt;</t>
+  </si>
+  <si>
+    <t>&lt;zdevsettings name=[Space_RoomPos] type=[string]&gt;</t>
+  </si>
+  <si>
+    <t>номер помещения</t>
+  </si>
+  <si>
+    <t>Группирование по именам и группам</t>
+  </si>
+  <si>
+    <t>Уникальность</t>
+  </si>
+  <si>
+    <t>&lt;zalldev&gt;DevGroup</t>
+  </si>
+  <si>
+    <t>&lt;zcopyrow targetsheet=[&lt;zalldev&gt;EXPORT] targetcodename=[zalldevimport] keynumcol=[67]&gt;</t>
+  </si>
+  <si>
+    <t>Номер группы</t>
+  </si>
+  <si>
+    <t>Позиция устройства</t>
+  </si>
+  <si>
+    <t>Сорт группирования</t>
+  </si>
+  <si>
+    <t>сорт имя ГУ</t>
+  </si>
+  <si>
+    <t>Сорт группа</t>
+  </si>
+  <si>
+    <t>Сорт Имя</t>
+  </si>
+  <si>
+    <t>Сорт помещение</t>
+  </si>
+  <si>
+    <t>Имя кабеля + устройство</t>
+  </si>
+  <si>
+    <t>в мет.тр.</t>
+  </si>
+  <si>
+    <t>в штробе</t>
+  </si>
+  <si>
+    <t>в лотке</t>
+  </si>
+  <si>
+    <t>в к/к</t>
+  </si>
+  <si>
+    <t>скр. в мет.тр.</t>
   </si>
 </sst>
 </file>
@@ -3004,7 +3058,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="68">
+  <fills count="69">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3404,6 +3458,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -4106,7 +4166,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="290">
+  <cellXfs count="293">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4300,9 +4360,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4338,7 +4395,6 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4778,81 +4834,19 @@
     <xf numFmtId="0" fontId="0" fillId="67" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="68" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="68" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4912,6 +4906,9 @@
     <xf numFmtId="0" fontId="0" fillId="46" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="38" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5003,8 +5000,80 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="43" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="43" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5411,9 +5480,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5451,7 +5520,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -5557,7 +5626,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5699,7 +5768,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5721,87 +5790,87 @@
   <sheetData>
     <row r="2" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:79" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="222" t="s">
+      <c r="A3" s="271" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="223"/>
-      <c r="C3" s="224"/>
-      <c r="F3" s="225" t="s">
+      <c r="B3" s="272"/>
+      <c r="C3" s="273"/>
+      <c r="F3" s="274" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="226"/>
-      <c r="H3" s="227"/>
-      <c r="K3" s="220" t="s">
+      <c r="G3" s="275"/>
+      <c r="H3" s="276"/>
+      <c r="K3" s="269" t="s">
         <v>73</v>
       </c>
-      <c r="L3" s="221"/>
-      <c r="M3" s="221"/>
-      <c r="N3" s="221"/>
-      <c r="O3" s="221"/>
-      <c r="P3" s="221"/>
-      <c r="Q3" s="221"/>
-      <c r="R3" s="221"/>
-      <c r="S3" s="221"/>
-      <c r="T3" s="221"/>
-      <c r="U3" s="221"/>
-      <c r="V3" s="221"/>
-      <c r="W3" s="221"/>
-      <c r="X3" s="221"/>
-      <c r="Y3" s="221"/>
-      <c r="Z3" s="221"/>
-      <c r="AA3" s="221"/>
-      <c r="AB3" s="221"/>
-      <c r="AC3" s="221"/>
-      <c r="AD3" s="221"/>
-      <c r="AE3" s="221"/>
-      <c r="AF3" s="221"/>
-      <c r="AG3" s="221"/>
-      <c r="AH3" s="221"/>
-      <c r="AI3" s="221"/>
-      <c r="AJ3" s="221"/>
-      <c r="AK3" s="221"/>
-      <c r="AL3" s="221"/>
-      <c r="AM3" s="221"/>
-      <c r="AN3" s="221"/>
-      <c r="AO3" s="221"/>
-      <c r="AP3" s="221"/>
-      <c r="AQ3" s="221"/>
-      <c r="AR3" s="221"/>
-      <c r="AS3" s="221"/>
-      <c r="AT3" s="221"/>
-      <c r="AU3" s="221"/>
-      <c r="AV3" s="221"/>
-      <c r="AW3" s="221"/>
-      <c r="AX3" s="221"/>
-      <c r="AY3" s="221"/>
-      <c r="AZ3" s="221"/>
-      <c r="BA3" s="221"/>
-      <c r="BB3" s="221"/>
-      <c r="BC3" s="221"/>
-      <c r="BD3" s="221"/>
-      <c r="BE3" s="221"/>
-      <c r="BF3" s="221"/>
-      <c r="BG3" s="221"/>
-      <c r="BH3" s="221"/>
-      <c r="BI3" s="221"/>
-      <c r="BJ3" s="221"/>
-      <c r="BK3" s="221"/>
-      <c r="BL3" s="221"/>
-      <c r="BM3" s="221"/>
-      <c r="BN3" s="221"/>
-      <c r="BO3" s="221"/>
-      <c r="BP3" s="221"/>
-      <c r="BQ3" s="221"/>
-      <c r="BR3" s="221"/>
-      <c r="BS3" s="221"/>
-      <c r="BT3" s="221"/>
-      <c r="BU3" s="221"/>
-      <c r="BV3" s="221"/>
-      <c r="BW3" s="221"/>
-      <c r="BX3" s="221"/>
-      <c r="BY3" s="221"/>
-      <c r="BZ3" s="221"/>
-      <c r="CA3" s="221"/>
+      <c r="L3" s="270"/>
+      <c r="M3" s="270"/>
+      <c r="N3" s="270"/>
+      <c r="O3" s="270"/>
+      <c r="P3" s="270"/>
+      <c r="Q3" s="270"/>
+      <c r="R3" s="270"/>
+      <c r="S3" s="270"/>
+      <c r="T3" s="270"/>
+      <c r="U3" s="270"/>
+      <c r="V3" s="270"/>
+      <c r="W3" s="270"/>
+      <c r="X3" s="270"/>
+      <c r="Y3" s="270"/>
+      <c r="Z3" s="270"/>
+      <c r="AA3" s="270"/>
+      <c r="AB3" s="270"/>
+      <c r="AC3" s="270"/>
+      <c r="AD3" s="270"/>
+      <c r="AE3" s="270"/>
+      <c r="AF3" s="270"/>
+      <c r="AG3" s="270"/>
+      <c r="AH3" s="270"/>
+      <c r="AI3" s="270"/>
+      <c r="AJ3" s="270"/>
+      <c r="AK3" s="270"/>
+      <c r="AL3" s="270"/>
+      <c r="AM3" s="270"/>
+      <c r="AN3" s="270"/>
+      <c r="AO3" s="270"/>
+      <c r="AP3" s="270"/>
+      <c r="AQ3" s="270"/>
+      <c r="AR3" s="270"/>
+      <c r="AS3" s="270"/>
+      <c r="AT3" s="270"/>
+      <c r="AU3" s="270"/>
+      <c r="AV3" s="270"/>
+      <c r="AW3" s="270"/>
+      <c r="AX3" s="270"/>
+      <c r="AY3" s="270"/>
+      <c r="AZ3" s="270"/>
+      <c r="BA3" s="270"/>
+      <c r="BB3" s="270"/>
+      <c r="BC3" s="270"/>
+      <c r="BD3" s="270"/>
+      <c r="BE3" s="270"/>
+      <c r="BF3" s="270"/>
+      <c r="BG3" s="270"/>
+      <c r="BH3" s="270"/>
+      <c r="BI3" s="270"/>
+      <c r="BJ3" s="270"/>
+      <c r="BK3" s="270"/>
+      <c r="BL3" s="270"/>
+      <c r="BM3" s="270"/>
+      <c r="BN3" s="270"/>
+      <c r="BO3" s="270"/>
+      <c r="BP3" s="270"/>
+      <c r="BQ3" s="270"/>
+      <c r="BR3" s="270"/>
+      <c r="BS3" s="270"/>
+      <c r="BT3" s="270"/>
+      <c r="BU3" s="270"/>
+      <c r="BV3" s="270"/>
+      <c r="BW3" s="270"/>
+      <c r="BX3" s="270"/>
+      <c r="BY3" s="270"/>
+      <c r="BZ3" s="270"/>
+      <c r="CA3" s="270"/>
     </row>
     <row r="4" spans="1:79" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
@@ -5955,14 +6024,14 @@
       <c r="BB4" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="BC4" s="215" t="s">
-        <v>613</v>
-      </c>
-      <c r="BD4" s="215" t="s">
-        <v>614</v>
-      </c>
-      <c r="BE4" s="215" t="s">
-        <v>615</v>
+      <c r="BC4" s="213" t="s">
+        <v>606</v>
+      </c>
+      <c r="BD4" s="213" t="s">
+        <v>607</v>
+      </c>
+      <c r="BE4" s="213" t="s">
+        <v>608</v>
       </c>
       <c r="BF4" s="43" t="s">
         <v>89</v>
@@ -6399,8 +6468,8 @@
       <c r="AH6" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AI6" s="212" t="s">
-        <v>631</v>
+      <c r="AI6" s="210" t="s">
+        <v>624</v>
       </c>
       <c r="AJ6" s="2">
         <v>0</v>
@@ -6448,20 +6517,20 @@
       <c r="AY6" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="AZ6" s="212" t="s">
-        <v>616</v>
+      <c r="AZ6" s="210" t="s">
+        <v>609</v>
       </c>
       <c r="BA6" s="2"/>
       <c r="BB6" s="2">
         <v>5</v>
       </c>
-      <c r="BC6" s="212" t="s">
-        <v>617</v>
-      </c>
-      <c r="BD6" s="212">
+      <c r="BC6" s="210" t="s">
+        <v>610</v>
+      </c>
+      <c r="BD6" s="210">
         <v>12.5</v>
       </c>
-      <c r="BE6" s="212">
+      <c r="BE6" s="210">
         <v>150</v>
       </c>
       <c r="BF6" s="2">
@@ -6599,8 +6668,8 @@
       <c r="AH7" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AI7" s="212" t="s">
-        <v>631</v>
+      <c r="AI7" s="210" t="s">
+        <v>624</v>
       </c>
       <c r="AJ7" s="2">
         <v>0</v>
@@ -6648,20 +6717,20 @@
       <c r="AY7" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="AZ7" s="212" t="s">
-        <v>616</v>
+      <c r="AZ7" s="210" t="s">
+        <v>609</v>
       </c>
       <c r="BA7" s="2"/>
       <c r="BB7" s="2">
         <v>5</v>
       </c>
-      <c r="BC7" s="212" t="s">
-        <v>617</v>
-      </c>
-      <c r="BD7" s="212">
+      <c r="BC7" s="210" t="s">
+        <v>610</v>
+      </c>
+      <c r="BD7" s="210">
         <v>12.5</v>
       </c>
-      <c r="BE7" s="212">
+      <c r="BE7" s="210">
         <v>150</v>
       </c>
       <c r="BF7" s="2">
@@ -6800,8 +6869,8 @@
       <c r="AH8" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AI8" s="212" t="s">
-        <v>631</v>
+      <c r="AI8" s="210" t="s">
+        <v>624</v>
       </c>
       <c r="AJ8" s="2">
         <v>0</v>
@@ -6849,20 +6918,20 @@
       <c r="AY8" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="AZ8" s="212" t="s">
-        <v>616</v>
+      <c r="AZ8" s="210" t="s">
+        <v>609</v>
       </c>
       <c r="BA8" s="2"/>
       <c r="BB8" s="2">
         <v>5</v>
       </c>
-      <c r="BC8" s="212" t="s">
-        <v>617</v>
-      </c>
-      <c r="BD8" s="212">
+      <c r="BC8" s="210" t="s">
+        <v>610</v>
+      </c>
+      <c r="BD8" s="210">
         <v>12.5</v>
       </c>
-      <c r="BE8" s="212">
+      <c r="BE8" s="210">
         <v>150</v>
       </c>
       <c r="BF8" s="2">
@@ -6920,10 +6989,10 @@
       <c r="CA8" s="2"/>
     </row>
     <row r="9" spans="1:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="228" t="s">
+      <c r="A9" s="277" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="229"/>
+      <c r="B9" s="278"/>
       <c r="F9" s="27">
         <v>2500</v>
       </c>
@@ -6999,8 +7068,8 @@
       <c r="AH9" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AI9" s="212" t="s">
-        <v>631</v>
+      <c r="AI9" s="210" t="s">
+        <v>624</v>
       </c>
       <c r="AJ9" s="2">
         <v>0</v>
@@ -7048,20 +7117,20 @@
       <c r="AY9" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="AZ9" s="212" t="s">
-        <v>616</v>
+      <c r="AZ9" s="210" t="s">
+        <v>609</v>
       </c>
       <c r="BA9" s="2"/>
       <c r="BB9" s="2">
         <v>5</v>
       </c>
-      <c r="BC9" s="212" t="s">
-        <v>617</v>
-      </c>
-      <c r="BD9" s="212">
+      <c r="BC9" s="210" t="s">
+        <v>610</v>
+      </c>
+      <c r="BD9" s="210">
         <v>12.5</v>
       </c>
-      <c r="BE9" s="212">
+      <c r="BE9" s="210">
         <v>150</v>
       </c>
       <c r="BF9" s="2">
@@ -7200,8 +7269,8 @@
       <c r="AH10" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AI10" s="212" t="s">
-        <v>631</v>
+      <c r="AI10" s="210" t="s">
+        <v>624</v>
       </c>
       <c r="AJ10" s="2">
         <v>0</v>
@@ -7249,20 +7318,20 @@
       <c r="AY10" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="AZ10" s="212" t="s">
-        <v>616</v>
+      <c r="AZ10" s="210" t="s">
+        <v>609</v>
       </c>
       <c r="BA10" s="2"/>
       <c r="BB10" s="2">
         <v>5</v>
       </c>
-      <c r="BC10" s="212" t="s">
-        <v>617</v>
-      </c>
-      <c r="BD10" s="212">
+      <c r="BC10" s="210" t="s">
+        <v>610</v>
+      </c>
+      <c r="BD10" s="210">
         <v>12.5</v>
       </c>
-      <c r="BE10" s="212">
+      <c r="BE10" s="210">
         <v>150</v>
       </c>
       <c r="BF10" s="2">
@@ -7401,8 +7470,8 @@
       <c r="AH11" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AI11" s="212" t="s">
-        <v>631</v>
+      <c r="AI11" s="210" t="s">
+        <v>624</v>
       </c>
       <c r="AJ11" s="2">
         <v>0</v>
@@ -7450,20 +7519,20 @@
       <c r="AY11" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="AZ11" s="212" t="s">
-        <v>616</v>
+      <c r="AZ11" s="210" t="s">
+        <v>609</v>
       </c>
       <c r="BA11" s="2"/>
       <c r="BB11" s="2">
         <v>5</v>
       </c>
-      <c r="BC11" s="212" t="s">
-        <v>617</v>
-      </c>
-      <c r="BD11" s="212">
+      <c r="BC11" s="210" t="s">
+        <v>610</v>
+      </c>
+      <c r="BD11" s="210">
         <v>12.5</v>
       </c>
-      <c r="BE11" s="212">
+      <c r="BE11" s="210">
         <v>150</v>
       </c>
       <c r="BF11" s="2">
@@ -7602,8 +7671,8 @@
       <c r="AH12" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AI12" s="212" t="s">
-        <v>631</v>
+      <c r="AI12" s="210" t="s">
+        <v>624</v>
       </c>
       <c r="AJ12" s="2">
         <v>0</v>
@@ -7651,20 +7720,20 @@
       <c r="AY12" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="AZ12" s="212" t="s">
-        <v>616</v>
+      <c r="AZ12" s="210" t="s">
+        <v>609</v>
       </c>
       <c r="BA12" s="2"/>
       <c r="BB12" s="2">
         <v>5</v>
       </c>
-      <c r="BC12" s="212" t="s">
-        <v>617</v>
-      </c>
-      <c r="BD12" s="212">
+      <c r="BC12" s="210" t="s">
+        <v>610</v>
+      </c>
+      <c r="BD12" s="210">
         <v>12.5</v>
       </c>
-      <c r="BE12" s="212">
+      <c r="BE12" s="210">
         <v>150</v>
       </c>
       <c r="BF12" s="2">
@@ -7797,8 +7866,8 @@
       <c r="AH13" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AI13" s="212" t="s">
-        <v>631</v>
+      <c r="AI13" s="210" t="s">
+        <v>624</v>
       </c>
       <c r="AJ13" s="2">
         <v>0</v>
@@ -7974,8 +8043,8 @@
       <c r="AH14" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AI14" s="212" t="s">
-        <v>631</v>
+      <c r="AI14" s="210" t="s">
+        <v>624</v>
       </c>
       <c r="AJ14" s="2">
         <v>0</v>
@@ -8145,8 +8214,8 @@
       <c r="AH15" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="AI15" s="212" t="s">
-        <v>631</v>
+      <c r="AI15" s="210" t="s">
+        <v>624</v>
       </c>
       <c r="AJ15" s="2">
         <v>0</v>
@@ -9612,8 +9681,8 @@
       <c r="N24" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O24" s="212" t="s">
-        <v>630</v>
+      <c r="O24" s="210" t="s">
+        <v>623</v>
       </c>
       <c r="P24" s="2"/>
       <c r="Q24" s="2">
@@ -9779,8 +9848,8 @@
       <c r="N25" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O25" s="212" t="s">
-        <v>630</v>
+      <c r="O25" s="210" t="s">
+        <v>623</v>
       </c>
       <c r="P25" s="2"/>
       <c r="Q25" s="2">
@@ -9946,8 +10015,8 @@
       <c r="N26" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O26" s="212" t="s">
-        <v>630</v>
+      <c r="O26" s="210" t="s">
+        <v>623</v>
       </c>
       <c r="P26" s="2"/>
       <c r="Q26" s="2">
@@ -10113,8 +10182,8 @@
       <c r="N27" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O27" s="212" t="s">
-        <v>630</v>
+      <c r="O27" s="210" t="s">
+        <v>623</v>
       </c>
       <c r="P27" s="2"/>
       <c r="Q27" s="2">
@@ -10280,8 +10349,8 @@
       <c r="N28" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O28" s="212" t="s">
-        <v>630</v>
+      <c r="O28" s="210" t="s">
+        <v>623</v>
       </c>
       <c r="P28" s="2"/>
       <c r="Q28" s="2">
@@ -10447,8 +10516,8 @@
       <c r="N29" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O29" s="212" t="s">
-        <v>630</v>
+      <c r="O29" s="210" t="s">
+        <v>623</v>
       </c>
       <c r="P29" s="2"/>
       <c r="Q29" s="2">
@@ -10614,8 +10683,8 @@
       <c r="N30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O30" s="212" t="s">
-        <v>630</v>
+      <c r="O30" s="210" t="s">
+        <v>623</v>
       </c>
       <c r="P30" s="2"/>
       <c r="Q30" s="2">
@@ -10781,8 +10850,8 @@
       <c r="N31" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O31" s="212" t="s">
-        <v>630</v>
+      <c r="O31" s="210" t="s">
+        <v>623</v>
       </c>
       <c r="P31" s="2"/>
       <c r="Q31" s="2">
@@ -10948,8 +11017,8 @@
       <c r="N32" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O32" s="212" t="s">
-        <v>630</v>
+      <c r="O32" s="210" t="s">
+        <v>623</v>
       </c>
       <c r="P32" s="2"/>
       <c r="Q32" s="2">
@@ -11115,8 +11184,8 @@
       <c r="N33" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O33" s="212" t="s">
-        <v>630</v>
+      <c r="O33" s="210" t="s">
+        <v>623</v>
       </c>
       <c r="P33" s="2"/>
       <c r="Q33" s="2">
@@ -11282,8 +11351,8 @@
       <c r="N34" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O34" s="212" t="s">
-        <v>630</v>
+      <c r="O34" s="210" t="s">
+        <v>623</v>
       </c>
       <c r="P34" s="2"/>
       <c r="Q34" s="2">
@@ -11449,8 +11518,8 @@
       <c r="N35" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O35" s="212" t="s">
-        <v>630</v>
+      <c r="O35" s="210" t="s">
+        <v>623</v>
       </c>
       <c r="P35" s="2"/>
       <c r="Q35" s="2">
@@ -11616,8 +11685,8 @@
       <c r="N36" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O36" s="212" t="s">
-        <v>630</v>
+      <c r="O36" s="210" t="s">
+        <v>623</v>
       </c>
       <c r="P36" s="2"/>
       <c r="Q36" s="2">
@@ -11774,8 +11843,8 @@
       <c r="N37" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O37" s="212" t="s">
-        <v>630</v>
+      <c r="O37" s="210" t="s">
+        <v>623</v>
       </c>
       <c r="P37" s="2"/>
       <c r="Q37" s="2">
@@ -12056,15 +12125,15 @@
     </row>
     <row r="41" spans="6:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="42" spans="6:79" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F42" s="225" t="s">
+      <c r="F42" s="274" t="s">
         <v>71</v>
       </c>
-      <c r="G42" s="226"/>
-      <c r="H42" s="227"/>
-      <c r="K42" s="230" t="s">
-        <v>508</v>
-      </c>
-      <c r="L42" s="231"/>
+      <c r="G42" s="275"/>
+      <c r="H42" s="276"/>
+      <c r="K42" s="279" t="s">
+        <v>503</v>
+      </c>
+      <c r="L42" s="280"/>
     </row>
     <row r="43" spans="6:79" ht="31.5" x14ac:dyDescent="0.25">
       <c r="F43" s="36" t="s">
@@ -12077,7 +12146,7 @@
         <v>22</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="L43" s="2">
         <v>1</v>
@@ -12090,7 +12159,7 @@
       <c r="G44" s="28"/>
       <c r="H44" s="29"/>
       <c r="K44" s="2" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="L44" s="2">
         <v>0</v>
@@ -12103,7 +12172,7 @@
       <c r="G45" s="28"/>
       <c r="H45" s="29"/>
       <c r="K45" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="L45" s="2">
         <v>1</v>
@@ -12116,7 +12185,7 @@
       <c r="G46" s="28"/>
       <c r="H46" s="29"/>
       <c r="K46" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="L46" s="2">
         <v>0</v>
@@ -12129,7 +12198,7 @@
       <c r="G47" s="28"/>
       <c r="H47" s="29"/>
       <c r="K47" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="L47" s="2">
         <v>0</v>
@@ -12157,14 +12226,14 @@
       <c r="H50" s="29"/>
     </row>
     <row r="56" spans="3:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C56" s="219" t="s">
-        <v>618</v>
-      </c>
-      <c r="D56" s="219"/>
+      <c r="C56" s="268" t="s">
+        <v>611</v>
+      </c>
+      <c r="D56" s="268"/>
     </row>
     <row r="57" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C57" s="2" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="D57" s="2">
         <v>0</v>
@@ -12172,7 +12241,7 @@
     </row>
     <row r="58" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C58" s="2" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D58" s="2">
         <v>0</v>
@@ -12180,26 +12249,26 @@
     </row>
     <row r="59" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C59" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
     </row>
     <row r="60" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C60" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
     </row>
     <row r="61" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C61" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -12294,6 +12363,45 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019AE8B5-0D80-438F-9CBA-ADEC7CDF9F04}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B2" t="str">
+        <f>"&lt;zsetformulatocell toSheet=[BD]  toCell=[A2] formula=[SUM(B4:B5)]"</f>
+        <v>&lt;zsetformulatocell toSheet=[BD]  toCell=[A2] formula=[SUM(B4:B5)]</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C18C41F-A7A1-44A1-BCA8-2DEB7768025B}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12314,7 +12422,7 @@
         <v>171</v>
       </c>
       <c r="B2" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -12330,7 +12438,7 @@
         <v>171</v>
       </c>
       <c r="B4" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -12346,7 +12454,7 @@
         <v>170</v>
       </c>
       <c r="B6" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
     </row>
   </sheetData>
@@ -12354,7 +12462,240 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADAE1986-1CF6-4370-AEB3-1DC97E00D4E1}">
+  <dimension ref="A2:S6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.7109375" customWidth="1"/>
+    <col min="5" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" customWidth="1"/>
+    <col min="8" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="3.7109375" customWidth="1"/>
+    <col min="13" max="18" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1">
+        <f>A2+1</f>
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <f t="shared" ref="C2:R2" si="0">B2+1</f>
+        <v>2</v>
+      </c>
+      <c r="D2" s="1">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E2" s="1">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F2" s="1">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="G2" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="H2" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="I2" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="J2" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="K2" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="L2" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="M2" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="N2" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="O2" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="P2" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="Q2" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="R2" s="75">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+      <c r="C3" s="61"/>
+      <c r="D3" s="288" t="s">
+        <v>331</v>
+      </c>
+      <c r="E3" s="288"/>
+      <c r="F3" s="288"/>
+      <c r="G3" s="288" t="s">
+        <v>332</v>
+      </c>
+      <c r="H3" s="288"/>
+      <c r="I3" s="288"/>
+      <c r="J3" s="70" t="s">
+        <v>335</v>
+      </c>
+      <c r="K3" s="70" t="s">
+        <v>333</v>
+      </c>
+      <c r="L3" s="288" t="s">
+        <v>334</v>
+      </c>
+      <c r="M3" s="288"/>
+      <c r="N3" s="288"/>
+      <c r="O3" s="291" t="s">
+        <v>342</v>
+      </c>
+      <c r="P3" s="291"/>
+      <c r="Q3" s="291"/>
+      <c r="R3" s="76" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C4" s="61"/>
+      <c r="D4" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="E4" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="H4" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="I4" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="J4" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="K4" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="L4" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="M4" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="N4" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="O4" s="71" t="s">
+        <v>164</v>
+      </c>
+      <c r="P4" s="72" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q4" s="73" t="s">
+        <v>163</v>
+      </c>
+      <c r="R4" s="76"/>
+    </row>
+    <row r="5" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="C5" s="69" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="47"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="73"/>
+      <c r="R5" s="76"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="C6" s="58" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>338</v>
+      </c>
+      <c r="E6" s="48"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="50" t="s">
+        <v>339</v>
+      </c>
+      <c r="H6" s="48"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="48" t="s">
+        <v>336</v>
+      </c>
+      <c r="K6" s="48" t="s">
+        <v>337</v>
+      </c>
+      <c r="L6" s="50" t="s">
+        <v>340</v>
+      </c>
+      <c r="M6" s="48"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="50" t="s">
+        <v>344</v>
+      </c>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="76">
+        <v>1</v>
+      </c>
+      <c r="S6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="O3:Q3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61A3016B-46A2-49B9-9A52-E38B657C2400}">
   <dimension ref="A4:AD7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12428,7 +12769,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="Q4" s="76">
+      <c r="Q4" s="75">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -12484,91 +12825,91 @@
     <row r="5" spans="1:30" ht="150" x14ac:dyDescent="0.25">
       <c r="B5" s="59"/>
       <c r="C5" s="59"/>
-      <c r="D5" s="118" t="s">
+      <c r="D5" s="116" t="s">
         <v>331</v>
       </c>
-      <c r="E5" s="118" t="s">
+      <c r="E5" s="116" t="s">
         <v>332</v>
       </c>
-      <c r="F5" s="118" t="s">
+      <c r="F5" s="116" t="s">
         <v>333</v>
       </c>
-      <c r="G5" s="118" t="s">
+      <c r="G5" s="116" t="s">
         <v>342</v>
       </c>
-      <c r="H5" s="118" t="s">
+      <c r="H5" s="116" t="s">
         <v>334</v>
       </c>
-      <c r="I5" s="118" t="s">
+      <c r="I5" s="116" t="s">
         <v>347</v>
       </c>
-      <c r="J5" s="118" t="s">
+      <c r="J5" s="116" t="s">
         <v>348</v>
       </c>
-      <c r="K5" s="118" t="s">
+      <c r="K5" s="116" t="s">
         <v>349</v>
       </c>
-      <c r="L5" s="118" t="s">
+      <c r="L5" s="116" t="s">
         <v>350</v>
       </c>
-      <c r="M5" s="118" t="s">
+      <c r="M5" s="116" t="s">
         <v>351</v>
       </c>
-      <c r="N5" s="118" t="s">
+      <c r="N5" s="116" t="s">
         <v>352</v>
       </c>
-      <c r="O5" s="118" t="s">
+      <c r="O5" s="116" t="s">
         <v>353</v>
       </c>
-      <c r="P5" s="118" t="s">
+      <c r="P5" s="116" t="s">
         <v>354</v>
       </c>
-      <c r="Q5" s="77" t="s">
+      <c r="Q5" s="76" t="s">
         <v>355</v>
       </c>
-      <c r="R5" s="118" t="s">
+      <c r="R5" s="116" t="s">
         <v>356</v>
       </c>
-      <c r="S5" s="118" t="s">
+      <c r="S5" s="116" t="s">
         <v>357</v>
       </c>
-      <c r="T5" s="118" t="s">
+      <c r="T5" s="116" t="s">
         <v>358</v>
       </c>
-      <c r="U5" s="118" t="s">
+      <c r="U5" s="116" t="s">
         <v>359</v>
       </c>
-      <c r="V5" s="118" t="s">
+      <c r="V5" s="116" t="s">
         <v>342</v>
       </c>
-      <c r="W5" s="118" t="s">
+      <c r="W5" s="116" t="s">
         <v>360</v>
       </c>
-      <c r="X5" s="119" t="s">
-        <v>378</v>
-      </c>
-      <c r="Y5" s="120" t="s">
-        <v>490</v>
-      </c>
-      <c r="Z5" s="120" t="s">
-        <v>491</v>
-      </c>
-      <c r="AA5" s="121" t="s">
-        <v>492</v>
-      </c>
-      <c r="AB5" s="121" t="s">
-        <v>493</v>
-      </c>
-      <c r="AC5" s="217" t="s">
-        <v>632</v>
+      <c r="X5" s="117" t="s">
+        <v>373</v>
+      </c>
+      <c r="Y5" s="118" t="s">
+        <v>485</v>
+      </c>
+      <c r="Z5" s="118" t="s">
+        <v>486</v>
+      </c>
+      <c r="AA5" s="119" t="s">
+        <v>487</v>
+      </c>
+      <c r="AB5" s="119" t="s">
+        <v>488</v>
+      </c>
+      <c r="AC5" s="215" t="s">
+        <v>625</v>
       </c>
       <c r="AD5" s="59"/>
     </row>
     <row r="6" spans="1:30" ht="60" x14ac:dyDescent="0.25">
-      <c r="B6" s="122" t="s">
+      <c r="B6" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="122"/>
+      <c r="C6" s="120"/>
       <c r="D6" s="59"/>
       <c r="E6" s="59"/>
       <c r="F6" s="59"/>
@@ -12582,24 +12923,24 @@
       <c r="N6" s="59"/>
       <c r="O6" s="59"/>
       <c r="P6" s="59"/>
-      <c r="Q6" s="123"/>
+      <c r="Q6" s="121"/>
       <c r="R6" s="59"/>
       <c r="S6" s="59"/>
       <c r="T6" s="59"/>
       <c r="U6" s="59"/>
       <c r="V6" s="59"/>
       <c r="W6" s="59"/>
-      <c r="X6" s="124"/>
-      <c r="Y6" s="125"/>
-      <c r="Z6" s="125"/>
-      <c r="AA6" s="121"/>
-      <c r="AB6" s="121"/>
-      <c r="AC6" s="121"/>
+      <c r="X6" s="122"/>
+      <c r="Y6" s="123"/>
+      <c r="Z6" s="123"/>
+      <c r="AA6" s="119"/>
+      <c r="AB6" s="119"/>
+      <c r="AC6" s="119"/>
       <c r="AD6" s="59"/>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="B7" s="59" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C7" s="59" t="str">
         <f>IF(COUNTIF($B$7:B7,B7)=1,"&lt;zzzimport&gt;",1)</f>
@@ -12656,7 +12997,7 @@
         <f>SUMIFS($H$7:H7,$D$7:D7,D7,$G$7:G7,G7)</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="126">
+      <c r="Q7" s="124">
         <f t="shared" ref="Q7" si="6">IF(K7=1,1,0)</f>
         <v>1</v>
       </c>
@@ -12688,17 +13029,17 @@
         <f>SUMIFS($H$7:$H$700000,$D$7:$D$700000,D7)</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="127"/>
-      <c r="Z7" s="127"/>
-      <c r="AA7" s="121">
+      <c r="Y7" s="125"/>
+      <c r="Z7" s="125"/>
+      <c r="AA7" s="119">
         <f>INDEX($Y$7:Y7,MATCH(D7,$D$7:D7,0))</f>
         <v>0</v>
       </c>
-      <c r="AB7" s="121">
+      <c r="AB7" s="119">
         <f>INDEX($Z$7:Z7,MATCH(D7,$D$7:D7,0))</f>
         <v>0</v>
       </c>
-      <c r="AC7" s="218">
+      <c r="AC7" s="216">
         <f>IF(W7&lt;&gt;" ",1,0)</f>
         <v>1</v>
       </c>
@@ -12711,7 +13052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B2FE768-E1A9-46E0-BBE4-ECE839204A01}">
   <dimension ref="B1:AS7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12720,51 +13061,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:45" x14ac:dyDescent="0.25">
-      <c r="C1" s="242" t="s">
-        <v>436</v>
-      </c>
-      <c r="D1" s="242"/>
-      <c r="L1" s="243" t="s">
-        <v>474</v>
-      </c>
-      <c r="M1" s="243"/>
-      <c r="N1" s="243"/>
-      <c r="O1" s="243"/>
-      <c r="P1" s="243"/>
-      <c r="Q1" s="243"/>
-      <c r="R1" s="243"/>
-      <c r="S1" s="243"/>
+      <c r="C1" s="241" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1" s="241"/>
+      <c r="L1" s="292" t="s">
+        <v>469</v>
+      </c>
+      <c r="M1" s="292"/>
+      <c r="N1" s="292"/>
+      <c r="O1" s="292"/>
+      <c r="P1" s="292"/>
+      <c r="Q1" s="292"/>
+      <c r="R1" s="292"/>
+      <c r="S1" s="292"/>
     </row>
     <row r="2" spans="2:45" x14ac:dyDescent="0.25">
-      <c r="C2" s="99" t="s">
-        <v>424</v>
-      </c>
-      <c r="D2" s="99">
+      <c r="C2" s="97" t="s">
+        <v>419</v>
+      </c>
+      <c r="D2" s="97">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:45" x14ac:dyDescent="0.25">
-      <c r="C3" s="99" t="s">
-        <v>425</v>
-      </c>
-      <c r="D3" s="99">
+      <c r="C3" s="97" t="s">
+        <v>420</v>
+      </c>
+      <c r="D3" s="97">
         <f>D2</f>
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="O3" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="P3" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="Q3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="R3" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="4" spans="2:45" x14ac:dyDescent="0.25">
@@ -12772,23 +13113,23 @@
         <v>209</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="N4" s="128">
-        <v>0</v>
-      </c>
-      <c r="O4" s="128">
-        <v>0</v>
-      </c>
-      <c r="P4" s="129">
+        <v>475</v>
+      </c>
+      <c r="N4" s="126">
+        <v>0</v>
+      </c>
+      <c r="O4" s="126">
+        <v>0</v>
+      </c>
+      <c r="P4" s="127">
         <f>D2</f>
         <v>1</v>
       </c>
-      <c r="Q4" s="129">
+      <c r="Q4" s="127">
         <f>D3</f>
         <v>1</v>
       </c>
-      <c r="R4" s="130">
+      <c r="R4" s="128">
         <v>0</v>
       </c>
       <c r="S4" t="s">
@@ -12797,13 +13138,13 @@
     </row>
     <row r="6" spans="2:45" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>165</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>342</v>
@@ -12812,26 +13153,26 @@
         <v>231</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="K6" s="104" t="s">
-        <v>495</v>
-      </c>
-      <c r="N6" s="131"/>
-      <c r="O6" s="128">
+      <c r="K6" s="102" t="s">
+        <v>490</v>
+      </c>
+      <c r="N6" s="129"/>
+      <c r="O6" s="126">
         <f>-24*D3</f>
         <v>-24</v>
       </c>
-      <c r="P6" s="129"/>
-      <c r="Q6" s="129"/>
-      <c r="R6" s="130"/>
+      <c r="P6" s="127"/>
+      <c r="Q6" s="127"/>
+      <c r="R6" s="128"/>
     </row>
     <row r="7" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C7" s="1">
         <f>'&lt;zallcab&gt;CALC'!S7</f>
@@ -12861,90 +13202,90 @@
         <f>'&lt;zallcab&gt;CALC'!W7</f>
         <v>0</v>
       </c>
-      <c r="K7" s="104">
+      <c r="K7" s="102">
         <v>1</v>
       </c>
       <c r="L7" t="s">
         <v>209</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="N7" s="131">
-        <v>0</v>
-      </c>
-      <c r="O7" s="128">
+        <v>476</v>
+      </c>
+      <c r="N7" s="129">
+        <v>0</v>
+      </c>
+      <c r="O7" s="126">
         <f>INDEX($O$6:O6,SUM($K$7:K7))-(8*Q7)</f>
         <v>-32</v>
       </c>
-      <c r="P7" s="129">
+      <c r="P7" s="127">
         <f>$D$2</f>
         <v>1</v>
       </c>
-      <c r="Q7" s="129">
+      <c r="Q7" s="127">
         <f>$D$3</f>
         <v>1</v>
       </c>
-      <c r="R7" s="130">
-        <v>0</v>
-      </c>
-      <c r="S7" s="132" t="s">
-        <v>482</v>
-      </c>
-      <c r="T7" s="117" t="str">
+      <c r="R7" s="128">
+        <v>0</v>
+      </c>
+      <c r="S7" s="130" t="s">
+        <v>477</v>
+      </c>
+      <c r="T7" s="115" t="str">
         <f>IF(C7=0,"",C7)</f>
         <v/>
       </c>
-      <c r="U7" s="133" t="s">
-        <v>483</v>
-      </c>
-      <c r="V7" s="133" t="str">
+      <c r="U7" s="131" t="s">
+        <v>478</v>
+      </c>
+      <c r="V7" s="131" t="str">
         <f>IF(C7=0,"",D7)</f>
         <v/>
       </c>
-      <c r="W7" s="134" t="s">
-        <v>484</v>
-      </c>
-      <c r="X7" s="135" t="str">
+      <c r="W7" s="132" t="s">
+        <v>479</v>
+      </c>
+      <c r="X7" s="133" t="str">
         <f>IF(C7=0,"",E7)</f>
         <v/>
       </c>
-      <c r="Y7" s="134" t="s">
-        <v>485</v>
-      </c>
-      <c r="Z7" s="133" t="str">
+      <c r="Y7" s="132" t="s">
+        <v>480</v>
+      </c>
+      <c r="Z7" s="131" t="str">
         <f>IF(C7=0,"",F7)</f>
         <v/>
       </c>
-      <c r="AA7" s="136" t="s">
-        <v>486</v>
-      </c>
-      <c r="AB7" s="137" t="str">
+      <c r="AA7" s="134" t="s">
+        <v>481</v>
+      </c>
+      <c r="AB7" s="135" t="str">
         <f>IF(C7=0,"",G7)</f>
         <v/>
       </c>
-      <c r="AC7" s="138" t="s">
-        <v>487</v>
-      </c>
-      <c r="AD7" s="137" t="str">
+      <c r="AC7" s="136" t="s">
+        <v>482</v>
+      </c>
+      <c r="AD7" s="135" t="str">
         <f>IF(C7=0,"",H7)</f>
         <v/>
       </c>
-      <c r="AE7" s="138" t="s">
-        <v>488</v>
-      </c>
-      <c r="AF7" s="139" t="str">
+      <c r="AE7" s="136" t="s">
+        <v>483</v>
+      </c>
+      <c r="AF7" s="137" t="str">
         <f>IF(C7=0,"",I7)</f>
         <v/>
       </c>
       <c r="AG7" t="s">
         <v>191</v>
       </c>
-      <c r="AI7" s="140"/>
+      <c r="AI7" s="138"/>
       <c r="AO7" t="s">
         <v>189</v>
       </c>
-      <c r="AS7" s="140"/>
+      <c r="AS7" s="138"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -12956,7 +13297,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC2F1E96-4609-417D-ADC2-516E48694036}">
   <dimension ref="B1:AE7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12969,34 +13310,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="C1" s="242" t="s">
-        <v>436</v>
-      </c>
-      <c r="D1" s="242"/>
+      <c r="C1" s="241" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1" s="241"/>
     </row>
     <row r="2" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="C2" s="99" t="s">
-        <v>424</v>
-      </c>
-      <c r="D2" s="99">
+      <c r="C2" s="97" t="s">
+        <v>419</v>
+      </c>
+      <c r="D2" s="97">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="C3" s="99" t="s">
-        <v>425</v>
-      </c>
-      <c r="D3" s="99">
+      <c r="C3" s="97" t="s">
+        <v>420</v>
+      </c>
+      <c r="D3" s="97">
         <f>D2</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:31" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>334</v>
@@ -13004,7 +13345,7 @@
     </row>
     <row r="7" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="C7" s="1">
         <f>'&lt;zallcab&gt;CALC'!D7</f>
@@ -13018,62 +13359,62 @@
         <f>'&lt;zallcab&gt;CALC'!W7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="133">
+      <c r="F7" s="131">
         <f>IF(MATCH(C7,$C$7:C7,0)=G7,C7,0)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="133">
+      <c r="G7" s="131">
         <f>COUNT($I$7:I7)</f>
         <v>1</v>
       </c>
-      <c r="H7" s="133" t="str">
+      <c r="H7" s="131" t="str">
         <f>ADDRESS(ROW(P7),COLUMN(P7))</f>
         <v>$P$7</v>
       </c>
-      <c r="I7" s="133">
+      <c r="I7" s="131">
         <v>1</v>
       </c>
-      <c r="J7" s="134">
+      <c r="J7" s="132">
         <f>IF(SUMIF(C7:$C$777777,C7,I7:$I$777777)=1,C7,0)</f>
         <v>0</v>
       </c>
-      <c r="K7" s="135">
+      <c r="K7" s="133">
         <f>MATCH(C7,$F$7:F7,0)</f>
         <v>1</v>
       </c>
-      <c r="L7" s="135">
+      <c r="L7" s="133">
         <f>MATCH(C7,$J$7:$J$777777,0)</f>
         <v>1</v>
       </c>
-      <c r="M7" s="134" t="str" cm="1">
+      <c r="M7" s="132" t="str" cm="1">
         <f t="array" ref="M7">INDEX($H$7:H7,K7)</f>
         <v>$P$7</v>
       </c>
-      <c r="N7" s="134" t="str" cm="1">
+      <c r="N7" s="132" t="str" cm="1">
         <f t="array" ref="N7">INDEX($H$7:$H$777777,L7)</f>
         <v>$P$7</v>
       </c>
-      <c r="O7" s="136" t="str">
+      <c r="O7" s="134" t="str">
         <f>"L="&amp;E7&amp;"м"</f>
         <v>L=0м</v>
       </c>
-      <c r="P7" s="137" t="e">
+      <c r="P7" s="135" t="e">
         <f>IF(L7=G7,D7&amp;" "&amp;O7,D7&amp;" "&amp;O7&amp;"\P")</f>
         <v>#N/A</v>
       </c>
-      <c r="Q7" s="138" t="e">
+      <c r="Q7" s="136" t="e">
         <f>IF(C7=INDEX($C$7:$C$777777,G7+1),P7&amp;INDEX($P$7:$P$777777,G7+1),P7)&amp;IF(C7=INDEX($C$7:$C$777777,G7+2),INDEX($P$7:$P$777777,G7+2),"")&amp;IF(C7=INDEX($C$7:$C$777777,G7+3),INDEX($P$7:$P$777777,G7+3),"")&amp;IF(C7=INDEX($C$7:$C$777777,G7+4),INDEX($P$7:$P$777777,G7+4),"")&amp;IF(C7=INDEX($C$7:$C$777777,G7+5),INDEX($P$7:$P$777777,G7+5),"")&amp;IF(C7=INDEX($C$7:$C$777777,G7+6),INDEX($P$7:$P$777777,G7+6),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="R7" s="139"/>
+      <c r="R7" s="137"/>
       <c r="S7" t="s">
         <v>191</v>
       </c>
-      <c r="U7" s="140"/>
+      <c r="U7" s="138"/>
       <c r="AA7" t="s">
         <v>189</v>
       </c>
-      <c r="AE7" s="140"/>
+      <c r="AE7" s="138"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -13084,7 +13425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5903E6AF-14E2-4CDD-BE66-209E502F0B4C}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13103,7 +13444,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -13111,7 +13452,7 @@
         <v>170</v>
       </c>
       <c r="B3" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -13124,12 +13465,12 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B6" t="s">
         <v>0</v>
@@ -13148,7 +13489,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E733FA54-8601-4F98-A939-D35DC81D32C1}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13208,7 +13549,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD83D9D-2229-4BC6-AB0E-E63357D0D337}">
   <dimension ref="A3:N6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -13291,36 +13632,36 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D5" s="71" t="s">
+      <c r="D5" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="71" t="s">
+      <c r="E5" s="70" t="s">
         <v>323</v>
       </c>
-      <c r="F5" s="71" t="s">
+      <c r="F5" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="G5" s="71" t="s">
+      <c r="G5" s="70" t="s">
         <v>178</v>
       </c>
-      <c r="H5" s="71" t="s">
+      <c r="H5" s="70" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="71" t="s">
-        <v>397</v>
-      </c>
-      <c r="J5" s="71" t="s">
-        <v>398</v>
-      </c>
-      <c r="K5" s="71" t="s">
-        <v>399</v>
-      </c>
-      <c r="L5" s="75"/>
-      <c r="M5" s="75"/>
+      <c r="I5" s="70" t="s">
+        <v>392</v>
+      </c>
+      <c r="J5" s="70" t="s">
+        <v>393</v>
+      </c>
+      <c r="K5" s="70" t="s">
+        <v>394</v>
+      </c>
+      <c r="L5" s="74"/>
+      <c r="M5" s="74"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>601</v>
+        <v>630</v>
       </c>
       <c r="C6" t="s">
         <v>318</v>
@@ -13346,11 +13687,11 @@
         <v>0</v>
       </c>
       <c r="I6" s="48" t="str">
-        <f>'&lt;zalldev&gt;EXPORT'!BG11</f>
+        <f>'&lt;zalldev&gt;EXPORT'!BJ11</f>
         <v>0</v>
       </c>
       <c r="J6" s="48">
-        <f>'&lt;zalldev&gt;EXPORT'!BF11</f>
+        <f>'&lt;zalldev&gt;EXPORT'!BI11</f>
         <v>0</v>
       </c>
       <c r="K6" s="48">
@@ -13368,9 +13709,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4B9844E-F661-46DB-A8DF-606C0C725DFB}">
-  <dimension ref="A1:JC28"/>
+  <dimension ref="A1:JD28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="2.7109375" customWidth="1"/>
@@ -13425,96 +13766,96 @@
       </c>
     </row>
     <row r="4" spans="4:57" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D4" s="248" t="s">
+      <c r="D4" s="226" t="s">
         <v>313</v>
       </c>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
+      <c r="E4" s="226"/>
+      <c r="F4" s="226"/>
+      <c r="G4" s="226"/>
+      <c r="H4" s="226"/>
       <c r="I4" s="62" t="s">
         <v>312</v>
       </c>
-      <c r="J4" s="91"/>
-      <c r="K4" s="91"/>
+      <c r="J4" s="89"/>
+      <c r="K4" s="89"/>
       <c r="P4" s="62"/>
-      <c r="Q4" s="248" t="s">
+      <c r="Q4" s="226" t="s">
         <v>311</v>
       </c>
-      <c r="R4" s="248"/>
-      <c r="S4" s="248"/>
-      <c r="T4" s="248"/>
-      <c r="U4" s="248"/>
-      <c r="V4" s="248"/>
-      <c r="Z4" s="242" t="s">
-        <v>436</v>
-      </c>
-      <c r="AA4" s="242"/>
-      <c r="AU4" s="96" t="s">
+      <c r="R4" s="226"/>
+      <c r="S4" s="226"/>
+      <c r="T4" s="226"/>
+      <c r="U4" s="226"/>
+      <c r="V4" s="226"/>
+      <c r="Z4" s="241" t="s">
+        <v>431</v>
+      </c>
+      <c r="AA4" s="241"/>
+      <c r="AU4" s="94" t="s">
+        <v>398</v>
+      </c>
+      <c r="AV4" s="94" t="s">
+        <v>399</v>
+      </c>
+      <c r="AW4" s="94"/>
+      <c r="AX4" s="94" t="s">
+        <v>165</v>
+      </c>
+      <c r="AY4" s="94"/>
+      <c r="AZ4" s="94" t="s">
+        <v>397</v>
+      </c>
+      <c r="BA4" s="94" t="s">
+        <v>402</v>
+      </c>
+      <c r="BB4" s="94" t="s">
+        <v>396</v>
+      </c>
+      <c r="BC4" s="94" t="s">
+        <v>400</v>
+      </c>
+      <c r="BD4" s="94" t="s">
         <v>403</v>
       </c>
-      <c r="AV4" s="96" t="s">
-        <v>404</v>
-      </c>
-      <c r="AW4" s="96"/>
-      <c r="AX4" s="96" t="s">
-        <v>165</v>
-      </c>
-      <c r="AY4" s="96"/>
-      <c r="AZ4" s="96" t="s">
-        <v>402</v>
-      </c>
-      <c r="BA4" s="96" t="s">
-        <v>407</v>
-      </c>
-      <c r="BB4" s="96" t="s">
-        <v>401</v>
-      </c>
-      <c r="BC4" s="96" t="s">
-        <v>405</v>
-      </c>
-      <c r="BD4" s="96" t="s">
-        <v>408</v>
-      </c>
     </row>
     <row r="5" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D5" s="249" t="s">
+      <c r="D5" s="227" t="s">
         <v>310</v>
       </c>
-      <c r="E5" s="249"/>
-      <c r="F5" s="249"/>
-      <c r="G5" s="249"/>
-      <c r="H5" s="100">
+      <c r="E5" s="227"/>
+      <c r="F5" s="227"/>
+      <c r="G5" s="227"/>
+      <c r="H5" s="98">
         <f>AU5</f>
         <v>0</v>
       </c>
       <c r="I5" s="61" t="s">
         <v>309</v>
       </c>
-      <c r="J5" s="92"/>
-      <c r="K5" s="92"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
       <c r="P5" s="61" t="s">
         <v>308</v>
       </c>
-      <c r="Q5" s="250" t="s">
+      <c r="Q5" s="228" t="s">
         <v>307</v>
       </c>
-      <c r="R5" s="250"/>
-      <c r="S5" s="250"/>
-      <c r="T5" s="250"/>
-      <c r="U5" s="250">
+      <c r="R5" s="228"/>
+      <c r="S5" s="228"/>
+      <c r="T5" s="228"/>
+      <c r="U5" s="228">
         <f ca="1">ROUNDUP(SUM($AC$26:$AC$900000),2)</f>
         <v>0</v>
       </c>
-      <c r="V5" s="250"/>
-      <c r="Z5" s="99" t="s">
-        <v>424</v>
-      </c>
-      <c r="AA5" s="99">
+      <c r="V5" s="228"/>
+      <c r="Z5" s="97" t="s">
+        <v>419</v>
+      </c>
+      <c r="AA5" s="97">
         <v>1</v>
       </c>
       <c r="AT5" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="AU5" s="48">
         <f>'&lt;zlight&gt;TEMPGU'!D6</f>
@@ -13546,7 +13887,7 @@
         <f>'&lt;zlight&gt;TEMPGU'!J6</f>
         <v>0</v>
       </c>
-      <c r="BD5" s="97">
+      <c r="BD5" s="95">
         <f>IF(BC5=0,0,1)</f>
         <v>0</v>
       </c>
@@ -13555,301 +13896,301 @@
       </c>
     </row>
     <row r="6" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D6" s="251" t="s">
+      <c r="D6" s="229" t="s">
         <v>306</v>
       </c>
-      <c r="E6" s="251"/>
-      <c r="F6" s="251"/>
-      <c r="G6" s="251"/>
-      <c r="H6" s="90" t="s">
-        <v>443</v>
+      <c r="E6" s="229"/>
+      <c r="F6" s="229"/>
+      <c r="G6" s="229"/>
+      <c r="H6" s="88" t="s">
+        <v>438</v>
       </c>
       <c r="I6" s="61" t="s">
         <v>305</v>
       </c>
-      <c r="J6" s="92"/>
-      <c r="K6" s="92"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="90"/>
       <c r="P6" s="61">
         <v>63</v>
       </c>
-      <c r="Q6" s="250" t="s">
+      <c r="Q6" s="228" t="s">
         <v>304</v>
       </c>
-      <c r="R6" s="250"/>
-      <c r="S6" s="250"/>
-      <c r="T6" s="250"/>
-      <c r="U6" s="250">
+      <c r="R6" s="228"/>
+      <c r="S6" s="228"/>
+      <c r="T6" s="228"/>
+      <c r="U6" s="228">
         <f ca="1">ROUNDUP(U5*U11,2)</f>
         <v>0</v>
       </c>
-      <c r="V6" s="250"/>
-      <c r="Z6" s="99" t="s">
-        <v>425</v>
-      </c>
-      <c r="AA6" s="99">
+      <c r="V6" s="228"/>
+      <c r="Z6" s="97" t="s">
+        <v>420</v>
+      </c>
+      <c r="AA6" s="97">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D7" s="244" t="s">
+      <c r="D7" s="222" t="s">
         <v>303</v>
       </c>
-      <c r="E7" s="244"/>
-      <c r="F7" s="244"/>
-      <c r="G7" s="244"/>
+      <c r="E7" s="222"/>
+      <c r="F7" s="222"/>
+      <c r="G7" s="222"/>
       <c r="H7" s="58">
         <v>45399</v>
       </c>
       <c r="I7" s="61" t="s">
         <v>302</v>
       </c>
-      <c r="J7" s="92"/>
-      <c r="K7" s="92"/>
+      <c r="J7" s="90"/>
+      <c r="K7" s="90"/>
       <c r="P7" s="61">
         <v>32</v>
       </c>
-      <c r="Q7" s="250" t="s">
+      <c r="Q7" s="228" t="s">
         <v>301</v>
       </c>
-      <c r="R7" s="250"/>
-      <c r="S7" s="250"/>
-      <c r="T7" s="250"/>
-      <c r="U7" s="250">
+      <c r="R7" s="228"/>
+      <c r="S7" s="228"/>
+      <c r="T7" s="228"/>
+      <c r="U7" s="228">
         <f ca="1">ROUNDUP((U6*1000)/(INDEX(BD!C4:C5,MATCH(H11,BD!B4:B5,0))*U8),2)</f>
         <v>0</v>
       </c>
-      <c r="V7" s="250"/>
+      <c r="V7" s="228"/>
     </row>
     <row r="8" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D8" s="244" t="s">
+      <c r="D8" s="222" t="s">
         <v>300</v>
       </c>
-      <c r="E8" s="244"/>
-      <c r="F8" s="244"/>
-      <c r="G8" s="244"/>
+      <c r="E8" s="222"/>
+      <c r="F8" s="222"/>
+      <c r="G8" s="222"/>
       <c r="H8" s="58" t="s">
         <v>299</v>
       </c>
       <c r="I8" s="61" t="s">
         <v>298</v>
       </c>
-      <c r="J8" s="92"/>
-      <c r="K8" s="92"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="90"/>
       <c r="P8" s="61">
         <v>6</v>
       </c>
-      <c r="Q8" s="252" t="s">
+      <c r="Q8" s="230" t="s">
         <v>297</v>
       </c>
-      <c r="R8" s="253"/>
-      <c r="S8" s="253"/>
-      <c r="T8" s="254"/>
-      <c r="U8" s="257">
+      <c r="R8" s="231"/>
+      <c r="S8" s="231"/>
+      <c r="T8" s="232"/>
+      <c r="U8" s="235">
         <v>0.92</v>
       </c>
-      <c r="V8" s="257"/>
+      <c r="V8" s="235"/>
     </row>
     <row r="9" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D9" s="244" t="s">
+      <c r="D9" s="222" t="s">
         <v>296</v>
       </c>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
+      <c r="E9" s="222"/>
+      <c r="F9" s="222"/>
+      <c r="G9" s="222"/>
       <c r="H9" s="58" t="s">
         <v>295</v>
       </c>
       <c r="I9" s="61" t="s">
         <v>294</v>
       </c>
-      <c r="J9" s="92"/>
-      <c r="K9" s="92"/>
+      <c r="J9" s="90"/>
+      <c r="K9" s="90"/>
       <c r="P9" s="61" t="s">
         <v>293</v>
       </c>
-      <c r="Q9" s="245" t="s">
+      <c r="Q9" s="223" t="s">
         <v>292</v>
       </c>
-      <c r="R9" s="245"/>
-      <c r="S9" s="245"/>
-      <c r="T9" s="245"/>
-      <c r="U9" s="246"/>
-      <c r="V9" s="246"/>
+      <c r="R9" s="223"/>
+      <c r="S9" s="223"/>
+      <c r="T9" s="223"/>
+      <c r="U9" s="224"/>
+      <c r="V9" s="224"/>
     </row>
     <row r="10" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D10" s="244" t="s">
+      <c r="D10" s="222" t="s">
         <v>291</v>
       </c>
-      <c r="E10" s="244"/>
-      <c r="F10" s="244"/>
-      <c r="G10" s="244"/>
+      <c r="E10" s="222"/>
+      <c r="F10" s="222"/>
+      <c r="G10" s="222"/>
       <c r="I10" s="61" t="s">
         <v>290</v>
       </c>
-      <c r="J10" s="92"/>
-      <c r="K10" s="92"/>
+      <c r="J10" s="90"/>
+      <c r="K10" s="90"/>
       <c r="P10" s="61">
         <v>4</v>
       </c>
-      <c r="Q10" s="245"/>
-      <c r="R10" s="245"/>
-      <c r="S10" s="245"/>
-      <c r="T10" s="245"/>
-      <c r="U10" s="246"/>
-      <c r="V10" s="246"/>
+      <c r="Q10" s="223"/>
+      <c r="R10" s="223"/>
+      <c r="S10" s="223"/>
+      <c r="T10" s="223"/>
+      <c r="U10" s="224"/>
+      <c r="V10" s="224"/>
     </row>
     <row r="11" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D11" s="244" t="s">
+      <c r="D11" s="222" t="s">
         <v>289</v>
       </c>
-      <c r="E11" s="244"/>
-      <c r="F11" s="244"/>
-      <c r="G11" s="244"/>
-      <c r="H11" s="99">
+      <c r="E11" s="222"/>
+      <c r="F11" s="222"/>
+      <c r="G11" s="222"/>
+      <c r="H11" s="97">
         <v>380</v>
       </c>
       <c r="I11" s="61" t="s">
         <v>288</v>
       </c>
-      <c r="J11" s="92"/>
-      <c r="K11" s="92"/>
+      <c r="J11" s="90"/>
+      <c r="K11" s="90"/>
       <c r="P11" s="61" t="s">
         <v>287</v>
       </c>
-      <c r="Q11" s="270" t="s">
+      <c r="Q11" s="249" t="s">
         <v>286</v>
       </c>
-      <c r="R11" s="271"/>
-      <c r="S11" s="271"/>
-      <c r="T11" s="272"/>
-      <c r="U11" s="273">
+      <c r="R11" s="250"/>
+      <c r="S11" s="250"/>
+      <c r="T11" s="251"/>
+      <c r="U11" s="252">
         <v>1</v>
       </c>
-      <c r="V11" s="274"/>
+      <c r="V11" s="253"/>
     </row>
     <row r="12" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D12" s="244" t="s">
+      <c r="D12" s="222" t="s">
         <v>285</v>
       </c>
-      <c r="E12" s="244"/>
-      <c r="F12" s="244"/>
-      <c r="G12" s="244"/>
+      <c r="E12" s="222"/>
+      <c r="F12" s="222"/>
+      <c r="G12" s="222"/>
       <c r="H12" s="58" t="s">
         <v>284</v>
       </c>
       <c r="I12" s="61" t="s">
         <v>214</v>
       </c>
-      <c r="J12" s="92"/>
-      <c r="K12" s="92"/>
+      <c r="J12" s="90"/>
+      <c r="K12" s="90"/>
       <c r="P12" s="61" t="s">
         <v>283</v>
       </c>
-      <c r="Q12" s="247" t="s">
+      <c r="Q12" s="225" t="s">
         <v>282</v>
       </c>
-      <c r="R12" s="247"/>
-      <c r="S12" s="247"/>
-      <c r="T12" s="247"/>
-      <c r="U12" s="247">
+      <c r="R12" s="225"/>
+      <c r="S12" s="225"/>
+      <c r="T12" s="225"/>
+      <c r="U12" s="225">
         <v>44.5</v>
       </c>
-      <c r="V12" s="247"/>
+      <c r="V12" s="225"/>
     </row>
     <row r="13" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D13" s="244" t="s">
+      <c r="D13" s="222" t="s">
         <v>281</v>
       </c>
-      <c r="E13" s="244"/>
-      <c r="F13" s="244"/>
-      <c r="G13" s="244"/>
+      <c r="E13" s="222"/>
+      <c r="F13" s="222"/>
+      <c r="G13" s="222"/>
       <c r="H13" s="58" t="s">
         <v>280</v>
       </c>
       <c r="I13" s="59"/>
       <c r="P13" s="59"/>
-      <c r="Q13" s="247" t="s">
+      <c r="Q13" s="225" t="s">
         <v>279</v>
       </c>
-      <c r="R13" s="247"/>
-      <c r="S13" s="247"/>
-      <c r="T13" s="247"/>
-      <c r="U13" s="247">
+      <c r="R13" s="225"/>
+      <c r="S13" s="225"/>
+      <c r="T13" s="225"/>
+      <c r="U13" s="225">
         <v>44.5</v>
       </c>
-      <c r="V13" s="247"/>
+      <c r="V13" s="225"/>
     </row>
     <row r="14" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D14" s="244" t="s">
+      <c r="D14" s="222" t="s">
         <v>278</v>
       </c>
-      <c r="E14" s="244"/>
-      <c r="F14" s="244"/>
-      <c r="G14" s="244"/>
+      <c r="E14" s="222"/>
+      <c r="F14" s="222"/>
+      <c r="G14" s="222"/>
       <c r="H14" s="60" t="str">
         <f>'&lt;zlight&gt;'!G20&amp;"."&amp;'&lt;zlight&gt;'!H20</f>
         <v>.</v>
       </c>
       <c r="I14" s="59"/>
       <c r="P14" s="59"/>
-      <c r="Q14" s="247" t="s">
+      <c r="Q14" s="225" t="s">
         <v>277</v>
       </c>
-      <c r="R14" s="247"/>
-      <c r="S14" s="247"/>
-      <c r="T14" s="247"/>
-      <c r="U14" s="247">
+      <c r="R14" s="225"/>
+      <c r="S14" s="225"/>
+      <c r="T14" s="225"/>
+      <c r="U14" s="225">
         <v>44.5</v>
       </c>
-      <c r="V14" s="247"/>
+      <c r="V14" s="225"/>
     </row>
     <row r="15" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="D15" s="244" t="s">
+      <c r="D15" s="222" t="s">
         <v>276</v>
       </c>
-      <c r="E15" s="244"/>
-      <c r="F15" s="244"/>
-      <c r="G15" s="244"/>
+      <c r="E15" s="222"/>
+      <c r="F15" s="222"/>
+      <c r="G15" s="222"/>
       <c r="H15" s="58">
         <v>77</v>
       </c>
       <c r="P15" s="59"/>
-      <c r="Q15" s="256" t="s">
+      <c r="Q15" s="234" t="s">
         <v>275</v>
       </c>
-      <c r="R15" s="256"/>
-      <c r="S15" s="256"/>
-      <c r="T15" s="256"/>
-      <c r="U15" s="257">
+      <c r="R15" s="234"/>
+      <c r="S15" s="234"/>
+      <c r="T15" s="234"/>
+      <c r="U15" s="235">
         <f ca="1">ROUNDUP((U6*1000)/(INDEX(BD!$C$4:$C$5,MATCH(H11,BD!$B$4:$B$5,0))*U8),2)</f>
         <v>0</v>
       </c>
-      <c r="V15" s="257"/>
+      <c r="V15" s="235"/>
     </row>
     <row r="16" spans="4:57" x14ac:dyDescent="0.25">
-      <c r="Q16" s="260" t="s">
-        <v>406</v>
-      </c>
-      <c r="R16" s="260"/>
-      <c r="S16" s="260"/>
-      <c r="T16" s="260"/>
-      <c r="U16" s="260" t="e">
+      <c r="Q16" s="238" t="s">
+        <v>401</v>
+      </c>
+      <c r="R16" s="238"/>
+      <c r="S16" s="238"/>
+      <c r="T16" s="238"/>
+      <c r="U16" s="238" t="e">
         <f>INDEX(BB5:BB9,MATCH(1,BD5:BD9,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="V16" s="260"/>
-    </row>
-    <row r="22" spans="1:263" x14ac:dyDescent="0.25">
-      <c r="L22" s="141" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="23" spans="1:263" x14ac:dyDescent="0.25">
-      <c r="L23" s="142">
+      <c r="V16" s="238"/>
+    </row>
+    <row r="22" spans="1:264" x14ac:dyDescent="0.25">
+      <c r="L22" s="139" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="23" spans="1:264" x14ac:dyDescent="0.25">
+      <c r="L23" s="140">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:263" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:264" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <f>COLUMN(A24)</f>
         <v>1</v>
@@ -14625,7 +14966,7 @@
         <v>195</v>
       </c>
       <c r="GN24" s="2">
-        <f t="shared" ref="GN24:IP24" si="3">COLUMN(GN24)</f>
+        <f t="shared" ref="GN24:IQ24" si="3">COLUMN(GN24)</f>
         <v>196</v>
       </c>
       <c r="GO24" s="2">
@@ -14837,16 +15178,13 @@
         <v>248</v>
       </c>
       <c r="IO24" s="2"/>
-      <c r="IP24" s="2">
+      <c r="IP24" s="2"/>
+      <c r="IQ24" s="2">
         <f t="shared" si="3"/>
-        <v>250</v>
-      </c>
-      <c r="IQ24" s="1">
-        <f t="shared" ref="IQ24:JC24" si="4">COLUMN(IQ24)</f>
         <v>251</v>
       </c>
       <c r="IR24" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="IR24:JD24" si="4">COLUMN(IR24)</f>
         <v>252</v>
       </c>
       <c r="IS24" s="1">
@@ -14893,211 +15231,215 @@
         <f t="shared" si="4"/>
         <v>263</v>
       </c>
-    </row>
-    <row r="25" spans="1:263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="BD25" s="264" t="s">
-        <v>514</v>
-      </c>
-      <c r="BE25" s="265"/>
-      <c r="BF25" s="265"/>
-      <c r="BG25" s="265"/>
-      <c r="BH25" s="265"/>
-      <c r="BI25" s="265"/>
-      <c r="BJ25" s="265"/>
-      <c r="BK25" s="265"/>
-      <c r="BL25" s="265"/>
-      <c r="BM25" s="265"/>
-      <c r="BN25" s="265"/>
-      <c r="BO25" s="265"/>
-      <c r="BP25" s="265"/>
-      <c r="BQ25" s="265"/>
-      <c r="BR25" s="265"/>
-      <c r="BS25" s="265"/>
-      <c r="BT25" s="265"/>
-      <c r="BU25" s="265"/>
-      <c r="BV25" s="265"/>
-      <c r="BW25" s="265"/>
-      <c r="BX25" s="265"/>
-      <c r="BY25" s="265"/>
-      <c r="BZ25" s="265"/>
-      <c r="CA25" s="266"/>
-      <c r="CB25" s="264" t="s">
-        <v>517</v>
-      </c>
-      <c r="CC25" s="265"/>
-      <c r="CD25" s="265"/>
-      <c r="CE25" s="265"/>
-      <c r="CF25" s="265"/>
-      <c r="CG25" s="265"/>
-      <c r="CH25" s="265"/>
-      <c r="CI25" s="265"/>
-      <c r="CJ25" s="265"/>
-      <c r="CK25" s="265"/>
-      <c r="CL25" s="265"/>
-      <c r="CM25" s="265"/>
-      <c r="CN25" s="265"/>
-      <c r="CO25" s="265"/>
-      <c r="CP25" s="265"/>
-      <c r="CQ25" s="265"/>
-      <c r="CR25" s="265"/>
-      <c r="CS25" s="265"/>
-      <c r="CT25" s="267" t="s">
+      <c r="JD24" s="1">
+        <f t="shared" si="4"/>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="25" spans="1:264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BD25" s="243" t="s">
+        <v>509</v>
+      </c>
+      <c r="BE25" s="244"/>
+      <c r="BF25" s="244"/>
+      <c r="BG25" s="244"/>
+      <c r="BH25" s="244"/>
+      <c r="BI25" s="244"/>
+      <c r="BJ25" s="244"/>
+      <c r="BK25" s="244"/>
+      <c r="BL25" s="244"/>
+      <c r="BM25" s="244"/>
+      <c r="BN25" s="244"/>
+      <c r="BO25" s="244"/>
+      <c r="BP25" s="244"/>
+      <c r="BQ25" s="244"/>
+      <c r="BR25" s="244"/>
+      <c r="BS25" s="244"/>
+      <c r="BT25" s="244"/>
+      <c r="BU25" s="244"/>
+      <c r="BV25" s="244"/>
+      <c r="BW25" s="244"/>
+      <c r="BX25" s="244"/>
+      <c r="BY25" s="244"/>
+      <c r="BZ25" s="244"/>
+      <c r="CA25" s="245"/>
+      <c r="CB25" s="243" t="s">
+        <v>512</v>
+      </c>
+      <c r="CC25" s="244"/>
+      <c r="CD25" s="244"/>
+      <c r="CE25" s="244"/>
+      <c r="CF25" s="244"/>
+      <c r="CG25" s="244"/>
+      <c r="CH25" s="244"/>
+      <c r="CI25" s="244"/>
+      <c r="CJ25" s="244"/>
+      <c r="CK25" s="244"/>
+      <c r="CL25" s="244"/>
+      <c r="CM25" s="244"/>
+      <c r="CN25" s="244"/>
+      <c r="CO25" s="244"/>
+      <c r="CP25" s="244"/>
+      <c r="CQ25" s="244"/>
+      <c r="CR25" s="244"/>
+      <c r="CS25" s="244"/>
+      <c r="CT25" s="246" t="s">
         <v>266</v>
       </c>
-      <c r="CU25" s="268"/>
-      <c r="CV25" s="268"/>
-      <c r="CW25" s="268"/>
-      <c r="CX25" s="268"/>
-      <c r="CY25" s="268"/>
-      <c r="CZ25" s="268"/>
-      <c r="DA25" s="268"/>
-      <c r="DB25" s="268"/>
-      <c r="DC25" s="268"/>
-      <c r="DD25" s="268"/>
-      <c r="DE25" s="268"/>
-      <c r="DF25" s="268"/>
-      <c r="DG25" s="268"/>
-      <c r="DH25" s="268"/>
-      <c r="DI25" s="268"/>
-      <c r="DJ25" s="268"/>
-      <c r="DK25" s="268"/>
-      <c r="DL25" s="268"/>
-      <c r="DM25" s="268"/>
-      <c r="DN25" s="268"/>
-      <c r="DO25" s="268"/>
-      <c r="DP25" s="268"/>
-      <c r="DQ25" s="268"/>
-      <c r="DR25" s="268"/>
-      <c r="DS25" s="268"/>
-      <c r="DT25" s="268"/>
-      <c r="DU25" s="268"/>
-      <c r="DV25" s="268"/>
-      <c r="DW25" s="268"/>
-      <c r="DX25" s="268"/>
-      <c r="DY25" s="268"/>
-      <c r="DZ25" s="268"/>
-      <c r="EA25" s="268"/>
-      <c r="EB25" s="268"/>
-      <c r="EC25" s="268"/>
-      <c r="ED25" s="268"/>
-      <c r="EE25" s="268"/>
-      <c r="EF25" s="268"/>
-      <c r="EG25" s="268"/>
-      <c r="EH25" s="268"/>
-      <c r="EI25" s="268"/>
-      <c r="EJ25" s="268"/>
-      <c r="EK25" s="268"/>
-      <c r="EL25" s="268"/>
-      <c r="EM25" s="268"/>
-      <c r="EN25" s="268"/>
-      <c r="EO25" s="268"/>
-      <c r="EP25" s="268"/>
-      <c r="EQ25" s="268"/>
-      <c r="ER25" s="268"/>
-      <c r="ES25" s="268"/>
-      <c r="ET25" s="268"/>
-      <c r="EU25" s="268"/>
-      <c r="EV25" s="268"/>
-      <c r="EW25" s="268"/>
-      <c r="EX25" s="268"/>
-      <c r="EY25" s="268"/>
-      <c r="EZ25" s="268"/>
-      <c r="FA25" s="268"/>
-      <c r="FB25" s="268"/>
-      <c r="FC25" s="268"/>
-      <c r="FD25" s="268"/>
-      <c r="FE25" s="268"/>
-      <c r="FF25" s="268"/>
-      <c r="FG25" s="268"/>
-      <c r="FH25" s="268"/>
-      <c r="FI25" s="268"/>
-      <c r="FJ25" s="268"/>
-      <c r="FK25" s="268"/>
-      <c r="FL25" s="268"/>
-      <c r="FM25" s="268"/>
-      <c r="FN25" s="268"/>
-      <c r="FO25" s="268"/>
-      <c r="FP25" s="269"/>
-    </row>
-    <row r="26" spans="1:263" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D26" s="258" t="s">
+      <c r="CU25" s="247"/>
+      <c r="CV25" s="247"/>
+      <c r="CW25" s="247"/>
+      <c r="CX25" s="247"/>
+      <c r="CY25" s="247"/>
+      <c r="CZ25" s="247"/>
+      <c r="DA25" s="247"/>
+      <c r="DB25" s="247"/>
+      <c r="DC25" s="247"/>
+      <c r="DD25" s="247"/>
+      <c r="DE25" s="247"/>
+      <c r="DF25" s="247"/>
+      <c r="DG25" s="247"/>
+      <c r="DH25" s="247"/>
+      <c r="DI25" s="247"/>
+      <c r="DJ25" s="247"/>
+      <c r="DK25" s="247"/>
+      <c r="DL25" s="247"/>
+      <c r="DM25" s="247"/>
+      <c r="DN25" s="247"/>
+      <c r="DO25" s="247"/>
+      <c r="DP25" s="247"/>
+      <c r="DQ25" s="247"/>
+      <c r="DR25" s="247"/>
+      <c r="DS25" s="247"/>
+      <c r="DT25" s="247"/>
+      <c r="DU25" s="247"/>
+      <c r="DV25" s="247"/>
+      <c r="DW25" s="247"/>
+      <c r="DX25" s="247"/>
+      <c r="DY25" s="247"/>
+      <c r="DZ25" s="247"/>
+      <c r="EA25" s="247"/>
+      <c r="EB25" s="247"/>
+      <c r="EC25" s="247"/>
+      <c r="ED25" s="247"/>
+      <c r="EE25" s="247"/>
+      <c r="EF25" s="247"/>
+      <c r="EG25" s="247"/>
+      <c r="EH25" s="247"/>
+      <c r="EI25" s="247"/>
+      <c r="EJ25" s="247"/>
+      <c r="EK25" s="247"/>
+      <c r="EL25" s="247"/>
+      <c r="EM25" s="247"/>
+      <c r="EN25" s="247"/>
+      <c r="EO25" s="247"/>
+      <c r="EP25" s="247"/>
+      <c r="EQ25" s="247"/>
+      <c r="ER25" s="247"/>
+      <c r="ES25" s="247"/>
+      <c r="ET25" s="247"/>
+      <c r="EU25" s="247"/>
+      <c r="EV25" s="247"/>
+      <c r="EW25" s="247"/>
+      <c r="EX25" s="247"/>
+      <c r="EY25" s="247"/>
+      <c r="EZ25" s="247"/>
+      <c r="FA25" s="247"/>
+      <c r="FB25" s="247"/>
+      <c r="FC25" s="247"/>
+      <c r="FD25" s="247"/>
+      <c r="FE25" s="247"/>
+      <c r="FF25" s="247"/>
+      <c r="FG25" s="247"/>
+      <c r="FH25" s="247"/>
+      <c r="FI25" s="247"/>
+      <c r="FJ25" s="247"/>
+      <c r="FK25" s="247"/>
+      <c r="FL25" s="247"/>
+      <c r="FM25" s="247"/>
+      <c r="FN25" s="247"/>
+      <c r="FO25" s="247"/>
+      <c r="FP25" s="248"/>
+    </row>
+    <row r="26" spans="1:264" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D26" s="236" t="s">
         <v>274</v>
       </c>
-      <c r="E26" s="255" t="s">
+      <c r="E26" s="233" t="s">
         <v>225</v>
       </c>
-      <c r="F26" s="255" t="s">
+      <c r="F26" s="233" t="s">
         <v>224</v>
       </c>
-      <c r="G26" s="255" t="s">
+      <c r="G26" s="233" t="s">
         <v>273</v>
       </c>
-      <c r="H26" s="255" t="s">
+      <c r="H26" s="233" t="s">
         <v>272</v>
       </c>
-      <c r="I26" s="255" t="s">
+      <c r="I26" s="233" t="s">
         <v>271</v>
       </c>
-      <c r="J26" s="279" t="s">
-        <v>612</v>
-      </c>
-      <c r="K26" s="259" t="s">
-        <v>390</v>
-      </c>
-      <c r="L26" s="282" t="s">
-        <v>391</v>
-      </c>
-      <c r="M26" s="282"/>
-      <c r="N26" s="282"/>
-      <c r="O26" s="255" t="s">
+      <c r="J26" s="258" t="s">
+        <v>605</v>
+      </c>
+      <c r="K26" s="237" t="s">
+        <v>385</v>
+      </c>
+      <c r="L26" s="261" t="s">
+        <v>386</v>
+      </c>
+      <c r="M26" s="261"/>
+      <c r="N26" s="261"/>
+      <c r="O26" s="233" t="s">
         <v>270</v>
       </c>
-      <c r="P26" s="283" t="s">
+      <c r="P26" s="262" t="s">
         <v>269</v>
       </c>
-      <c r="Q26" s="283"/>
-      <c r="R26" s="283"/>
-      <c r="S26" s="283"/>
-      <c r="T26" s="283"/>
-      <c r="U26" s="283"/>
-      <c r="V26" s="283"/>
-      <c r="W26" s="283"/>
-      <c r="X26" s="283"/>
-      <c r="Y26" s="283"/>
-      <c r="Z26" s="283"/>
-      <c r="AA26" s="283"/>
-      <c r="AB26" s="284" t="s">
+      <c r="Q26" s="262"/>
+      <c r="R26" s="262"/>
+      <c r="S26" s="262"/>
+      <c r="T26" s="262"/>
+      <c r="U26" s="262"/>
+      <c r="V26" s="262"/>
+      <c r="W26" s="262"/>
+      <c r="X26" s="262"/>
+      <c r="Y26" s="262"/>
+      <c r="Z26" s="262"/>
+      <c r="AA26" s="262"/>
+      <c r="AB26" s="263" t="s">
         <v>268</v>
       </c>
-      <c r="AC26" s="284"/>
-      <c r="AD26" s="284"/>
-      <c r="AE26" s="284"/>
-      <c r="AF26" s="284"/>
-      <c r="AG26" s="284"/>
-      <c r="AH26" s="284"/>
-      <c r="AI26" s="284"/>
-      <c r="AJ26" s="284"/>
-      <c r="AK26" s="284"/>
-      <c r="AL26" s="284"/>
-      <c r="AM26" s="284"/>
-      <c r="AN26" s="284" t="s">
+      <c r="AC26" s="263"/>
+      <c r="AD26" s="263"/>
+      <c r="AE26" s="263"/>
+      <c r="AF26" s="263"/>
+      <c r="AG26" s="263"/>
+      <c r="AH26" s="263"/>
+      <c r="AI26" s="263"/>
+      <c r="AJ26" s="263"/>
+      <c r="AK26" s="263"/>
+      <c r="AL26" s="263"/>
+      <c r="AM26" s="263"/>
+      <c r="AN26" s="263" t="s">
         <v>267</v>
       </c>
-      <c r="AO26" s="284"/>
-      <c r="AP26" s="284"/>
-      <c r="AQ26" s="284"/>
-      <c r="AR26" s="284"/>
-      <c r="AS26" s="284"/>
-      <c r="AT26" s="284"/>
-      <c r="AU26" s="284"/>
-      <c r="AV26" s="284"/>
-      <c r="AW26" s="284"/>
-      <c r="AX26" s="284"/>
-      <c r="AY26" s="284"/>
-      <c r="AZ26" s="284"/>
-      <c r="BA26" s="284"/>
-      <c r="BB26" s="284"/>
-      <c r="BC26" s="284"/>
+      <c r="AO26" s="263"/>
+      <c r="AP26" s="263"/>
+      <c r="AQ26" s="263"/>
+      <c r="AR26" s="263"/>
+      <c r="AS26" s="263"/>
+      <c r="AT26" s="263"/>
+      <c r="AU26" s="263"/>
+      <c r="AV26" s="263"/>
+      <c r="AW26" s="263"/>
+      <c r="AX26" s="263"/>
+      <c r="AY26" s="263"/>
+      <c r="AZ26" s="263"/>
+      <c r="BA26" s="263"/>
+      <c r="BB26" s="263"/>
+      <c r="BC26" s="263"/>
       <c r="BD26" s="59"/>
       <c r="BE26" s="59"/>
       <c r="BF26" s="59"/>
@@ -15106,26 +15448,26 @@
       <c r="BI26" s="59"/>
       <c r="BJ26" s="59"/>
       <c r="BK26" s="59"/>
-      <c r="BL26" s="286" t="s">
-        <v>503</v>
-      </c>
-      <c r="BM26" s="286"/>
-      <c r="BN26" s="286"/>
-      <c r="BO26" s="286"/>
-      <c r="BP26" s="286"/>
-      <c r="BQ26" s="286"/>
-      <c r="BR26" s="286"/>
-      <c r="BS26" s="286"/>
+      <c r="BL26" s="265" t="s">
+        <v>498</v>
+      </c>
+      <c r="BM26" s="265"/>
+      <c r="BN26" s="265"/>
+      <c r="BO26" s="265"/>
+      <c r="BP26" s="265"/>
+      <c r="BQ26" s="265"/>
+      <c r="BR26" s="265"/>
+      <c r="BS26" s="265"/>
       <c r="BT26" s="59"/>
       <c r="BU26" s="59"/>
       <c r="BV26" s="59"/>
-      <c r="BW26" s="287" t="s">
-        <v>516</v>
-      </c>
-      <c r="BX26" s="287"/>
-      <c r="BY26" s="287"/>
-      <c r="BZ26" s="287"/>
-      <c r="CA26" s="287"/>
+      <c r="BW26" s="266" t="s">
+        <v>511</v>
+      </c>
+      <c r="BX26" s="266"/>
+      <c r="BY26" s="266"/>
+      <c r="BZ26" s="266"/>
+      <c r="CA26" s="266"/>
       <c r="CB26" s="59"/>
       <c r="CC26" s="59"/>
       <c r="CD26" s="59"/>
@@ -15156,110 +15498,110 @@
       <c r="DC26" s="59"/>
       <c r="DD26" s="59"/>
       <c r="DE26" s="59"/>
-      <c r="DF26" s="276" t="s">
-        <v>535</v>
-      </c>
-      <c r="DG26" s="276"/>
-      <c r="DH26" s="276"/>
-      <c r="DI26" s="276"/>
-      <c r="DJ26" s="276"/>
-      <c r="DK26" s="276"/>
-      <c r="DL26" s="276"/>
-      <c r="DM26" s="276"/>
-      <c r="DN26" s="276"/>
-      <c r="DO26" s="276"/>
-      <c r="DP26" s="276"/>
-      <c r="DQ26" s="276"/>
-      <c r="DR26" s="276"/>
-      <c r="DS26" s="276"/>
-      <c r="DT26" s="276"/>
-      <c r="DU26" s="276"/>
-      <c r="DV26" s="276"/>
-      <c r="DW26" s="276"/>
-      <c r="DX26" s="275" t="s">
+      <c r="DF26" s="255" t="s">
+        <v>530</v>
+      </c>
+      <c r="DG26" s="255"/>
+      <c r="DH26" s="255"/>
+      <c r="DI26" s="255"/>
+      <c r="DJ26" s="255"/>
+      <c r="DK26" s="255"/>
+      <c r="DL26" s="255"/>
+      <c r="DM26" s="255"/>
+      <c r="DN26" s="255"/>
+      <c r="DO26" s="255"/>
+      <c r="DP26" s="255"/>
+      <c r="DQ26" s="255"/>
+      <c r="DR26" s="255"/>
+      <c r="DS26" s="255"/>
+      <c r="DT26" s="255"/>
+      <c r="DU26" s="255"/>
+      <c r="DV26" s="255"/>
+      <c r="DW26" s="255"/>
+      <c r="DX26" s="254" t="s">
         <v>206</v>
       </c>
-      <c r="DY26" s="275"/>
-      <c r="DZ26" s="275"/>
-      <c r="EA26" s="261" t="s">
+      <c r="DY26" s="254"/>
+      <c r="DZ26" s="254"/>
+      <c r="EA26" s="239" t="s">
         <v>205</v>
       </c>
-      <c r="EB26" s="262"/>
-      <c r="EC26" s="262"/>
-      <c r="ED26" s="262"/>
-      <c r="EE26" s="262"/>
-      <c r="EF26" s="262"/>
-      <c r="EG26" s="262"/>
-      <c r="EH26" s="262"/>
-      <c r="EI26" s="262"/>
-      <c r="EJ26" s="262"/>
-      <c r="EK26" s="262"/>
-      <c r="EL26" s="262"/>
-      <c r="EM26" s="262"/>
-      <c r="EN26" s="262"/>
-      <c r="EO26" s="262"/>
-      <c r="EP26" s="262"/>
-      <c r="EQ26" s="277" t="s">
+      <c r="EB26" s="240"/>
+      <c r="EC26" s="240"/>
+      <c r="ED26" s="240"/>
+      <c r="EE26" s="240"/>
+      <c r="EF26" s="240"/>
+      <c r="EG26" s="240"/>
+      <c r="EH26" s="240"/>
+      <c r="EI26" s="240"/>
+      <c r="EJ26" s="240"/>
+      <c r="EK26" s="240"/>
+      <c r="EL26" s="240"/>
+      <c r="EM26" s="240"/>
+      <c r="EN26" s="240"/>
+      <c r="EO26" s="240"/>
+      <c r="EP26" s="240"/>
+      <c r="EQ26" s="256" t="s">
         <v>204</v>
       </c>
-      <c r="ER26" s="277"/>
-      <c r="ES26" s="277"/>
-      <c r="ET26" s="277"/>
-      <c r="EU26" s="277"/>
-      <c r="EV26" s="277"/>
-      <c r="EW26" s="278" t="s">
+      <c r="ER26" s="256"/>
+      <c r="ES26" s="256"/>
+      <c r="ET26" s="256"/>
+      <c r="EU26" s="256"/>
+      <c r="EV26" s="256"/>
+      <c r="EW26" s="257" t="s">
         <v>203</v>
       </c>
-      <c r="EX26" s="278"/>
-      <c r="EY26" s="278"/>
-      <c r="EZ26" s="278"/>
-      <c r="FA26" s="278" t="s">
+      <c r="EX26" s="257"/>
+      <c r="EY26" s="257"/>
+      <c r="EZ26" s="257"/>
+      <c r="FA26" s="257" t="s">
         <v>202</v>
       </c>
-      <c r="FB26" s="278"/>
-      <c r="FC26" s="278"/>
-      <c r="FD26" s="278"/>
-      <c r="FE26" s="278" t="s">
+      <c r="FB26" s="257"/>
+      <c r="FC26" s="257"/>
+      <c r="FD26" s="257"/>
+      <c r="FE26" s="257" t="s">
         <v>201</v>
       </c>
-      <c r="FF26" s="278"/>
-      <c r="FG26" s="278"/>
-      <c r="FH26" s="278"/>
-      <c r="FI26" s="278"/>
-      <c r="FJ26" s="278"/>
-      <c r="FK26" s="278" t="s">
+      <c r="FF26" s="257"/>
+      <c r="FG26" s="257"/>
+      <c r="FH26" s="257"/>
+      <c r="FI26" s="257"/>
+      <c r="FJ26" s="257"/>
+      <c r="FK26" s="257" t="s">
         <v>200</v>
       </c>
-      <c r="FL26" s="278"/>
-      <c r="FM26" s="278"/>
-      <c r="FN26" s="278"/>
-      <c r="FO26" s="278"/>
+      <c r="FL26" s="257"/>
+      <c r="FM26" s="257"/>
+      <c r="FN26" s="257"/>
+      <c r="FO26" s="257"/>
       <c r="FP26" s="59"/>
-      <c r="FQ26" s="83"/>
-      <c r="FR26" s="83"/>
+      <c r="FQ26" s="81"/>
+      <c r="FR26" s="81"/>
       <c r="FS26" t="s">
         <v>209</v>
       </c>
       <c r="FT26" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="FU26" s="111">
+      <c r="FU26" s="109">
         <f>60*$AA$5</f>
         <v>60</v>
       </c>
-      <c r="FV26" s="111">
+      <c r="FV26" s="109">
         <f>0*$AA$6</f>
         <v>0</v>
       </c>
-      <c r="FW26" s="108">
+      <c r="FW26" s="106">
         <f>$AA$5</f>
         <v>1</v>
       </c>
-      <c r="FX26" s="108">
+      <c r="FX26" s="106">
         <f>$AA$6</f>
         <v>1</v>
       </c>
-      <c r="FY26" s="113">
+      <c r="FY26" s="111">
         <v>0</v>
       </c>
       <c r="FZ26" t="s">
@@ -15315,574 +15657,575 @@
         <v>191</v>
       </c>
     </row>
-    <row r="27" spans="1:263" ht="103.5" x14ac:dyDescent="0.25">
-      <c r="D27" s="258"/>
-      <c r="E27" s="255"/>
-      <c r="F27" s="255"/>
-      <c r="G27" s="255"/>
-      <c r="H27" s="255"/>
-      <c r="I27" s="255"/>
-      <c r="J27" s="280"/>
-      <c r="K27" s="259"/>
-      <c r="L27" s="93" t="s">
+    <row r="27" spans="1:264" ht="103.5" x14ac:dyDescent="0.25">
+      <c r="D27" s="236"/>
+      <c r="E27" s="233"/>
+      <c r="F27" s="233"/>
+      <c r="G27" s="233"/>
+      <c r="H27" s="233"/>
+      <c r="I27" s="233"/>
+      <c r="J27" s="259"/>
+      <c r="K27" s="237"/>
+      <c r="L27" s="91" t="s">
         <v>257</v>
       </c>
-      <c r="M27" s="93" t="s">
+      <c r="M27" s="91" t="s">
         <v>256</v>
       </c>
-      <c r="N27" s="93" t="s">
+      <c r="N27" s="91" t="s">
         <v>255</v>
       </c>
-      <c r="O27" s="255"/>
-      <c r="P27" s="163" t="s">
+      <c r="O27" s="233"/>
+      <c r="P27" s="161" t="s">
         <v>329</v>
       </c>
-      <c r="Q27" s="163" t="s">
+      <c r="Q27" s="161" t="s">
         <v>254</v>
       </c>
-      <c r="R27" s="163" t="s">
+      <c r="R27" s="161" t="s">
         <v>3</v>
       </c>
-      <c r="S27" s="164" t="s">
+      <c r="S27" s="162" t="s">
         <v>253</v>
       </c>
-      <c r="T27" s="165" t="s">
+      <c r="T27" s="163" t="s">
         <v>252</v>
       </c>
-      <c r="U27" s="164" t="s">
+      <c r="U27" s="162" t="s">
         <v>251</v>
       </c>
-      <c r="V27" s="164" t="s">
+      <c r="V27" s="162" t="s">
         <v>250</v>
       </c>
-      <c r="W27" s="164" t="s">
+      <c r="W27" s="162" t="s">
         <v>249</v>
       </c>
-      <c r="X27" s="165" t="s">
+      <c r="X27" s="163" t="s">
         <v>248</v>
       </c>
-      <c r="Y27" s="166" t="s">
+      <c r="Y27" s="164" t="s">
         <v>247</v>
       </c>
-      <c r="Z27" s="167" t="s">
+      <c r="Z27" s="165" t="s">
         <v>246</v>
       </c>
-      <c r="AA27" s="163" t="s">
+      <c r="AA27" s="161" t="s">
         <v>245</v>
       </c>
-      <c r="AB27" s="168" t="s">
+      <c r="AB27" s="166" t="s">
         <v>244</v>
       </c>
-      <c r="AC27" s="168" t="s">
+      <c r="AC27" s="166" t="s">
+        <v>407</v>
+      </c>
+      <c r="AD27" s="166" t="s">
+        <v>242</v>
+      </c>
+      <c r="AE27" s="166" t="s">
+        <v>408</v>
+      </c>
+      <c r="AF27" s="166" t="s">
+        <v>241</v>
+      </c>
+      <c r="AG27" s="166" t="s">
+        <v>240</v>
+      </c>
+      <c r="AH27" s="166" t="s">
+        <v>243</v>
+      </c>
+      <c r="AI27" s="166" t="s">
+        <v>404</v>
+      </c>
+      <c r="AJ27" s="166" t="s">
+        <v>405</v>
+      </c>
+      <c r="AK27" s="166" t="s">
+        <v>406</v>
+      </c>
+      <c r="AL27" s="166" t="s">
+        <v>221</v>
+      </c>
+      <c r="AM27" s="166" t="s">
+        <v>239</v>
+      </c>
+      <c r="AN27" s="166" t="s">
+        <v>238</v>
+      </c>
+      <c r="AO27" s="166" t="s">
+        <v>237</v>
+      </c>
+      <c r="AP27" s="166" t="s">
+        <v>236</v>
+      </c>
+      <c r="AQ27" s="166" t="s">
+        <v>235</v>
+      </c>
+      <c r="AR27" s="166" t="s">
+        <v>234</v>
+      </c>
+      <c r="AS27" s="166" t="s">
+        <v>233</v>
+      </c>
+      <c r="AT27" s="166" t="s">
+        <v>232</v>
+      </c>
+      <c r="AU27" s="166" t="s">
+        <v>35</v>
+      </c>
+      <c r="AV27" s="166" t="s">
+        <v>231</v>
+      </c>
+      <c r="AW27" s="167" t="s">
+        <v>484</v>
+      </c>
+      <c r="AX27" s="166" t="s">
+        <v>230</v>
+      </c>
+      <c r="AY27" s="212" t="s">
+        <v>604</v>
+      </c>
+      <c r="AZ27" s="166" t="s">
+        <v>229</v>
+      </c>
+      <c r="BA27" s="166" t="s">
+        <v>228</v>
+      </c>
+      <c r="BB27" s="166" t="s">
+        <v>227</v>
+      </c>
+      <c r="BC27" s="166" t="s">
+        <v>226</v>
+      </c>
+      <c r="BD27" s="168" t="s">
+        <v>492</v>
+      </c>
+      <c r="BE27" s="168" t="s">
+        <v>493</v>
+      </c>
+      <c r="BF27" s="168" t="s">
+        <v>494</v>
+      </c>
+      <c r="BG27" s="169" t="s">
+        <v>222</v>
+      </c>
+      <c r="BH27" s="170" t="s">
+        <v>510</v>
+      </c>
+      <c r="BI27" s="171" t="s">
+        <v>495</v>
+      </c>
+      <c r="BJ27" s="172" t="s">
+        <v>497</v>
+      </c>
+      <c r="BK27" s="173" t="s">
+        <v>496</v>
+      </c>
+      <c r="BL27" s="166" t="s">
+        <v>223</v>
+      </c>
+      <c r="BM27" s="172" t="s">
+        <v>221</v>
+      </c>
+      <c r="BN27" s="166" t="s">
+        <v>220</v>
+      </c>
+      <c r="BO27" s="166" t="s">
+        <v>219</v>
+      </c>
+      <c r="BP27" s="174" t="s">
+        <v>218</v>
+      </c>
+      <c r="BQ27" s="174" t="s">
+        <v>499</v>
+      </c>
+      <c r="BR27" s="166" t="s">
+        <v>500</v>
+      </c>
+      <c r="BS27" s="166" t="s">
+        <v>501</v>
+      </c>
+      <c r="BT27" s="172" t="s">
+        <v>217</v>
+      </c>
+      <c r="BU27" s="172" t="s">
+        <v>520</v>
+      </c>
+      <c r="BV27" s="171" t="s">
+        <v>521</v>
+      </c>
+      <c r="BW27" s="173" t="s">
+        <v>216</v>
+      </c>
+      <c r="BX27" s="173" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY27" s="173" t="s">
+        <v>214</v>
+      </c>
+      <c r="BZ27" s="173" t="s">
+        <v>213</v>
+      </c>
+      <c r="CA27" s="173" t="s">
+        <v>212</v>
+      </c>
+      <c r="CB27" s="168" t="s">
+        <v>502</v>
+      </c>
+      <c r="CC27" s="169" t="s">
+        <v>222</v>
+      </c>
+      <c r="CD27" s="169" t="s">
+        <v>513</v>
+      </c>
+      <c r="CE27" s="172" t="s">
+        <v>221</v>
+      </c>
+      <c r="CF27" s="166" t="s">
+        <v>220</v>
+      </c>
+      <c r="CG27" s="166" t="s">
+        <v>514</v>
+      </c>
+      <c r="CH27" s="174" t="s">
+        <v>218</v>
+      </c>
+      <c r="CI27" s="174" t="s">
+        <v>499</v>
+      </c>
+      <c r="CJ27" s="166" t="s">
+        <v>500</v>
+      </c>
+      <c r="CK27" s="166" t="s">
+        <v>501</v>
+      </c>
+      <c r="CL27" s="172" t="s">
+        <v>217</v>
+      </c>
+      <c r="CM27" s="172" t="s">
+        <v>520</v>
+      </c>
+      <c r="CN27" s="171" t="s">
+        <v>521</v>
+      </c>
+      <c r="CO27" s="173" t="s">
+        <v>216</v>
+      </c>
+      <c r="CP27" s="173" t="s">
+        <v>215</v>
+      </c>
+      <c r="CQ27" s="173" t="s">
+        <v>214</v>
+      </c>
+      <c r="CR27" s="173" t="s">
+        <v>213</v>
+      </c>
+      <c r="CS27" s="173" t="s">
+        <v>212</v>
+      </c>
+      <c r="CT27" s="81" t="s">
+        <v>378</v>
+      </c>
+      <c r="CU27" s="81" t="s">
+        <v>377</v>
+      </c>
+      <c r="CV27" s="81" t="s">
+        <v>379</v>
+      </c>
+      <c r="CW27" s="175" t="s">
+        <v>384</v>
+      </c>
+      <c r="CX27" s="176" t="s">
+        <v>409</v>
+      </c>
+      <c r="CY27" s="176" t="s">
+        <v>410</v>
+      </c>
+      <c r="CZ27" s="176" t="s">
+        <v>411</v>
+      </c>
+      <c r="DA27" s="176" t="s">
+        <v>468</v>
+      </c>
+      <c r="DB27" s="176" t="s">
         <v>412</v>
       </c>
-      <c r="AD27" s="168" t="s">
-        <v>242</v>
-      </c>
-      <c r="AE27" s="168" t="s">
+      <c r="DC27" s="177" t="s">
         <v>413</v>
       </c>
-      <c r="AF27" s="168" t="s">
-        <v>241</v>
-      </c>
-      <c r="AG27" s="168" t="s">
-        <v>240</v>
-      </c>
-      <c r="AH27" s="168" t="s">
-        <v>243</v>
-      </c>
-      <c r="AI27" s="168" t="s">
-        <v>409</v>
-      </c>
-      <c r="AJ27" s="168" t="s">
-        <v>410</v>
-      </c>
-      <c r="AK27" s="168" t="s">
-        <v>411</v>
-      </c>
-      <c r="AL27" s="168" t="s">
-        <v>221</v>
-      </c>
-      <c r="AM27" s="168" t="s">
-        <v>239</v>
-      </c>
-      <c r="AN27" s="168" t="s">
-        <v>238</v>
-      </c>
-      <c r="AO27" s="168" t="s">
-        <v>237</v>
-      </c>
-      <c r="AP27" s="168" t="s">
-        <v>236</v>
-      </c>
-      <c r="AQ27" s="168" t="s">
-        <v>235</v>
-      </c>
-      <c r="AR27" s="168" t="s">
-        <v>234</v>
-      </c>
-      <c r="AS27" s="168" t="s">
-        <v>233</v>
-      </c>
-      <c r="AT27" s="168" t="s">
-        <v>232</v>
-      </c>
-      <c r="AU27" s="168" t="s">
-        <v>35</v>
-      </c>
-      <c r="AV27" s="168" t="s">
-        <v>231</v>
-      </c>
-      <c r="AW27" s="169" t="s">
-        <v>489</v>
-      </c>
-      <c r="AX27" s="168" t="s">
-        <v>230</v>
-      </c>
-      <c r="AY27" s="214" t="s">
-        <v>611</v>
-      </c>
-      <c r="AZ27" s="168" t="s">
-        <v>229</v>
-      </c>
-      <c r="BA27" s="168" t="s">
-        <v>228</v>
-      </c>
-      <c r="BB27" s="168" t="s">
-        <v>227</v>
-      </c>
-      <c r="BC27" s="168" t="s">
-        <v>226</v>
-      </c>
-      <c r="BD27" s="170" t="s">
-        <v>497</v>
-      </c>
-      <c r="BE27" s="170" t="s">
-        <v>498</v>
-      </c>
-      <c r="BF27" s="170" t="s">
-        <v>499</v>
-      </c>
-      <c r="BG27" s="171" t="s">
-        <v>222</v>
-      </c>
-      <c r="BH27" s="172" t="s">
+      <c r="DD27" s="177" t="s">
+        <v>534</v>
+      </c>
+      <c r="DE27" s="82"/>
+      <c r="DF27" s="178" t="s">
+        <v>526</v>
+      </c>
+      <c r="DG27" s="178" t="s">
+        <v>527</v>
+      </c>
+      <c r="DH27" s="179" t="s">
+        <v>550</v>
+      </c>
+      <c r="DI27" s="179" t="s">
+        <v>551</v>
+      </c>
+      <c r="DJ27" s="179" t="s">
+        <v>552</v>
+      </c>
+      <c r="DK27" s="180" t="s">
+        <v>538</v>
+      </c>
+      <c r="DL27" s="180" t="s">
+        <v>528</v>
+      </c>
+      <c r="DM27" s="180" t="s">
+        <v>578</v>
+      </c>
+      <c r="DN27" s="180" t="s">
+        <v>579</v>
+      </c>
+      <c r="DO27" s="154" t="s">
         <v>515</v>
       </c>
-      <c r="BI27" s="173" t="s">
-        <v>500</v>
-      </c>
-      <c r="BJ27" s="174" t="s">
-        <v>502</v>
-      </c>
-      <c r="BK27" s="175" t="s">
-        <v>501</v>
-      </c>
-      <c r="BL27" s="168" t="s">
-        <v>223</v>
-      </c>
-      <c r="BM27" s="174" t="s">
-        <v>221</v>
-      </c>
-      <c r="BN27" s="168" t="s">
-        <v>220</v>
-      </c>
-      <c r="BO27" s="168" t="s">
-        <v>219</v>
-      </c>
-      <c r="BP27" s="176" t="s">
-        <v>218</v>
-      </c>
-      <c r="BQ27" s="176" t="s">
-        <v>504</v>
-      </c>
-      <c r="BR27" s="168" t="s">
-        <v>505</v>
-      </c>
-      <c r="BS27" s="168" t="s">
-        <v>506</v>
-      </c>
-      <c r="BT27" s="174" t="s">
-        <v>217</v>
-      </c>
-      <c r="BU27" s="174" t="s">
-        <v>525</v>
-      </c>
-      <c r="BV27" s="173" t="s">
-        <v>526</v>
-      </c>
-      <c r="BW27" s="175" t="s">
-        <v>216</v>
-      </c>
-      <c r="BX27" s="175" t="s">
-        <v>215</v>
-      </c>
-      <c r="BY27" s="175" t="s">
-        <v>214</v>
-      </c>
-      <c r="BZ27" s="175" t="s">
-        <v>213</v>
-      </c>
-      <c r="CA27" s="175" t="s">
-        <v>212</v>
-      </c>
-      <c r="CB27" s="170" t="s">
-        <v>507</v>
-      </c>
-      <c r="CC27" s="171" t="s">
-        <v>222</v>
-      </c>
-      <c r="CD27" s="171" t="s">
-        <v>518</v>
-      </c>
-      <c r="CE27" s="174" t="s">
-        <v>221</v>
-      </c>
-      <c r="CF27" s="168" t="s">
-        <v>220</v>
-      </c>
-      <c r="CG27" s="168" t="s">
-        <v>519</v>
-      </c>
-      <c r="CH27" s="176" t="s">
-        <v>218</v>
-      </c>
-      <c r="CI27" s="176" t="s">
-        <v>504</v>
-      </c>
-      <c r="CJ27" s="168" t="s">
-        <v>505</v>
-      </c>
-      <c r="CK27" s="168" t="s">
-        <v>506</v>
-      </c>
-      <c r="CL27" s="174" t="s">
-        <v>217</v>
-      </c>
-      <c r="CM27" s="174" t="s">
-        <v>525</v>
-      </c>
-      <c r="CN27" s="173" t="s">
-        <v>526</v>
-      </c>
-      <c r="CO27" s="175" t="s">
-        <v>216</v>
-      </c>
-      <c r="CP27" s="175" t="s">
-        <v>215</v>
-      </c>
-      <c r="CQ27" s="175" t="s">
-        <v>214</v>
-      </c>
-      <c r="CR27" s="175" t="s">
-        <v>213</v>
-      </c>
-      <c r="CS27" s="175" t="s">
-        <v>212</v>
-      </c>
-      <c r="CT27" s="83" t="s">
-        <v>383</v>
-      </c>
-      <c r="CU27" s="83" t="s">
-        <v>382</v>
-      </c>
-      <c r="CV27" s="83" t="s">
-        <v>384</v>
-      </c>
-      <c r="CW27" s="177" t="s">
-        <v>389</v>
-      </c>
-      <c r="CX27" s="178" t="s">
-        <v>414</v>
-      </c>
-      <c r="CY27" s="178" t="s">
-        <v>415</v>
-      </c>
-      <c r="CZ27" s="178" t="s">
-        <v>416</v>
-      </c>
-      <c r="DA27" s="178" t="s">
-        <v>473</v>
-      </c>
-      <c r="DB27" s="178" t="s">
-        <v>417</v>
-      </c>
-      <c r="DC27" s="179" t="s">
-        <v>418</v>
-      </c>
-      <c r="DD27" s="179" t="s">
+      <c r="DP27" s="154" t="s">
+        <v>516</v>
+      </c>
+      <c r="DQ27" s="154" t="s">
+        <v>517</v>
+      </c>
+      <c r="DR27" s="178" t="s">
+        <v>529</v>
+      </c>
+      <c r="DS27" s="180" t="s">
+        <v>531</v>
+      </c>
+      <c r="DT27" s="181" t="s">
+        <v>532</v>
+      </c>
+      <c r="DU27" s="181" t="s">
+        <v>516</v>
+      </c>
+      <c r="DV27" s="181" t="s">
+        <v>517</v>
+      </c>
+      <c r="DW27" s="180" t="s">
+        <v>533</v>
+      </c>
+      <c r="DX27" s="157" t="s">
+        <v>535</v>
+      </c>
+      <c r="DY27" s="157" t="s">
+        <v>536</v>
+      </c>
+      <c r="DZ27" s="158" t="s">
+        <v>511</v>
+      </c>
+      <c r="EA27" s="182" t="s">
+        <v>537</v>
+      </c>
+      <c r="EB27" s="182" t="s">
         <v>539</v>
       </c>
-      <c r="DE27" s="84"/>
-      <c r="DF27" s="180" t="s">
-        <v>531</v>
-      </c>
-      <c r="DG27" s="180" t="s">
-        <v>532</v>
-      </c>
-      <c r="DH27" s="181" t="s">
+      <c r="EC27" s="182" t="s">
+        <v>540</v>
+      </c>
+      <c r="ED27" s="183" t="s">
+        <v>542</v>
+      </c>
+      <c r="EE27" s="184" t="s">
+        <v>543</v>
+      </c>
+      <c r="EF27" s="184" t="s">
+        <v>544</v>
+      </c>
+      <c r="EG27" s="184" t="s">
+        <v>517</v>
+      </c>
+      <c r="EH27" s="184" t="s">
+        <v>545</v>
+      </c>
+      <c r="EI27" s="184" t="s">
+        <v>546</v>
+      </c>
+      <c r="EJ27" s="184" t="s">
+        <v>585</v>
+      </c>
+      <c r="EK27" s="184" t="s">
+        <v>586</v>
+      </c>
+      <c r="EL27" s="185" t="s">
+        <v>583</v>
+      </c>
+      <c r="EM27" s="186" t="s">
+        <v>547</v>
+      </c>
+      <c r="EN27" s="187" t="s">
+        <v>541</v>
+      </c>
+      <c r="EO27" s="188" t="s">
+        <v>553</v>
+      </c>
+      <c r="EP27" s="189" t="s">
+        <v>511</v>
+      </c>
+      <c r="EQ27" s="186" t="s">
+        <v>548</v>
+      </c>
+      <c r="ER27" s="186" t="s">
+        <v>549</v>
+      </c>
+      <c r="ES27" s="190" t="s">
         <v>555</v>
       </c>
-      <c r="DI27" s="181" t="s">
+      <c r="ET27" s="190" t="s">
         <v>556</v>
       </c>
-      <c r="DJ27" s="181" t="s">
+      <c r="EU27" s="190" t="s">
+        <v>554</v>
+      </c>
+      <c r="EV27" s="191" t="s">
+        <v>511</v>
+      </c>
+      <c r="EW27" s="190" t="s">
         <v>557</v>
       </c>
-      <c r="DK27" s="182" t="s">
-        <v>543</v>
-      </c>
-      <c r="DL27" s="182" t="s">
-        <v>533</v>
-      </c>
-      <c r="DM27" s="182" t="s">
-        <v>583</v>
-      </c>
-      <c r="DN27" s="182" t="s">
+      <c r="EX27" s="190" t="s">
+        <v>558</v>
+      </c>
+      <c r="EY27" s="190" t="s">
+        <v>559</v>
+      </c>
+      <c r="EZ27" s="191" t="s">
+        <v>511</v>
+      </c>
+      <c r="FA27" s="191" t="s">
+        <v>572</v>
+      </c>
+      <c r="FB27" s="191"/>
+      <c r="FC27" s="191"/>
+      <c r="FD27" s="191" t="s">
+        <v>511</v>
+      </c>
+      <c r="FE27" s="191" t="s">
+        <v>577</v>
+      </c>
+      <c r="FF27" s="192" t="s">
+        <v>580</v>
+      </c>
+      <c r="FG27" s="192" t="s">
+        <v>581</v>
+      </c>
+      <c r="FH27" s="192" t="s">
+        <v>582</v>
+      </c>
+      <c r="FI27" s="192" t="s">
         <v>584</v>
       </c>
-      <c r="DO27" s="156" t="s">
-        <v>520</v>
-      </c>
-      <c r="DP27" s="156" t="s">
-        <v>521</v>
-      </c>
-      <c r="DQ27" s="156" t="s">
-        <v>522</v>
-      </c>
-      <c r="DR27" s="180" t="s">
-        <v>534</v>
-      </c>
-      <c r="DS27" s="182" t="s">
-        <v>536</v>
-      </c>
-      <c r="DT27" s="183" t="s">
-        <v>537</v>
-      </c>
-      <c r="DU27" s="183" t="s">
-        <v>521</v>
-      </c>
-      <c r="DV27" s="183" t="s">
-        <v>522</v>
-      </c>
-      <c r="DW27" s="182" t="s">
-        <v>538</v>
-      </c>
-      <c r="DX27" s="159" t="s">
-        <v>540</v>
-      </c>
-      <c r="DY27" s="159" t="s">
-        <v>541</v>
-      </c>
-      <c r="DZ27" s="160" t="s">
-        <v>516</v>
-      </c>
-      <c r="EA27" s="184" t="s">
-        <v>542</v>
-      </c>
-      <c r="EB27" s="184" t="s">
-        <v>544</v>
-      </c>
-      <c r="EC27" s="184" t="s">
-        <v>545</v>
-      </c>
-      <c r="ED27" s="185" t="s">
-        <v>547</v>
-      </c>
-      <c r="EE27" s="186" t="s">
-        <v>548</v>
-      </c>
-      <c r="EF27" s="186" t="s">
-        <v>549</v>
-      </c>
-      <c r="EG27" s="186" t="s">
-        <v>522</v>
-      </c>
-      <c r="EH27" s="186" t="s">
-        <v>550</v>
-      </c>
-      <c r="EI27" s="186" t="s">
-        <v>551</v>
-      </c>
-      <c r="EJ27" s="186" t="s">
-        <v>590</v>
-      </c>
-      <c r="EK27" s="186" t="s">
-        <v>591</v>
-      </c>
-      <c r="EL27" s="187" t="s">
+      <c r="FJ27" s="192" t="s">
+        <v>511</v>
+      </c>
+      <c r="FK27" s="191" t="s">
+        <v>573</v>
+      </c>
+      <c r="FL27" s="191" t="s">
+        <v>574</v>
+      </c>
+      <c r="FM27" s="191" t="s">
+        <v>575</v>
+      </c>
+      <c r="FN27" s="191" t="s">
+        <v>576</v>
+      </c>
+      <c r="FO27" s="191" t="s">
+        <v>511</v>
+      </c>
+      <c r="FP27" s="193" t="s">
+        <v>427</v>
+      </c>
+      <c r="FQ27" s="267" t="s">
         <v>588</v>
       </c>
-      <c r="EM27" s="188" t="s">
-        <v>552</v>
-      </c>
-      <c r="EN27" s="189" t="s">
-        <v>546</v>
-      </c>
-      <c r="EO27" s="190" t="s">
-        <v>558</v>
-      </c>
-      <c r="EP27" s="191" t="s">
-        <v>516</v>
-      </c>
-      <c r="EQ27" s="188" t="s">
-        <v>553</v>
-      </c>
-      <c r="ER27" s="188" t="s">
-        <v>554</v>
-      </c>
-      <c r="ES27" s="192" t="s">
-        <v>560</v>
-      </c>
-      <c r="ET27" s="192" t="s">
-        <v>561</v>
-      </c>
-      <c r="EU27" s="192" t="s">
-        <v>559</v>
-      </c>
-      <c r="EV27" s="193" t="s">
-        <v>516</v>
-      </c>
-      <c r="EW27" s="192" t="s">
-        <v>562</v>
-      </c>
-      <c r="EX27" s="192" t="s">
-        <v>563</v>
-      </c>
-      <c r="EY27" s="192" t="s">
-        <v>564</v>
-      </c>
-      <c r="EZ27" s="193" t="s">
-        <v>516</v>
-      </c>
-      <c r="FA27" s="193" t="s">
-        <v>577</v>
-      </c>
-      <c r="FB27" s="193"/>
-      <c r="FC27" s="193"/>
-      <c r="FD27" s="193" t="s">
-        <v>516</v>
-      </c>
-      <c r="FE27" s="193" t="s">
-        <v>582</v>
-      </c>
-      <c r="FF27" s="194" t="s">
-        <v>585</v>
-      </c>
-      <c r="FG27" s="194" t="s">
-        <v>586</v>
-      </c>
-      <c r="FH27" s="194" t="s">
-        <v>587</v>
-      </c>
-      <c r="FI27" s="194" t="s">
-        <v>589</v>
-      </c>
-      <c r="FJ27" s="194" t="s">
-        <v>516</v>
-      </c>
-      <c r="FK27" s="193" t="s">
-        <v>578</v>
-      </c>
-      <c r="FL27" s="193" t="s">
-        <v>579</v>
-      </c>
-      <c r="FM27" s="193" t="s">
-        <v>580</v>
-      </c>
-      <c r="FN27" s="193" t="s">
-        <v>581</v>
-      </c>
-      <c r="FO27" s="193" t="s">
-        <v>516</v>
-      </c>
-      <c r="FP27" s="195" t="s">
-        <v>432</v>
-      </c>
-      <c r="FQ27" s="288" t="s">
-        <v>593</v>
-      </c>
-      <c r="FR27" s="288"/>
-      <c r="FU27" s="115">
+      <c r="FR27" s="267"/>
+      <c r="FU27" s="113">
         <f>35*$AA$5</f>
         <v>35</v>
       </c>
-      <c r="FV27" s="112">
+      <c r="FV27" s="110">
         <f>$AA$6</f>
         <v>1</v>
       </c>
-      <c r="FW27" s="109"/>
-      <c r="FX27" s="109"/>
-      <c r="FY27" s="114"/>
-      <c r="GF27" s="102"/>
-      <c r="GG27" s="102"/>
-      <c r="GH27" s="104"/>
-      <c r="GI27" s="105"/>
-      <c r="GJ27" s="117"/>
-      <c r="GK27" s="132"/>
-      <c r="GL27" s="104"/>
-      <c r="GM27" s="105"/>
-      <c r="GN27" s="106"/>
-      <c r="GO27" s="106"/>
-      <c r="GP27" s="106"/>
-      <c r="GQ27" s="106"/>
-      <c r="GR27" s="106"/>
-      <c r="GS27" s="106"/>
-      <c r="HM27" s="285" t="s">
-        <v>421</v>
-      </c>
-      <c r="HN27" s="285"/>
-      <c r="HO27" s="285"/>
-      <c r="HP27" s="285"/>
-      <c r="HQ27" s="285"/>
-      <c r="HR27" s="285"/>
-      <c r="HS27" s="285"/>
-      <c r="HT27" s="285"/>
-      <c r="HU27" s="263" t="s">
+      <c r="FW27" s="107"/>
+      <c r="FX27" s="107"/>
+      <c r="FY27" s="112"/>
+      <c r="GF27" s="100"/>
+      <c r="GG27" s="100"/>
+      <c r="GH27" s="102"/>
+      <c r="GI27" s="103"/>
+      <c r="GJ27" s="115"/>
+      <c r="GK27" s="130"/>
+      <c r="GL27" s="102"/>
+      <c r="GM27" s="103"/>
+      <c r="GN27" s="104"/>
+      <c r="GO27" s="104"/>
+      <c r="GP27" s="104"/>
+      <c r="GQ27" s="104"/>
+      <c r="GR27" s="104"/>
+      <c r="GS27" s="104"/>
+      <c r="HM27" s="264" t="s">
+        <v>416</v>
+      </c>
+      <c r="HN27" s="264"/>
+      <c r="HO27" s="264"/>
+      <c r="HP27" s="264"/>
+      <c r="HQ27" s="264"/>
+      <c r="HR27" s="264"/>
+      <c r="HS27" s="264"/>
+      <c r="HT27" s="264"/>
+      <c r="HU27" s="242" t="s">
         <v>211</v>
       </c>
-      <c r="HV27" s="263"/>
-      <c r="HW27" s="263"/>
-      <c r="HX27" s="263"/>
-      <c r="HY27" s="263"/>
-      <c r="HZ27" s="263"/>
-      <c r="IA27" s="263"/>
-      <c r="IB27" s="263"/>
-      <c r="IC27" s="263"/>
-      <c r="ID27" s="263"/>
-      <c r="IE27" s="281" t="s">
+      <c r="HV27" s="242"/>
+      <c r="HW27" s="242"/>
+      <c r="HX27" s="242"/>
+      <c r="HY27" s="242"/>
+      <c r="HZ27" s="242"/>
+      <c r="IA27" s="242"/>
+      <c r="IB27" s="242"/>
+      <c r="IC27" s="242"/>
+      <c r="ID27" s="242"/>
+      <c r="IE27" s="260" t="s">
         <v>210</v>
       </c>
-      <c r="IF27" s="281"/>
-      <c r="IG27" s="281"/>
-      <c r="IH27" s="281"/>
-      <c r="II27" s="281"/>
-      <c r="IJ27" s="281"/>
-      <c r="IK27" s="281"/>
-      <c r="IL27" s="281"/>
-      <c r="IM27" s="281"/>
-      <c r="IN27" s="281"/>
-      <c r="IO27" s="216" t="s">
+      <c r="IF27" s="260"/>
+      <c r="IG27" s="260"/>
+      <c r="IH27" s="260"/>
+      <c r="II27" s="260"/>
+      <c r="IJ27" s="260"/>
+      <c r="IK27" s="260"/>
+      <c r="IL27" s="260"/>
+      <c r="IM27" s="260"/>
+      <c r="IN27" s="260"/>
+      <c r="IO27" s="214" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="28" spans="1:263" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="210" t="s">
-        <v>602</v>
+      <c r="IP27" s="214"/>
+    </row>
+    <row r="28" spans="1:264" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="208" t="s">
+        <v>629</v>
       </c>
       <c r="D28" s="57">
         <f>IF(COUNT($CU$28:CU28)=MATCH(CT28,$CT$28:CT28,0),CT28,"")</f>
         <v>-1</v>
       </c>
-      <c r="E28" s="143" t="str">
+      <c r="E28" s="141" t="str">
         <f>IF(D28="","","АВДТ")</f>
         <v>АВДТ</v>
       </c>
-      <c r="F28" s="143">
+      <c r="F28" s="141">
         <f>IF(D28="","",1)</f>
         <v>1</v>
       </c>
-      <c r="G28" s="143" t="str">
+      <c r="G28" s="141" t="str">
         <f>IF(D28="","","АВ")</f>
         <v>АВ</v>
       </c>
@@ -15894,7 +16237,7 @@
         <f ca="1">IF(G28="","",CQ28&amp;", "&amp;CR28&amp;", "&amp;CS28)</f>
         <v>#N/A</v>
       </c>
-      <c r="J28" s="99" t="e">
+      <c r="J28" s="97" t="e">
         <f ca="1">AY28</f>
         <v>#N/A</v>
       </c>
@@ -15902,15 +16245,15 @@
         <f ca="1">IF(D28="","",AC28&amp;"кВт; "&amp;Q28&amp;"В; "&amp;AD28&amp;"A; "&amp;AE28&amp;"; dU="&amp;AH28)</f>
         <v>#N/A</v>
       </c>
-      <c r="L28" s="196" t="e">
+      <c r="L28" s="194" t="e">
         <f>IF(CX28=0,IF($L$23=1,AN28,P28),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="M28" s="196" t="e">
+      <c r="M28" s="194" t="e">
         <f>IF(CX28=1,IF($L$23=1,AN28,P28),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="N28" s="196" t="e">
+      <c r="N28" s="194" t="e">
         <f>IF(CX28=2,IF($L$23=1,AN28,P28),"")</f>
         <v>#N/A</v>
       </c>
@@ -15951,7 +16294,7 @@
         <v>0</v>
       </c>
       <c r="X28" s="49">
-        <f>'&lt;zalldev&gt;EXPORT'!BA11</f>
+        <f>'&lt;zalldev&gt;EXPORT'!BD11</f>
         <v>1</v>
       </c>
       <c r="Y28" s="49">
@@ -15991,15 +16334,15 @@
         <f ca="1">IF(D28="","",ROUNDUP((1/1000)*(100/Q28)*IF(Q28&lt;380,2,SQRT(3))*AD28*AP28*(INDEX(INDIRECT("BDКаб!"&amp;INDEX(BDКаб!$C$4:$AH$4,1,MATCH(AQ28&amp;AR28&amp;AS28&amp;"R",BDКаб!$C$3:$AH$3,0))),MATCH(AU28,BDКаб!$B$5:$B$20,0))*AE28 + INDEX(INDIRECT("BDКаб!"&amp;INDEX(BDКаб!$C$4:$AH$4,1,MATCH(AQ28&amp;AR28&amp;AS28&amp;"X",BDКаб!$C$3:$AH$3,0))),MATCH(AU28,BDКаб!$B$5:$B$20,0))*SQRT(1-AE28*AE28)),2))</f>
         <v>#N/A</v>
       </c>
-      <c r="AI28" s="98" t="e">
+      <c r="AI28" s="96" t="e">
         <f>IF(CX28=0,IF(DB28=0,S28,S28+SUMIF(CY28:$CY$700000,P28,AJ28:$AJ$700000)),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="AJ28" s="98" t="e">
+      <c r="AJ28" s="96" t="e">
         <f>IF(CX28=1,IF(DB28=0,S28,S28+SUMIF(CY28:$CY$700000,P28,AK28:$AK$700000)),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="AK28" s="98" t="e">
+      <c r="AK28" s="96" t="e">
         <f>IF(CX28=2,S28,"")</f>
         <v>#N/A</v>
       </c>
@@ -16019,7 +16362,7 @@
         <f>IF(AN28="","",AV28&amp;"-"&amp;AT28&amp;"х"&amp;AU28&amp;"мм²")</f>
         <v>#N/A</v>
       </c>
-      <c r="AP28" s="89" t="e">
+      <c r="AP28" s="87" t="e">
         <f>IF(AN28="","",INDEX('&lt;zallcab&gt;CALC'!$X$7:$X$700000,MATCH(AN28,'&lt;zallcab&gt;CALC'!$D$7:$D$700000,0)))</f>
         <v>#N/A</v>
       </c>
@@ -16069,352 +16412,352 @@
         <f ca="1">IF(AN28="","",INDEX(BDКаб!$B$5:$B$20,MATCH(IF(AN28="","",IF(E28="",U28,AD28)),INDIRECT("BDКаб!"&amp;INDEX(BDКаб!$B$4:$AH$4,MATCH(AQ28&amp;AR28&amp;AS28&amp;"I",BDКаб!$B$3:$AH$3,0))),1)+1))</f>
         <v>#N/A</v>
       </c>
-      <c r="BD28" s="144" t="str">
+      <c r="BD28" s="142" t="str">
         <f>IF(E28="","",E28)</f>
         <v>АВДТ</v>
       </c>
-      <c r="BE28" s="144">
+      <c r="BE28" s="142">
         <f>IF(F28="","",F28)</f>
         <v>1</v>
       </c>
-      <c r="BF28" s="144" t="e">
+      <c r="BF28" s="142" t="e">
         <f ca="1">IF(AD28="","",AD28)</f>
         <v>#N/A</v>
       </c>
-      <c r="BG28" s="144" t="e">
+      <c r="BG28" s="142" t="e">
         <f ca="1">IF(BD28="","",IF(Q28&lt;380,1,3))</f>
         <v>#N/A</v>
       </c>
-      <c r="BH28" s="145">
+      <c r="BH28" s="143">
         <f>IF(BD28="","",IF(F28="",1,IF(MATCH(F28,$F$28:F28,0)=MATCH(F28,$F$28:F28,1),1,"")))</f>
         <v>1</v>
       </c>
-      <c r="BI28" s="145">
+      <c r="BI28" s="143">
         <f ca="1">IF(BH28=1,IF(BD28="","",IF(BE28="",BG28,IF(COUNTIFS($BE$28:$BE$700000,BE28,$BG$28:$BG$700000,3)&gt;0,3,1))),"")</f>
         <v>1</v>
       </c>
-      <c r="BJ28" s="146"/>
-      <c r="BK28" s="147">
+      <c r="BJ28" s="144"/>
+      <c r="BK28" s="145">
         <f ca="1">IF(BH28=1,IF(BJ28="",BI28,BJ28),"")</f>
         <v>1</v>
       </c>
-      <c r="BL28" s="148" t="e">
+      <c r="BL28" s="146" t="e">
         <f ca="1">IF(BH28=1,IF(BD28="","",IF(BE28="",BF28,SUMIFS($BF$28:$BF$500004,$BE$28:$BE$500004,BE28))),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="BM28" s="146">
+      <c r="BM28" s="144">
         <f>IF(BH28=1,IF(BD28="","",1.3),"")</f>
         <v>1.3</v>
       </c>
-      <c r="BN28" s="148" t="e">
+      <c r="BN28" s="146" t="e">
         <f ca="1">IF(BH28=1,IF(BD28="","",IF(BM28="",BL28*1.3,BM28*BL28)),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="BO28" s="148" t="e">
+      <c r="BO28" s="146" t="e">
         <f ca="1">IF(BH28=1,IF(BD28="","",INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(BD28&amp;"I",BD!$K$4:$CB$4,0))),MATCH(BN28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(BD28&amp;"I",BD!$K$4:$CB$4,0))),-1))),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="BP28" s="146">
+      <c r="BP28" s="144">
         <f>IF(BH28=1,IF(BD28="","",10),"")</f>
         <v>10</v>
       </c>
-      <c r="BQ28" s="146"/>
-      <c r="BR28" s="148" t="e">
+      <c r="BQ28" s="144"/>
+      <c r="BR28" s="146" t="e">
         <f ca="1">IF(BD28="","",IF(BQ28="",IF(BO28&gt;=BP28,BO28,BP28),BQ28))</f>
         <v>#N/A</v>
       </c>
-      <c r="BS28" s="148"/>
-      <c r="BT28" s="146" t="str">
+      <c r="BS28" s="146"/>
+      <c r="BT28" s="144" t="str">
         <f>IF(BH28="","","C")</f>
         <v>C</v>
       </c>
-      <c r="BU28" s="146" t="str">
+      <c r="BU28" s="144" t="str">
         <f>IF(BH28="","",INDEX(BD!$D$57:$D$61,MATCH($BD28,BD!$C$57:$C$61,0)))</f>
         <v>N</v>
       </c>
-      <c r="BV28" s="145">
+      <c r="BV28" s="143">
         <f ca="1">IF(BH28=1,BK28+IF(BU28="N",1,0),"")</f>
         <v>2</v>
       </c>
-      <c r="BW28" s="147" t="str">
+      <c r="BW28" s="145" t="str">
         <f ca="1">IF(BH28=1,IF(BU28="N",BK28&amp;"P+N",BK28&amp;"P"),"")</f>
         <v>1P+N</v>
       </c>
-      <c r="BX28" s="147" t="str">
+      <c r="BX28" s="145" t="str">
         <f>IF(BH28="","",IF(BD28="АВДТ","30мА",IF(BD28="УЗО","30мА","")))</f>
         <v>30мА</v>
       </c>
-      <c r="BY28" s="147" t="e">
+      <c r="BY28" s="145" t="e">
         <f ca="1">IF(BH28="","",INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"О",BD!$K$4:$CB$4,0))),MATCH(BO28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"I",BD!$K$4:$CB$4,0))),0))&amp;D28)</f>
         <v>#N/A</v>
       </c>
-      <c r="BZ28" s="151" t="e">
+      <c r="BZ28" s="149" t="e">
         <f ca="1">IF(BH28="","",INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"М",BD!$K$4:$CB$4,0))),MATCH(BO28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CA$5,1,MATCH(E28&amp;"I",BD!$K$4:$CB$4,0))),0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="CA28" s="150" t="e">
+      <c r="CA28" s="148" t="e">
         <f ca="1">IF(BH28="","",BW28&amp;","&amp;BR28&amp;"А,"&amp;BT28&amp;IF(BX28="","",","&amp;BX28))</f>
         <v>#N/A</v>
       </c>
-      <c r="CB28" s="197" t="str">
+      <c r="CB28" s="195" t="str">
         <f>IF(G28=0,"",G28)</f>
         <v>АВ</v>
       </c>
-      <c r="CC28" s="144" t="e">
+      <c r="CC28" s="142" t="e">
         <f ca="1">IF(CB28="","",IF(Q28&lt;380,1,3))</f>
         <v>#N/A</v>
       </c>
-      <c r="CD28" s="144" t="e">
+      <c r="CD28" s="142" t="e">
         <f ca="1">IF(CB28="","",AD28)</f>
         <v>#N/A</v>
       </c>
-      <c r="CE28" s="146">
+      <c r="CE28" s="144">
         <f>IF(CB28="","",1.3)</f>
         <v>1.3</v>
       </c>
-      <c r="CF28" s="148" t="e">
+      <c r="CF28" s="146" t="e">
         <f ca="1">IF(CB28="","",CD28*CE28)</f>
         <v>#N/A</v>
       </c>
-      <c r="CG28" s="148" t="e">
+      <c r="CG28" s="146" t="e">
         <f ca="1">IF(CB28="","",INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(CB28&amp;"I",BD!$K$4:$CE$4,0))),MATCH(CF28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(CB28&amp;"I",BD!$K$4:$CE$4,0))),-1)))</f>
         <v>#N/A</v>
       </c>
-      <c r="CH28" s="146">
+      <c r="CH28" s="144">
         <f>IF(CB28="","",10)</f>
         <v>10</v>
       </c>
-      <c r="CI28" s="146"/>
-      <c r="CJ28" s="148" t="e">
+      <c r="CI28" s="144"/>
+      <c r="CJ28" s="146" t="e">
         <f ca="1">IF(CB28="","",IF(CI28="",IF(CG28&gt;=CH28,CG28,CH28),CI28))</f>
         <v>#N/A</v>
       </c>
-      <c r="CK28" s="148"/>
-      <c r="CL28" s="146" t="str">
+      <c r="CK28" s="146"/>
+      <c r="CL28" s="144" t="str">
         <f>IF(CB28="","","C")</f>
         <v>C</v>
       </c>
-      <c r="CM28" s="146">
+      <c r="CM28" s="144">
         <f>IF(CB28="","",INDEX(BD!$D$57:$D$61,MATCH($CB28,BD!$C$57:$C$61,0)))</f>
         <v>0</v>
       </c>
-      <c r="CN28" s="145" t="e">
+      <c r="CN28" s="143" t="e">
         <f ca="1">IF(CB28="","",CC28+IF(CM28="N",1,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="CO28" s="147" t="e">
+      <c r="CO28" s="145" t="e">
         <f ca="1">IF(CB28="","",IF(CM28="N",CC28&amp;"P+N",CC28&amp;"P"))</f>
         <v>#N/A</v>
       </c>
-      <c r="CP28" s="147" t="str">
+      <c r="CP28" s="145" t="str">
         <f>IF(CB28="","",IF(CB28="АВДТ","30мА",IF(CB28="УЗО","30мА","")))</f>
         <v/>
       </c>
-      <c r="CQ28" s="147" t="e">
+      <c r="CQ28" s="145" t="e">
         <f ca="1">IF(CB28="","",INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"О",BD!$K$4:$CE$4,0))),MATCH(CG28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"I",BD!$K$4:$CE$4,0))),0))&amp;D28)</f>
         <v>#N/A</v>
       </c>
-      <c r="CR28" s="151" t="e">
+      <c r="CR28" s="149" t="e">
         <f ca="1">IF(CB28="","",INDEX(INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"М",BD!$K$4:$CE$4,0))),MATCH(CG28,INDIRECT("BD!"&amp;INDEX(BD!$K$5:$CD$5,1,MATCH(G28&amp;"I",BD!$K$4:$CE$4,0))),0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="CS28" s="150" t="e">
+      <c r="CS28" s="148" t="e">
         <f ca="1">IF(CB28="","",CO28&amp;","&amp;CJ28&amp;"А,"&amp;CL28&amp;IF(CP28="","",","&amp;CP28))</f>
         <v>#N/A</v>
       </c>
-      <c r="CT28" s="198">
-        <f>'&lt;zalldev&gt;EXPORT'!AX11</f>
+      <c r="CT28" s="196">
+        <f>'&lt;zalldev&gt;EXPORT'!BA11</f>
         <v>-1</v>
       </c>
-      <c r="CU28" s="198">
+      <c r="CU28" s="196">
         <f>COUNT($CT$28:CT28)</f>
         <v>1</v>
       </c>
-      <c r="CV28" s="198" t="e">
+      <c r="CV28" s="196" t="e">
         <f ca="1">INDIRECT("'"&amp;P28&amp;"'!"&amp;"X14")</f>
         <v>#REF!</v>
       </c>
-      <c r="CW28" s="198" t="str">
-        <f>'&lt;zalldev&gt;EXPORT'!AY11</f>
+      <c r="CW28" s="196" t="str">
+        <f>'&lt;zalldev&gt;EXPORT'!BB11</f>
         <v>-1</v>
       </c>
-      <c r="CX28" s="199" t="e">
-        <f>'&lt;zalldev&gt;EXPORT'!BG11-$U$16-1</f>
+      <c r="CX28" s="197" t="e">
+        <f>'&lt;zalldev&gt;EXPORT'!BJ11-$U$16-1</f>
         <v>#N/A</v>
       </c>
-      <c r="CY28" s="199">
+      <c r="CY28" s="197">
         <f>'&lt;zalldev&gt;EXPORT'!J11</f>
         <v>0</v>
       </c>
-      <c r="CZ28" s="199">
+      <c r="CZ28" s="197">
         <f>'&lt;zalldev&gt;EXPORT'!M11*1</f>
         <v>0</v>
       </c>
-      <c r="DA28" s="199" t="str">
+      <c r="DA28" s="197" t="str">
         <f>CY28&amp;"."&amp;CZ28</f>
         <v>0.0</v>
       </c>
-      <c r="DB28" s="199">
-        <f>'&lt;zalldev&gt;EXPORT'!BF11*1</f>
-        <v>0</v>
-      </c>
-      <c r="DC28" s="200">
+      <c r="DB28" s="197">
+        <f>'&lt;zalldev&gt;EXPORT'!BI11*1</f>
+        <v>0</v>
+      </c>
+      <c r="DC28" s="198">
         <f>IF(COUNT($CT$28:CT28)=1,1,IF(INDEX($CT$28:CT28,COUNT($CT$28:CT28)-1)=INDEX($CT$28:CT28,COUNT($CT$28:CT28)),0,COUNT($CT$28:CT28)))*1</f>
         <v>1</v>
       </c>
-      <c r="DD28" s="200">
+      <c r="DD28" s="198">
         <f>IF(DB28&gt;0,IF(CX28=0,SUMIFS(CW28:$CW$700000,CT28:$CT$700000,CT28,CX28:$CX$700000,1),0),0)*1</f>
         <v>0</v>
       </c>
-      <c r="DE28" s="201">
+      <c r="DE28" s="199">
         <f>IF('&lt;zalldev&gt;EXPORT'!W11=0,'&lt;zalldev&gt;EXPORT'!W11,1)</f>
         <v>0</v>
       </c>
-      <c r="DF28" s="202">
+      <c r="DF28" s="200">
         <f>IF(SUMIF($CT$28:$CT$700000,CT28,$DB$28:$DB$700000)&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="DG28" s="202">
+      <c r="DG28" s="200">
         <f>IF($H$5=CY28,1,0)</f>
         <v>1</v>
       </c>
-      <c r="DH28" s="203" t="e">
+      <c r="DH28" s="201" t="e">
         <f>IF(CX28=0,IF(DF28=0,0,DA28),IF(CX28=1,INDEX($DH$28:DH28,CU28-1),IF(CX28=2,INDEX($DH$28:DH28,CU28-1),0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="DI28" s="203">
+      <c r="DI28" s="201">
         <f>IF(DF28=1,MATCH(DH28,$DH$28:DH28,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DJ28" s="203">
+      <c r="DJ28" s="201">
         <f>IF(COUNTIF(DA28:$DA$699946,DH28)&gt;0,IF(DI28=CU28,0,1),0)</f>
         <v>0</v>
       </c>
-      <c r="DK28" s="202" t="e">
+      <c r="DK28" s="200" t="e">
         <f>IF(CX28=0,IF(DB28&gt;0,1,0),0)</f>
         <v>#N/A</v>
       </c>
-      <c r="DL28" s="202">
+      <c r="DL28" s="200">
         <f>IF(SUMIF($DO$28:$DO$700000,P28,$DS$28:$DS$700000)&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="DM28" s="204" t="e">
+      <c r="DM28" s="202" t="e">
         <f>IF(DH28=0,0,IF(SUMIF($DH$28:$DH$700000,DH28,$DL$28:$DL$700000)&gt;0,1,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="DN28" s="204" t="e">
+      <c r="DN28" s="202" t="e">
         <f>IF(DH28=0,0,IF(SUMIF($EE$28:$EE$700000,EE28,$DS$28:$DS$700000)&gt;0,1,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="DO28" s="157" t="e">
+      <c r="DO28" s="155" t="e">
         <f>IF(CX28=1,CY28,IF(CX28=2,INDEX($DO$28:DO28,CU28-1),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="DP28" s="157" t="e">
+      <c r="DP28" s="155" t="e">
         <f>IF(CX28=1,MATCH(DO28,$DO$28:DO28,0),IF(CX28=2,INDEX($DP$28:DP28,CU28-1),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="DQ28" s="157">
+      <c r="DQ28" s="155">
         <f>COUNTIF($DO$28:$DO$700000,DO28)</f>
         <v>1</v>
       </c>
-      <c r="DR28" s="202" t="e">
+      <c r="DR28" s="200" t="e">
         <f>IF(DO28=0,0,IF(CU28&gt;=DP28,IF(CU28&lt;=DP28+DQ28,1,0),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="DS28" s="202">
+      <c r="DS28" s="200">
         <f>IF(DB28&gt;0,IF(CX28=1,1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="DT28" s="157" t="e">
+      <c r="DT28" s="155" t="e">
         <f>IF(CX28=2,CY28,IF(CX28=2,INDEX($DT$28:DT28,CU28-1),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="DU28" s="157" t="e">
+      <c r="DU28" s="155" t="e">
         <f>IF(CX28=2,MATCH(DT28,$DT$28:DT28,0),IF(CX28=2,INDEX($DU$28:DU28,CU28-1),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="DV28" s="157">
+      <c r="DV28" s="155">
         <f>COUNTIF($DT$28:$DT$700000,DT28)</f>
         <v>1</v>
       </c>
-      <c r="DW28" s="202" t="e">
+      <c r="DW28" s="200" t="e">
         <f>IF(DT28=0,0,IF(CU28&gt;=DU28,IF(CU28&lt;=DU28+DV28,1,0),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="DX28" s="161">
+      <c r="DX28" s="159">
         <f>IF(MATCH(CT28,$CT$28:CT28,0)=COUNT($CT$28:CT28),COUNTIFS(F28:$F$120004,F28),0)*1</f>
         <v>1</v>
       </c>
-      <c r="DY28" s="161">
+      <c r="DY28" s="159">
         <f>IF(INDEX($DX$28:DX28,MATCH(CT28,$CT$28:CT28,0))&gt;1,IF(DX28=0,2,1),IF(DX28=1,1,0))*1</f>
         <v>1</v>
       </c>
-      <c r="DZ28" s="162" t="e">
+      <c r="DZ28" s="160" t="e">
         <f ca="1">IF(H28&lt;&gt;"",0,IF(DX28=0,IF(DY28=0,3,DY28),DY28))</f>
         <v>#N/A</v>
       </c>
-      <c r="EA28" s="205" t="e">
+      <c r="EA28" s="203" t="e">
         <f t="shared" ref="EA28" ca="1" si="5">IF(DZ28=0,1,IF(DZ28=1,1,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="EB28" s="205" t="e">
+      <c r="EB28" s="203" t="e">
         <f>IF(SUM(EC28,EN28)&gt;0,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="EC28" s="205" t="e">
+      <c r="EC28" s="203" t="e">
         <f>INDEX($DK$28:DK28,CU28-1)</f>
         <v>#N/A</v>
       </c>
-      <c r="ED28" s="205">
+      <c r="ED28" s="203">
         <f>IF(INDEX($DL$28:DL28,CU28-1)&gt;0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="EE28" s="206" t="e">
+      <c r="EE28" s="204" t="e">
         <f>IF(DO28=0,0,IF(INDEX($DO$28:DO28,CU28-1)=0,DA28,IF(DO28=INDEX($DO$28:DO28,CU28-1),IF(DO28=CY28,DA28,INDEX($EE$28:EE28,CU28-1)),0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="EF28" s="206" t="e">
+      <c r="EF28" s="204" t="e">
         <f>IF(EE28=0,0,MATCH(EE28,$DA$28:DA28,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="EG28" s="206">
+      <c r="EG28" s="204">
         <f>COUNTIF(DA28:$DA$700000,EE28)</f>
         <v>0</v>
       </c>
-      <c r="EH28" s="206" t="e">
+      <c r="EH28" s="204" t="e">
         <f>IF(EE28=0,0,IF(INDEX($EE$28:EE28,CU28-1)=EE28,0,1))</f>
         <v>#N/A</v>
       </c>
-      <c r="EI28" s="206" t="e">
+      <c r="EI28" s="204" t="e">
         <f>IF(EH28=1,0,IF(EG28&gt;0,1,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="EJ28" s="206" t="e">
+      <c r="EJ28" s="204" t="e">
         <f>IF(EI28=1,IF(INDEX($EE$28:EE28,CU28-2)=EE28,1,0),0)</f>
         <v>#N/A</v>
       </c>
-      <c r="EK28" s="206" t="e">
+      <c r="EK28" s="204" t="e">
         <f>IF(INDEX($EJ$28:EJ28,CU28-1)=1,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="EL28" s="204" t="e">
+      <c r="EL28" s="202" t="e">
         <f>IF(EE28=0,0,SUMIF(EE28:$EE$700000,EE28,DS28:$DS$700000))</f>
         <v>#N/A</v>
       </c>
-      <c r="EM28" s="206" t="e">
+      <c r="EM28" s="204" t="e">
         <f>IF(EJ28&gt;0,IF(INDEX($DO$28:DO28,CU28-1)=DO28,IF(DT28=0,IF(INDEX($DT$28:DT28,CU28-1)=DT28,0,1),0),0),0)</f>
         <v>#N/A</v>
       </c>
-      <c r="EN28" s="205">
+      <c r="EN28" s="203">
         <f>INDEX($DS$28:DS28,CU28-1)</f>
         <v>0</v>
       </c>
-      <c r="EO28" s="207">
+      <c r="EO28" s="205">
         <f>IF(DJ28=0,0,IF(CU28-1=DI28,1,0))</f>
         <v>0</v>
       </c>
-      <c r="EP28" s="208" t="e">
+      <c r="EP28" s="206" t="e">
         <f>_xlfn.IFS(IF(DM28,IF(EJ28,1,0),0),IF(EM28=1,0,IF(EK28=0,3,5)),ED28=1,IF(EO28=1,4,2),1,0)</f>
         <v>#N/A</v>
       </c>
@@ -16422,105 +16765,105 @@
         <f>IF(DO28=0,0,IF(CU28&gt;=DP28,IF(CU28&lt;=DP28+DQ28,IF(SUMIF($DO$28:$DO$700000,DO28,$DW$28:$DW$700000)&gt;0,1,0),0),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="ER28" s="205" t="e">
+      <c r="ER28" s="203" t="e">
         <f>IF(EQ28=0,0,IF(CU28&gt;=DP28,IF(CU28&lt;=DP28+DQ28,IF(SUMIF(DO28:$DO$700000,DO28,EH28:$EH$700000)&gt;0,1,0),0),0))</f>
         <v>#N/A</v>
       </c>
-      <c r="ES28" s="208" t="e">
+      <c r="ES28" s="206" t="e">
         <f>IF(EM28&gt;0,IF(ER28&gt;0,1,0),0)</f>
         <v>#N/A</v>
       </c>
-      <c r="ET28" s="208" t="e">
+      <c r="ET28" s="206" t="e">
         <f>IF(DR28&gt;0,IF(EP28=2,0,IF(ER28&gt;0,IF(EB28=0,1,0),0)),0)</f>
         <v>#N/A</v>
       </c>
-      <c r="EU28" s="208">
+      <c r="EU28" s="206">
         <f>IF(DJ28=0,0,IF(CU28-1=DI28,0,DJ28))</f>
         <v>0</v>
       </c>
-      <c r="EV28" s="205" t="e">
+      <c r="EV28" s="203" t="e">
         <f>_xlfn.IFS(ES28,4,EM28&gt;0,3,ET28,2,EU28,IF(EN28&gt;0,0,1),1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="EW28" s="209">
+      <c r="EW28" s="207">
         <f>IF(DC28&gt;0,1,0)</f>
         <v>1</v>
       </c>
-      <c r="EX28" s="209">
+      <c r="EX28" s="207">
         <f>IF(DF28=1,IF(DG28=1,1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="EY28" s="209" t="e">
+      <c r="EY28" s="207" t="e">
         <f>IF(DW28=0,IF(DR28=1,1,0),0)</f>
         <v>#N/A</v>
       </c>
-      <c r="EZ28" s="209">
+      <c r="EZ28" s="207">
         <f>_xlfn.IFS(EW28,4,IF(EH28,IF(DM28,1,0),0),2,EX28,1,DN28=0,0,IF(EY28=1,IF(EG28&gt;0,1,0),0),3,1,0)</f>
         <v>4</v>
       </c>
-      <c r="FA28" s="209">
+      <c r="FA28" s="207">
         <f>IF(INDEX($DA$28:DA28,CU28-1)=DA28,1,0)</f>
         <v>1</v>
       </c>
-      <c r="FB28" s="209"/>
-      <c r="FC28" s="209"/>
-      <c r="FD28" s="209" t="e">
+      <c r="FB28" s="207"/>
+      <c r="FC28" s="207"/>
+      <c r="FD28" s="207" t="e">
         <f>_xlfn.IFS(DK28,0,EB28,0,EW28,0,EP28=5,0,FA28,3,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="FE28" s="209" t="e">
+      <c r="FE28" s="207" t="e">
         <f>_xlfn.IFS(DB28&gt;0,0,DW28,1,DR28,1,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="FF28" s="205" t="e">
+      <c r="FF28" s="203" t="e">
         <f>IF(FE28=1,DA28,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="FG28" s="205" t="e">
+      <c r="FG28" s="203" t="e">
         <f>IF(FF28=0,0,IF(INDEX($FF$28:FF28,CU28-1)=FF28,0,1))</f>
         <v>#N/A</v>
       </c>
-      <c r="FH28" s="205" t="e">
+      <c r="FH28" s="203" t="e">
         <f>IF(FF28=0,0,SUMIF(CY28:$CY$700000,CY28,FG28:$FG$700000))</f>
         <v>#N/A</v>
       </c>
-      <c r="FI28" s="205" t="e">
+      <c r="FI28" s="203" t="e">
         <f>IF(DR28=1,IF(DM28=1,IF(DW28=0,IF(DB28&gt;0,0,1),0),0),0)</f>
         <v>#N/A</v>
       </c>
-      <c r="FJ28" s="205" t="e">
+      <c r="FJ28" s="203" t="e">
         <f>_xlfn.IFS(DK28,0,EB28,0,IF(FH28&gt;0,IF(FI28=0,1,0),0),4,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="FK28" s="209" t="e">
+      <c r="FK28" s="207" t="e">
         <f>IF(FD28=3,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="FL28" s="209">
+      <c r="FL28" s="207">
         <f>IF(EZ28=4,1,0)</f>
         <v>1</v>
       </c>
-      <c r="FM28" s="209">
+      <c r="FM28" s="207">
         <f>IF(DG28=0,1,0)</f>
         <v>0</v>
       </c>
-      <c r="FN28" s="209" t="e">
+      <c r="FN28" s="207" t="e">
         <f>IF(EB28=1,IF(DB28=0,1,0),0)</f>
         <v>#N/A</v>
       </c>
-      <c r="FO28" s="209" t="e">
+      <c r="FO28" s="207" t="e">
         <f>_xlfn.IFS(DK28,0,FK28,3,FN28,5,FL28,5,IF(FH28=1,IF(FJ28=4,1,0),0),4,FI28,5,1,0)</f>
         <v>#N/A</v>
       </c>
-      <c r="FP28" s="200">
+      <c r="FP28" s="198">
         <f>IF(CU28=1,0,IF(DB28=0,IF(INDEX($DB$28:$DB$700000,CU28-1)&gt;0,1,0),0))</f>
         <v>0</v>
       </c>
-      <c r="FQ28" s="116" t="e">
+      <c r="FQ28" s="114" t="e">
         <f>"&lt;zsetformulatocell toSheet=[zallcabCALC]  toCell=["&amp;ADDRESS(MATCH(AN28,'&lt;zallcab&gt;CALC'!$D$7:$D$700000,0)+ROW('&lt;zallcab&gt;CALC'!$D$7)-1,COLUMN('&lt;zallcab&gt;CALC'!Y7)) &amp; "] formula=[fromSheet!"&amp;ADDRESS(ROW(AV28),COLUMN(AV28))&amp;"]"</f>
         <v>#N/A</v>
       </c>
-      <c r="FR28" s="116" t="e">
+      <c r="FR28" s="114" t="e">
         <f>"&lt;zsetformulatocell toSheet=[zallcabCALC]  toCell=["&amp;ADDRESS(MATCH(AN28,'&lt;zallcab&gt;CALC'!$D$7:$D$700000,0)+ROW('&lt;zallcab&gt;CALC'!$D$7)-1,COLUMN('&lt;zallcab&gt;CALC'!Z7)) &amp; "] formula=[fromSheet!"&amp;ADDRESS(ROW(AW28),COLUMN(AW28))&amp;"]"</f>
         <v>#N/A</v>
       </c>
@@ -16530,22 +16873,22 @@
       <c r="FT28" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="FU28" s="115">
+      <c r="FU28" s="113">
         <f>$FU$27+25*$AA$5*CU28-COUNTIF($FP$28:FP28,1)*25*$AA$5</f>
         <v>60</v>
       </c>
-      <c r="FV28" s="111">
-        <v>0</v>
-      </c>
-      <c r="FW28" s="108">
+      <c r="FV28" s="109">
+        <v>0</v>
+      </c>
+      <c r="FW28" s="106">
         <f>$AA$5</f>
         <v>1</v>
       </c>
-      <c r="FX28" s="108">
+      <c r="FX28" s="106">
         <f>$AA$6</f>
         <v>1</v>
       </c>
-      <c r="FY28" s="113">
+      <c r="FY28" s="111">
         <v>0</v>
       </c>
       <c r="FZ28" s="1" t="s">
@@ -16555,122 +16898,122 @@
         <f ca="1">IF(R28="ABC","BOOLEAN_1","BOOLEAN_0")</f>
         <v>#N/A</v>
       </c>
-      <c r="GB28" s="158" t="s">
+      <c r="GB28" s="156" t="s">
         <v>206</v>
       </c>
-      <c r="GC28" s="158" t="e">
+      <c r="GC28" s="156" t="e">
         <f ca="1">"INTEGER_"&amp;DZ28</f>
         <v>#N/A</v>
       </c>
-      <c r="GD28" s="103" t="s">
-        <v>523</v>
-      </c>
-      <c r="GE28" s="153" t="e">
+      <c r="GD28" s="101" t="s">
+        <v>518</v>
+      </c>
+      <c r="GE28" s="151" t="e">
         <f ca="1">IF(H28="",IF(GC28&lt;&gt;"INTEGER_0","INTEGER_2","INTEGER_0"),IF(BU28&lt;&gt;"N","INTEGER_1","INTEGER_2"))</f>
         <v>#N/A</v>
       </c>
-      <c r="GF28" s="103" t="s">
-        <v>524</v>
-      </c>
-      <c r="GG28" s="152" t="e">
+      <c r="GF28" s="101" t="s">
+        <v>519</v>
+      </c>
+      <c r="GG28" s="150" t="e">
         <f ca="1">IF(GC28="INTEGER_2","INTEGER_2",IF(GC28="INTEGER_3","INTEGER_2",IF(CM28="N","INTEGER_2",IF(CM28=0,"INTEGER_1","INTEGER_0"))))</f>
         <v>#N/A</v>
       </c>
-      <c r="GH28" s="104" t="s">
+      <c r="GH28" s="102" t="s">
         <v>205</v>
       </c>
-      <c r="GI28" s="149" t="e">
+      <c r="GI28" s="147" t="e">
         <f>"INTEGER_"&amp;EP28</f>
         <v>#N/A</v>
       </c>
-      <c r="GJ28" s="117" t="s">
+      <c r="GJ28" s="115" t="s">
         <v>204</v>
       </c>
-      <c r="GK28" s="117" t="e">
+      <c r="GK28" s="115" t="e">
         <f>"INTEGER_"&amp;EV28</f>
         <v>#N/A</v>
       </c>
-      <c r="GL28" s="104" t="s">
+      <c r="GL28" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="GM28" s="115" t="str">
+      <c r="GM28" s="113" t="str">
         <f>"INTEGER_"&amp;EZ28</f>
         <v>INTEGER_4</v>
       </c>
-      <c r="GN28" s="107" t="s">
+      <c r="GN28" s="105" t="s">
         <v>202</v>
       </c>
-      <c r="GO28" s="115" t="e">
+      <c r="GO28" s="113" t="e">
         <f>"INTEGER_"&amp;FD28</f>
         <v>#N/A</v>
       </c>
-      <c r="GP28" s="107" t="s">
+      <c r="GP28" s="105" t="s">
         <v>201</v>
       </c>
-      <c r="GQ28" s="107" t="e">
+      <c r="GQ28" s="105" t="e">
         <f>"INTEGER_"&amp;FJ28</f>
         <v>#N/A</v>
       </c>
-      <c r="GR28" s="107" t="s">
+      <c r="GR28" s="105" t="s">
         <v>200</v>
       </c>
-      <c r="GS28" s="115" t="e">
+      <c r="GS28" s="113" t="e">
         <f>"INTEGER_"&amp;FO28</f>
         <v>#N/A</v>
       </c>
       <c r="GT28" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="GU28" s="115">
+      <c r="GU28" s="113">
         <f>IF(DB28&gt;0,"",IF(X28&gt;1,P28&amp;"("&amp;X28&amp;"шт.)",P28))</f>
         <v>0</v>
       </c>
       <c r="GV28" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="GW28" s="115">
+      <c r="GW28" s="113">
         <f ca="1">IF(DB28&gt;0,"",S28)</f>
         <v>0</v>
       </c>
       <c r="GX28" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="GY28" s="115" t="e">
+      <c r="GY28" s="113" t="e">
         <f ca="1">IF(DB28&gt;0,"",U28)</f>
         <v>#N/A</v>
       </c>
       <c r="GZ28" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="HA28" s="115" t="e">
-        <f ca="1">IF(DB28&gt;0,"",AA28&amp;"\P~"&amp;Q28&amp;"V")</f>
+      <c r="HA28" s="129" t="e">
+        <f ca="1">IF(DB28&gt;0,"",AA28&amp;"\P~"&amp;Q28&amp;"V"&amp;"\P пом. "&amp;IP28)</f>
         <v>#N/A</v>
       </c>
       <c r="HB28" s="52" t="s">
         <v>195</v>
       </c>
-      <c r="HC28" s="52" t="str">
-        <f>" "</f>
-        <v xml:space="preserve"> </v>
+      <c r="HC28" s="52" t="e">
+        <f>IF(HE28="",AN28,"")</f>
+        <v>#N/A</v>
       </c>
       <c r="HD28" s="52" t="s">
         <v>194</v>
       </c>
-      <c r="HE28" s="115" t="str">
+      <c r="HE28" s="113" t="str">
         <f>IFERROR(_xlfn.IFS(IF(DD28&gt;0,1,0),AO28,IF(DB28&gt;0,IF(EH28,1,0),0),AO28,IF(DD28=0,1,0),""),AO28)</f>
         <v/>
       </c>
       <c r="HF28" s="52" t="s">
         <v>193</v>
       </c>
-      <c r="HG28" s="115" t="str">
+      <c r="HG28" s="113" t="str">
         <f>IF(HE28="","","("&amp;AN28&amp;") L="&amp;AP28&amp;"м")</f>
         <v/>
       </c>
       <c r="HH28" s="52" t="s">
         <v>192</v>
       </c>
-      <c r="HI28" s="115" t="e">
+      <c r="HI28" s="113" t="e">
         <f>IF(HE28="",AO28,"")</f>
         <v>#N/A</v>
       </c>
@@ -16678,41 +17021,41 @@
         <f>"VSCHEMACable22"</f>
         <v>VSCHEMACable22</v>
       </c>
-      <c r="HK28" s="115" t="e">
-        <f>IF(HG28="",IF(AP28&lt;&gt;"","("&amp;AN28&amp;") L="&amp;AP28&amp;"м"," "),"")</f>
+      <c r="HK28" s="113" t="e">
+        <f>IF(HG28="",IO28,"")</f>
         <v>#N/A</v>
       </c>
       <c r="HL28" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="HM28" s="108" t="s">
+      <c r="HM28" s="106" t="s">
         <v>209</v>
       </c>
-      <c r="HN28" s="115" t="str">
+      <c r="HN28" s="113" t="str">
         <f>'&lt;zalldev&gt;EXPORT'!AP11</f>
         <v>&lt;zcadnameblock&gt;</v>
       </c>
-      <c r="HO28" s="115" t="e">
+      <c r="HO28" s="113" t="e">
         <f>FU28+12.5*$AA$5+INDEX(BDUGO!$D$4:$D$51,MATCH(IF(DB28&gt;0,"UU","")&amp;HN28,BDUGO!$C$4:$C$51,0))*$AA$5</f>
         <v>#N/A</v>
       </c>
-      <c r="HP28" s="115" t="e">
+      <c r="HP28" s="113" t="e">
         <f>FV28+42.5*$AA$6+INDEX(BDUGO!$E$4:$E$51,MATCH(IF(DB28&gt;0,"UU","")&amp;HN28,BDUGO!$C$4:$C$51,0))*$AA$6</f>
         <v>#N/A</v>
       </c>
-      <c r="HQ28" s="115" t="e">
+      <c r="HQ28" s="113" t="e">
         <f>IF(INDEX(BDUGO!$F$4:$F$51,MATCH(IF(DB28&gt;0,"UU","")&amp;HN28,BDUGO!$C$4:$C$51,0))=0,1,INDEX(BDUGO!$F$4:$F$51,MATCH(IF(DB28&gt;0,"UU","")&amp;HN28,BDUGO!$C$4:$C$51,0)))*$AA$5</f>
         <v>#N/A</v>
       </c>
-      <c r="HR28" s="115" t="e">
+      <c r="HR28" s="113" t="e">
         <f>IF(INDEX(BDUGO!$G$4:$G$51,MATCH(IF(DB28&gt;0,"UU","")&amp;HN28,BDUGO!$C$4:$C$51,0))=0,1,INDEX(BDUGO!$G$4:$G$51,MATCH(IF(DB28&gt;0,"UU","")&amp;HN28,BDUGO!$C$4:$C$51,0)))*$AA$6</f>
         <v>#N/A</v>
       </c>
-      <c r="HS28" s="115" t="e">
+      <c r="HS28" s="113" t="e">
         <f>INDEX(BDUGO!$H$4:$H$51,MATCH(IF(DB28&gt;0,"UU","")&amp;HN28,BDUGO!$C$4:$C$51,0))</f>
         <v>#N/A</v>
       </c>
-      <c r="HT28" s="108" t="s">
+      <c r="HT28" s="106" t="s">
         <v>191</v>
       </c>
       <c r="HU28" s="1" t="e">
@@ -16795,7 +17138,11 @@
         <f>IF(AN28="","",INDEX('&lt;zallcab&gt;CabGroup'!$Q$7:$Q$700000,MATCH(AN28,'&lt;zallcab&gt;CabGroup'!$C$7:$C$700000,0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="IP28" s="1" t="s">
+      <c r="IP28" s="1" t="str">
+        <f ca="1">IF(GU28="","",INDEX('&lt;zalldev&gt;DevGroup'!$R$7:$R$700000,MATCH(DA28&amp;"."&amp;P28,'&lt;zalldev&gt;DevGroup'!$G$7:$G$700000,0)))</f>
+        <v>0</v>
+      </c>
+      <c r="IQ28" s="1" t="s">
         <v>189</v>
       </c>
     </row>
@@ -16990,239 +17337,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADAE1986-1CF6-4370-AEB3-1DC97E00D4E1}">
-  <dimension ref="A2:S6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" customWidth="1"/>
-    <col min="5" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="3.7109375" customWidth="1"/>
-    <col min="8" max="11" width="12.7109375" customWidth="1"/>
-    <col min="12" max="12" width="3.7109375" customWidth="1"/>
-    <col min="13" max="18" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1">
-        <f>A2+1</f>
-        <v>1</v>
-      </c>
-      <c r="C2" s="1">
-        <f t="shared" ref="C2:R2" si="0">B2+1</f>
-        <v>2</v>
-      </c>
-      <c r="D2" s="1">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E2" s="1">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="F2" s="1">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="G2" s="1">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="H2" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="I2" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="J2" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="K2" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="L2" s="1">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="M2" s="1">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="N2" s="1">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="O2" s="1">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="P2" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="Q2" s="1">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="R2" s="76">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="90" x14ac:dyDescent="0.25">
-      <c r="C3" s="61"/>
-      <c r="D3" s="239" t="s">
-        <v>331</v>
-      </c>
-      <c r="E3" s="239"/>
-      <c r="F3" s="239"/>
-      <c r="G3" s="239" t="s">
-        <v>332</v>
-      </c>
-      <c r="H3" s="239"/>
-      <c r="I3" s="239"/>
-      <c r="J3" s="71" t="s">
-        <v>335</v>
-      </c>
-      <c r="K3" s="71" t="s">
-        <v>333</v>
-      </c>
-      <c r="L3" s="239" t="s">
-        <v>334</v>
-      </c>
-      <c r="M3" s="239"/>
-      <c r="N3" s="239"/>
-      <c r="O3" s="289" t="s">
-        <v>342</v>
-      </c>
-      <c r="P3" s="289"/>
-      <c r="Q3" s="289"/>
-      <c r="R3" s="77" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C4" s="61"/>
-      <c r="D4" s="47" t="s">
-        <v>164</v>
-      </c>
-      <c r="E4" s="48" t="s">
-        <v>162</v>
-      </c>
-      <c r="F4" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="G4" s="47" t="s">
-        <v>164</v>
-      </c>
-      <c r="H4" s="48" t="s">
-        <v>162</v>
-      </c>
-      <c r="I4" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="J4" s="48" t="s">
-        <v>162</v>
-      </c>
-      <c r="K4" s="48" t="s">
-        <v>162</v>
-      </c>
-      <c r="L4" s="47" t="s">
-        <v>164</v>
-      </c>
-      <c r="M4" s="48" t="s">
-        <v>162</v>
-      </c>
-      <c r="N4" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="O4" s="72" t="s">
-        <v>164</v>
-      </c>
-      <c r="P4" s="73" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q4" s="74" t="s">
-        <v>163</v>
-      </c>
-      <c r="R4" s="77"/>
-    </row>
-    <row r="5" spans="1:19" ht="45" x14ac:dyDescent="0.25">
-      <c r="C5" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="47"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="47"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="49"/>
-      <c r="J5" s="48"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="48"/>
-      <c r="N5" s="49"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="73"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="77"/>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="C6" s="58" t="s">
-        <v>142</v>
-      </c>
-      <c r="D6" s="50" t="s">
-        <v>338</v>
-      </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="50" t="s">
-        <v>339</v>
-      </c>
-      <c r="H6" s="48"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="48" t="s">
-        <v>336</v>
-      </c>
-      <c r="K6" s="48" t="s">
-        <v>337</v>
-      </c>
-      <c r="L6" s="50" t="s">
-        <v>340</v>
-      </c>
-      <c r="M6" s="48"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="50" t="s">
-        <v>344</v>
-      </c>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="49"/>
-      <c r="R6" s="77">
-        <v>1</v>
-      </c>
-      <c r="S6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="O3:Q3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8B6AA6F-5182-413B-A37A-EA05D8E4268E}">
   <dimension ref="B1:AH20"/>
@@ -17230,41 +17344,41 @@
   <sheetData>
     <row r="1" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:34" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="220" t="s">
+      <c r="B2" s="269" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="221"/>
-      <c r="D2" s="221"/>
-      <c r="E2" s="221"/>
-      <c r="F2" s="221"/>
-      <c r="G2" s="221"/>
-      <c r="H2" s="221"/>
-      <c r="I2" s="221"/>
-      <c r="J2" s="221"/>
-      <c r="K2" s="221"/>
-      <c r="L2" s="221"/>
-      <c r="M2" s="221"/>
-      <c r="N2" s="221"/>
-      <c r="O2" s="221"/>
-      <c r="P2" s="221"/>
-      <c r="Q2" s="221"/>
-      <c r="R2" s="221"/>
-      <c r="S2" s="221"/>
-      <c r="T2" s="221"/>
-      <c r="U2" s="221"/>
-      <c r="V2" s="221"/>
-      <c r="W2" s="221"/>
-      <c r="X2" s="221"/>
-      <c r="Y2" s="221"/>
-      <c r="Z2" s="221"/>
-      <c r="AA2" s="221"/>
-      <c r="AB2" s="221"/>
-      <c r="AC2" s="221"/>
-      <c r="AD2" s="221"/>
-      <c r="AE2" s="221"/>
-      <c r="AF2" s="221"/>
-      <c r="AG2" s="221"/>
-      <c r="AH2" s="232"/>
+      <c r="C2" s="270"/>
+      <c r="D2" s="270"/>
+      <c r="E2" s="270"/>
+      <c r="F2" s="270"/>
+      <c r="G2" s="270"/>
+      <c r="H2" s="270"/>
+      <c r="I2" s="270"/>
+      <c r="J2" s="270"/>
+      <c r="K2" s="270"/>
+      <c r="L2" s="270"/>
+      <c r="M2" s="270"/>
+      <c r="N2" s="270"/>
+      <c r="O2" s="270"/>
+      <c r="P2" s="270"/>
+      <c r="Q2" s="270"/>
+      <c r="R2" s="270"/>
+      <c r="S2" s="270"/>
+      <c r="T2" s="270"/>
+      <c r="U2" s="270"/>
+      <c r="V2" s="270"/>
+      <c r="W2" s="270"/>
+      <c r="X2" s="270"/>
+      <c r="Y2" s="270"/>
+      <c r="Z2" s="270"/>
+      <c r="AA2" s="270"/>
+      <c r="AB2" s="270"/>
+      <c r="AC2" s="270"/>
+      <c r="AD2" s="270"/>
+      <c r="AE2" s="270"/>
+      <c r="AF2" s="270"/>
+      <c r="AG2" s="270"/>
+      <c r="AH2" s="281"/>
     </row>
     <row r="3" spans="2:34" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="44" t="s">
@@ -18181,488 +18295,488 @@
       <c r="AH12" s="2"/>
     </row>
     <row r="13" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B13" s="212">
+      <c r="B13" s="210">
         <v>35</v>
       </c>
-      <c r="C13" s="212">
+      <c r="C13" s="210">
         <v>147</v>
       </c>
-      <c r="D13" s="213">
+      <c r="D13" s="211">
         <v>0.52400000000000002</v>
       </c>
-      <c r="E13" s="212">
+      <c r="E13" s="210">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="F13" s="213">
+      <c r="F13" s="211">
         <f t="shared" ref="F13:F20" si="5">SQRT(SUMSQ(D13,E13))</f>
         <v>0.53308535901860976</v>
       </c>
-      <c r="G13" s="212">
+      <c r="G13" s="210">
         <v>163</v>
       </c>
-      <c r="H13" s="212">
+      <c r="H13" s="210">
         <f>D13</f>
         <v>0.52400000000000002</v>
       </c>
-      <c r="I13" s="212">
+      <c r="I13" s="210">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="J13" s="213">
+      <c r="J13" s="211">
         <f t="shared" ref="J13:J20" si="6">SQRT(SUMSQ(H13,I13))</f>
         <v>0.53308535901860976</v>
       </c>
-      <c r="K13" s="212">
+      <c r="K13" s="210">
         <v>137</v>
       </c>
-      <c r="L13" s="213">
+      <c r="L13" s="211">
         <f>D13</f>
         <v>0.52400000000000002</v>
       </c>
-      <c r="M13" s="212">
+      <c r="M13" s="210">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="N13" s="213">
+      <c r="N13" s="211">
         <f>SQRT(SUMSQ(L13,M13))</f>
         <v>0.52992169232821562</v>
       </c>
-      <c r="O13" s="212">
+      <c r="O13" s="210">
         <v>158</v>
       </c>
-      <c r="P13" s="213">
+      <c r="P13" s="211">
         <f>D13</f>
         <v>0.52400000000000002</v>
       </c>
-      <c r="Q13" s="212">
+      <c r="Q13" s="210">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="R13" s="213">
+      <c r="R13" s="211">
         <f>SQRT(SUMSQ(P13,Q13))</f>
         <v>0.52992169232821562</v>
       </c>
     </row>
     <row r="14" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B14" s="212">
+      <c r="B14" s="210">
         <v>50</v>
       </c>
-      <c r="C14" s="212">
+      <c r="C14" s="210">
         <v>179</v>
       </c>
-      <c r="D14" s="213">
+      <c r="D14" s="211">
         <f>D$13*$B$13/$B14</f>
         <v>0.36680000000000001</v>
       </c>
-      <c r="E14" s="212">
+      <c r="E14" s="210">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="F14" s="213">
+      <c r="F14" s="211">
         <f t="shared" si="5"/>
         <v>0.37890267879760364</v>
       </c>
-      <c r="G14" s="212">
+      <c r="G14" s="210">
         <v>194</v>
       </c>
-      <c r="H14" s="213">
+      <c r="H14" s="211">
         <f>D14</f>
         <v>0.36680000000000001</v>
       </c>
-      <c r="I14" s="212">
+      <c r="I14" s="210">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="J14" s="213">
+      <c r="J14" s="211">
         <f t="shared" si="6"/>
         <v>0.37890267879760364</v>
       </c>
-      <c r="K14" s="212">
+      <c r="K14" s="210">
         <v>167</v>
       </c>
-      <c r="L14" s="213">
+      <c r="L14" s="211">
         <f t="shared" ref="L14:L20" si="7">D14</f>
         <v>0.36680000000000001</v>
       </c>
-      <c r="M14" s="212">
+      <c r="M14" s="210">
         <v>7.8E-2</v>
       </c>
-      <c r="N14" s="213">
+      <c r="N14" s="211">
         <f t="shared" ref="N14:N20" si="8">SQRT(SUMSQ(L14,M14))</f>
         <v>0.37500165332968871</v>
       </c>
-      <c r="O14" s="212">
+      <c r="O14" s="210">
         <v>187</v>
       </c>
-      <c r="P14" s="213">
+      <c r="P14" s="211">
         <f t="shared" ref="P14:P20" si="9">D14</f>
         <v>0.36680000000000001</v>
       </c>
-      <c r="Q14" s="212">
+      <c r="Q14" s="210">
         <v>7.8E-2</v>
       </c>
-      <c r="R14" s="213">
+      <c r="R14" s="211">
         <f t="shared" ref="R14:R20" si="10">SQRT(SUMSQ(P14,Q14))</f>
         <v>0.37500165332968871</v>
       </c>
     </row>
     <row r="15" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B15" s="212">
+      <c r="B15" s="210">
         <v>70</v>
       </c>
-      <c r="C15" s="212">
+      <c r="C15" s="210">
         <v>226</v>
       </c>
-      <c r="D15" s="213">
+      <c r="D15" s="211">
         <f t="shared" ref="D15:D20" si="11">D$13*$B$13/$B15</f>
         <v>0.26200000000000001</v>
       </c>
-      <c r="E15" s="212">
+      <c r="E15" s="210">
         <v>0.09</v>
       </c>
-      <c r="F15" s="213">
+      <c r="F15" s="211">
         <f t="shared" si="5"/>
         <v>0.27702707448911923</v>
       </c>
-      <c r="G15" s="212">
+      <c r="G15" s="210">
         <v>237</v>
       </c>
-      <c r="H15" s="213">
+      <c r="H15" s="211">
         <f t="shared" ref="H15:H20" si="12">D15</f>
         <v>0.26200000000000001</v>
       </c>
-      <c r="I15" s="212">
+      <c r="I15" s="210">
         <v>0.09</v>
       </c>
-      <c r="J15" s="213">
+      <c r="J15" s="211">
         <f t="shared" si="6"/>
         <v>0.27702707448911923</v>
       </c>
-      <c r="K15" s="212">
+      <c r="K15" s="210">
         <v>211</v>
       </c>
-      <c r="L15" s="213">
+      <c r="L15" s="211">
         <f t="shared" si="7"/>
         <v>0.26200000000000001</v>
       </c>
-      <c r="M15" s="212">
+      <c r="M15" s="210">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="N15" s="213">
+      <c r="N15" s="211">
         <f t="shared" si="8"/>
         <v>0.27252339349127447</v>
       </c>
-      <c r="O15" s="212">
+      <c r="O15" s="210">
         <v>231</v>
       </c>
-      <c r="P15" s="213">
+      <c r="P15" s="211">
         <f t="shared" si="9"/>
         <v>0.26200000000000001</v>
       </c>
-      <c r="Q15" s="212">
+      <c r="Q15" s="210">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="R15" s="213">
+      <c r="R15" s="211">
         <f t="shared" si="10"/>
         <v>0.27252339349127447</v>
       </c>
     </row>
     <row r="16" spans="2:34" x14ac:dyDescent="0.25">
-      <c r="B16" s="212">
+      <c r="B16" s="210">
         <v>95</v>
       </c>
-      <c r="C16" s="212">
+      <c r="C16" s="210">
         <v>280</v>
       </c>
-      <c r="D16" s="213">
+      <c r="D16" s="211">
         <f t="shared" si="11"/>
         <v>0.19305263157894736</v>
       </c>
-      <c r="E16" s="212">
+      <c r="E16" s="210">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="F16" s="213">
+      <c r="F16" s="211">
         <f t="shared" si="5"/>
         <v>0.21216342417946782</v>
       </c>
-      <c r="G16" s="212">
+      <c r="G16" s="210">
         <v>285</v>
       </c>
-      <c r="H16" s="213">
+      <c r="H16" s="211">
         <f t="shared" si="12"/>
         <v>0.19305263157894736</v>
       </c>
-      <c r="I16" s="212">
+      <c r="I16" s="210">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="J16" s="213">
+      <c r="J16" s="211">
         <f t="shared" si="6"/>
         <v>0.21216342417946782</v>
       </c>
-      <c r="K16" s="212">
+      <c r="K16" s="210">
         <v>261</v>
       </c>
-      <c r="L16" s="213">
+      <c r="L16" s="211">
         <f t="shared" si="7"/>
         <v>0.19305263157894736</v>
       </c>
-      <c r="M16" s="212">
+      <c r="M16" s="210">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="N16" s="213">
+      <c r="N16" s="211">
         <f t="shared" si="8"/>
         <v>0.2071094361914898</v>
       </c>
-      <c r="O16" s="212">
+      <c r="O16" s="210">
         <v>279</v>
       </c>
-      <c r="P16" s="213">
+      <c r="P16" s="211">
         <f t="shared" si="9"/>
         <v>0.19305263157894736</v>
       </c>
-      <c r="Q16" s="212">
+      <c r="Q16" s="210">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="R16" s="213">
+      <c r="R16" s="211">
         <f t="shared" si="10"/>
         <v>0.2071094361914898</v>
       </c>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B17" s="212">
+      <c r="B17" s="210">
         <v>120</v>
       </c>
-      <c r="C17" s="212">
+      <c r="C17" s="210">
         <v>326</v>
       </c>
-      <c r="D17" s="213">
+      <c r="D17" s="211">
         <f t="shared" si="11"/>
         <v>0.15283333333333332</v>
       </c>
-      <c r="E17" s="212">
+      <c r="E17" s="210">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="F17" s="213">
+      <c r="F17" s="211">
         <f t="shared" si="5"/>
         <v>0.17488003824844553</v>
       </c>
-      <c r="G17" s="212">
+      <c r="G17" s="210">
         <v>324</v>
       </c>
-      <c r="H17" s="213">
+      <c r="H17" s="211">
         <f t="shared" si="12"/>
         <v>0.15283333333333332</v>
       </c>
-      <c r="I17" s="212">
+      <c r="I17" s="210">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="J17" s="213">
+      <c r="J17" s="211">
         <f t="shared" si="6"/>
         <v>0.17488003824844553</v>
       </c>
-      <c r="K17" s="212">
+      <c r="K17" s="210">
         <v>302</v>
       </c>
-      <c r="L17" s="213">
+      <c r="L17" s="211">
         <f t="shared" si="7"/>
         <v>0.15283333333333332</v>
       </c>
-      <c r="M17" s="212">
+      <c r="M17" s="210">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="N17" s="213">
+      <c r="N17" s="211">
         <f t="shared" si="8"/>
         <v>0.1693724528303755</v>
       </c>
-      <c r="O17" s="212">
+      <c r="O17" s="210">
         <v>317</v>
       </c>
-      <c r="P17" s="213">
+      <c r="P17" s="211">
         <f t="shared" si="9"/>
         <v>0.15283333333333332</v>
       </c>
-      <c r="Q17" s="212">
+      <c r="Q17" s="210">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="R17" s="213">
+      <c r="R17" s="211">
         <f t="shared" si="10"/>
         <v>0.1693724528303755</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B18" s="212">
+      <c r="B18" s="210">
         <v>150</v>
       </c>
-      <c r="C18" s="212">
+      <c r="C18" s="210">
         <v>373</v>
       </c>
-      <c r="D18" s="213">
+      <c r="D18" s="211">
         <f t="shared" si="11"/>
         <v>0.12226666666666666</v>
       </c>
-      <c r="E18" s="212">
+      <c r="E18" s="210">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="F18" s="213">
+      <c r="F18" s="211">
         <f t="shared" si="5"/>
         <v>0.14834128817621134</v>
       </c>
-      <c r="G18" s="212">
+      <c r="G18" s="210">
         <v>364</v>
       </c>
-      <c r="H18" s="213">
+      <c r="H18" s="211">
         <f t="shared" si="12"/>
         <v>0.12226666666666666</v>
       </c>
-      <c r="I18" s="212">
+      <c r="I18" s="210">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="J18" s="213">
+      <c r="J18" s="211">
         <f t="shared" si="6"/>
         <v>0.14834128817621134</v>
       </c>
-      <c r="K18" s="212">
+      <c r="K18" s="210">
         <v>346</v>
       </c>
-      <c r="L18" s="213">
+      <c r="L18" s="211">
         <f t="shared" si="7"/>
         <v>0.12226666666666666</v>
       </c>
-      <c r="M18" s="212">
+      <c r="M18" s="210">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="N18" s="213">
+      <c r="N18" s="211">
         <f t="shared" si="8"/>
         <v>0.14240132646073833</v>
       </c>
-      <c r="O18" s="212">
+      <c r="O18" s="210">
         <v>358</v>
       </c>
-      <c r="P18" s="213">
+      <c r="P18" s="211">
         <f t="shared" si="9"/>
         <v>0.12226666666666666</v>
       </c>
-      <c r="Q18" s="212">
+      <c r="Q18" s="210">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="R18" s="213">
+      <c r="R18" s="211">
         <f t="shared" si="10"/>
         <v>0.14240132646073833</v>
       </c>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B19" s="212">
+      <c r="B19" s="210">
         <v>185</v>
       </c>
-      <c r="C19" s="212">
+      <c r="C19" s="210">
         <v>431</v>
       </c>
-      <c r="D19" s="213">
+      <c r="D19" s="211">
         <f t="shared" si="11"/>
         <v>9.9135135135135138E-2</v>
       </c>
-      <c r="E19" s="212">
+      <c r="E19" s="210">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="F19" s="213">
+      <c r="F19" s="211">
         <f t="shared" si="5"/>
         <v>0.12993758123907612</v>
       </c>
-      <c r="G19" s="212">
+      <c r="G19" s="210">
         <v>412</v>
       </c>
-      <c r="H19" s="213">
+      <c r="H19" s="211">
         <f t="shared" si="12"/>
         <v>9.9135135135135138E-2</v>
       </c>
-      <c r="I19" s="212">
+      <c r="I19" s="210">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="J19" s="213">
+      <c r="J19" s="211">
         <f t="shared" si="6"/>
         <v>0.12993758123907612</v>
       </c>
-      <c r="K19" s="212">
+      <c r="K19" s="210">
         <v>397</v>
       </c>
-      <c r="L19" s="213">
+      <c r="L19" s="211">
         <f t="shared" si="7"/>
         <v>9.9135135135135138E-2</v>
       </c>
-      <c r="M19" s="212">
+      <c r="M19" s="210">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="N19" s="213">
+      <c r="N19" s="211">
         <f t="shared" si="8"/>
         <v>0.12311285480509947</v>
       </c>
-      <c r="O19" s="212">
+      <c r="O19" s="210">
         <v>405</v>
       </c>
-      <c r="P19" s="213">
+      <c r="P19" s="211">
         <f t="shared" si="9"/>
         <v>9.9135135135135138E-2</v>
       </c>
-      <c r="Q19" s="212">
+      <c r="Q19" s="210">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="R19" s="213">
+      <c r="R19" s="211">
         <f t="shared" si="10"/>
         <v>0.12311285480509947</v>
       </c>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B20" s="212">
+      <c r="B20" s="210">
         <v>240</v>
       </c>
-      <c r="C20" s="212">
+      <c r="C20" s="210">
         <v>512</v>
       </c>
-      <c r="D20" s="213">
+      <c r="D20" s="211">
         <f t="shared" si="11"/>
         <v>7.6416666666666661E-2</v>
       </c>
-      <c r="E20" s="212">
+      <c r="E20" s="210">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="F20" s="213">
+      <c r="F20" s="211">
         <f t="shared" si="5"/>
         <v>0.11208705074380557</v>
       </c>
-      <c r="G20" s="212">
+      <c r="G20" s="210">
         <v>477</v>
       </c>
-      <c r="H20" s="213">
+      <c r="H20" s="211">
         <f t="shared" si="12"/>
         <v>7.6416666666666661E-2</v>
       </c>
-      <c r="I20" s="212">
+      <c r="I20" s="210">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="J20" s="213">
+      <c r="J20" s="211">
         <f t="shared" si="6"/>
         <v>0.11208705074380557</v>
       </c>
-      <c r="K20" s="212">
+      <c r="K20" s="210">
         <v>472</v>
       </c>
-      <c r="L20" s="213">
+      <c r="L20" s="211">
         <f t="shared" si="7"/>
         <v>7.6416666666666661E-2</v>
       </c>
-      <c r="M20" s="212">
+      <c r="M20" s="210">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="N20" s="213">
+      <c r="N20" s="211">
         <f t="shared" si="8"/>
         <v>0.10499288997091394</v>
       </c>
-      <c r="O20" s="212">
+      <c r="O20" s="210">
         <v>471</v>
       </c>
-      <c r="P20" s="213">
+      <c r="P20" s="211">
         <f t="shared" si="9"/>
         <v>7.6416666666666661E-2</v>
       </c>
-      <c r="Q20" s="212">
+      <c r="Q20" s="210">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="R20" s="213">
+      <c r="R20" s="211">
         <f t="shared" si="10"/>
         <v>0.10499288997091394</v>
       </c>
@@ -18687,49 +18801,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="233" t="s">
+      <c r="B1" s="282" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="233"/>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
-      <c r="I1" s="233"/>
-      <c r="J1" s="233"/>
-      <c r="K1" s="233"/>
-      <c r="L1" s="233"/>
-      <c r="M1" s="233"/>
-      <c r="N1" s="233"/>
-      <c r="O1" s="233"/>
-      <c r="P1" s="233"/>
-      <c r="Q1" s="233"/>
-      <c r="R1" s="233"/>
+      <c r="C1" s="282"/>
+      <c r="D1" s="282"/>
+      <c r="E1" s="282"/>
+      <c r="F1" s="282"/>
+      <c r="G1" s="282"/>
+      <c r="H1" s="282"/>
+      <c r="I1" s="282"/>
+      <c r="J1" s="282"/>
+      <c r="K1" s="282"/>
+      <c r="L1" s="282"/>
+      <c r="M1" s="282"/>
+      <c r="N1" s="282"/>
+      <c r="O1" s="282"/>
+      <c r="P1" s="282"/>
+      <c r="Q1" s="282"/>
+      <c r="R1" s="282"/>
     </row>
     <row r="2" spans="1:18" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="24"/>
       <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="234" t="s">
+      <c r="C2" s="283" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="234"/>
-      <c r="E2" s="234"/>
-      <c r="F2" s="234"/>
-      <c r="G2" s="234"/>
-      <c r="H2" s="234"/>
-      <c r="I2" s="234"/>
-      <c r="J2" s="234"/>
-      <c r="K2" s="234"/>
-      <c r="L2" s="234"/>
-      <c r="M2" s="234"/>
-      <c r="N2" s="234"/>
-      <c r="O2" s="234"/>
-      <c r="P2" s="234"/>
-      <c r="Q2" s="234"/>
-      <c r="R2" s="235"/>
+      <c r="D2" s="283"/>
+      <c r="E2" s="283"/>
+      <c r="F2" s="283"/>
+      <c r="G2" s="283"/>
+      <c r="H2" s="283"/>
+      <c r="I2" s="283"/>
+      <c r="J2" s="283"/>
+      <c r="K2" s="283"/>
+      <c r="L2" s="283"/>
+      <c r="M2" s="283"/>
+      <c r="N2" s="283"/>
+      <c r="O2" s="283"/>
+      <c r="P2" s="283"/>
+      <c r="Q2" s="283"/>
+      <c r="R2" s="284"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="12"/>
@@ -19188,992 +19302,992 @@
   <sheetData>
     <row r="1" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="3:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="236" t="s">
+      <c r="C2" s="285" t="s">
+        <v>417</v>
+      </c>
+      <c r="D2" s="286"/>
+      <c r="E2" s="286"/>
+      <c r="F2" s="286"/>
+      <c r="G2" s="286"/>
+      <c r="H2" s="287"/>
+    </row>
+    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C3" s="108" t="s">
+        <v>418</v>
+      </c>
+      <c r="D3" s="108" t="s">
+        <v>419</v>
+      </c>
+      <c r="E3" s="108" t="s">
+        <v>420</v>
+      </c>
+      <c r="F3" s="108" t="s">
+        <v>421</v>
+      </c>
+      <c r="G3" s="108" t="s">
         <v>422</v>
       </c>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="237"/>
-      <c r="H2" s="238"/>
-    </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C3" s="110" t="s">
+      <c r="H3" s="108" t="s">
         <v>423</v>
       </c>
-      <c r="D3" s="110" t="s">
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C4" s="152" t="s">
         <v>424</v>
       </c>
-      <c r="E3" s="110" t="s">
+      <c r="D4" s="153">
+        <v>0</v>
+      </c>
+      <c r="E4" s="153">
+        <v>0</v>
+      </c>
+      <c r="F4" s="153">
+        <v>1</v>
+      </c>
+      <c r="G4" s="153">
+        <v>1</v>
+      </c>
+      <c r="H4" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C5" s="152" t="s">
+        <v>428</v>
+      </c>
+      <c r="D5" s="153">
+        <v>0</v>
+      </c>
+      <c r="E5" s="153">
+        <v>35</v>
+      </c>
+      <c r="F5" s="153">
+        <v>1</v>
+      </c>
+      <c r="G5" s="153">
+        <v>1</v>
+      </c>
+      <c r="H5" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C6" s="152" t="s">
+        <v>596</v>
+      </c>
+      <c r="D6" s="153">
+        <v>0</v>
+      </c>
+      <c r="E6" s="153">
+        <v>0</v>
+      </c>
+      <c r="F6" s="153">
+        <v>1</v>
+      </c>
+      <c r="G6" s="153">
+        <v>1</v>
+      </c>
+      <c r="H6" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C7" s="152" t="s">
+        <v>597</v>
+      </c>
+      <c r="D7" s="153">
+        <v>0</v>
+      </c>
+      <c r="E7" s="153">
+        <v>35</v>
+      </c>
+      <c r="F7" s="153">
+        <v>1</v>
+      </c>
+      <c r="G7" s="153">
+        <v>1</v>
+      </c>
+      <c r="H7" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C8" s="152" t="s">
+        <v>560</v>
+      </c>
+      <c r="D8" s="153">
+        <v>0</v>
+      </c>
+      <c r="E8" s="153">
+        <v>0</v>
+      </c>
+      <c r="F8" s="153">
+        <v>1</v>
+      </c>
+      <c r="G8" s="153">
+        <v>1</v>
+      </c>
+      <c r="H8" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="152" t="s">
+        <v>561</v>
+      </c>
+      <c r="D9" s="153">
+        <v>0</v>
+      </c>
+      <c r="E9" s="153">
+        <v>35</v>
+      </c>
+      <c r="F9" s="153">
+        <v>1</v>
+      </c>
+      <c r="G9" s="153">
+        <v>1</v>
+      </c>
+      <c r="H9" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C10" s="152" t="s">
+        <v>598</v>
+      </c>
+      <c r="D10" s="153">
+        <v>0</v>
+      </c>
+      <c r="E10" s="153">
+        <v>0</v>
+      </c>
+      <c r="F10" s="153">
+        <v>1</v>
+      </c>
+      <c r="G10" s="153">
+        <v>1</v>
+      </c>
+      <c r="H10" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C11" s="152" t="s">
+        <v>599</v>
+      </c>
+      <c r="D11" s="153">
+        <v>0</v>
+      </c>
+      <c r="E11" s="153">
+        <v>35</v>
+      </c>
+      <c r="F11" s="153">
+        <v>1</v>
+      </c>
+      <c r="G11" s="153">
+        <v>1</v>
+      </c>
+      <c r="H11" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="152" t="s">
+        <v>564</v>
+      </c>
+      <c r="D12" s="153">
+        <v>0</v>
+      </c>
+      <c r="E12" s="153">
+        <v>0</v>
+      </c>
+      <c r="F12" s="153">
+        <v>1</v>
+      </c>
+      <c r="G12" s="153">
+        <v>1</v>
+      </c>
+      <c r="H12" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C13" s="152" t="s">
+        <v>565</v>
+      </c>
+      <c r="D13" s="153">
+        <v>0</v>
+      </c>
+      <c r="E13" s="153">
+        <v>35</v>
+      </c>
+      <c r="F13" s="153">
+        <v>1</v>
+      </c>
+      <c r="G13" s="153">
+        <v>1</v>
+      </c>
+      <c r="H13" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C14" s="152" t="s">
+        <v>600</v>
+      </c>
+      <c r="D14" s="153">
+        <v>0</v>
+      </c>
+      <c r="E14" s="153">
+        <v>0</v>
+      </c>
+      <c r="F14" s="153">
+        <v>1</v>
+      </c>
+      <c r="G14" s="153">
+        <v>1</v>
+      </c>
+      <c r="H14" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C15" s="152" t="s">
+        <v>601</v>
+      </c>
+      <c r="D15" s="153">
+        <v>0</v>
+      </c>
+      <c r="E15" s="153">
+        <v>35</v>
+      </c>
+      <c r="F15" s="153">
+        <v>1</v>
+      </c>
+      <c r="G15" s="153">
+        <v>1</v>
+      </c>
+      <c r="H15" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C16" s="152" t="s">
+        <v>602</v>
+      </c>
+      <c r="D16" s="153">
+        <v>0</v>
+      </c>
+      <c r="E16" s="153">
+        <v>0</v>
+      </c>
+      <c r="F16" s="153">
+        <v>1</v>
+      </c>
+      <c r="G16" s="153">
+        <v>1</v>
+      </c>
+      <c r="H16" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C17" s="152" t="s">
+        <v>603</v>
+      </c>
+      <c r="D17" s="153">
+        <v>0</v>
+      </c>
+      <c r="E17" s="153">
+        <v>35</v>
+      </c>
+      <c r="F17" s="153">
+        <v>1</v>
+      </c>
+      <c r="G17" s="153">
+        <v>1</v>
+      </c>
+      <c r="H17" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C18" s="152" t="s">
+        <v>562</v>
+      </c>
+      <c r="D18" s="153">
+        <v>0</v>
+      </c>
+      <c r="E18" s="153">
+        <v>0</v>
+      </c>
+      <c r="F18" s="153">
+        <v>1</v>
+      </c>
+      <c r="G18" s="153">
+        <v>1</v>
+      </c>
+      <c r="H18" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C19" s="152" t="s">
+        <v>563</v>
+      </c>
+      <c r="D19" s="153">
+        <v>0</v>
+      </c>
+      <c r="E19" s="153">
+        <v>35</v>
+      </c>
+      <c r="F19" s="153">
+        <v>1</v>
+      </c>
+      <c r="G19" s="153">
+        <v>1</v>
+      </c>
+      <c r="H19" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C20" s="152" t="s">
+        <v>570</v>
+      </c>
+      <c r="D20" s="153">
+        <v>0</v>
+      </c>
+      <c r="E20" s="153">
+        <v>0</v>
+      </c>
+      <c r="F20" s="153">
+        <v>1</v>
+      </c>
+      <c r="G20" s="153">
+        <v>1</v>
+      </c>
+      <c r="H20" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C21" s="152" t="s">
+        <v>571</v>
+      </c>
+      <c r="D21" s="153">
+        <v>0</v>
+      </c>
+      <c r="E21" s="153">
+        <v>35</v>
+      </c>
+      <c r="F21" s="153">
+        <v>1</v>
+      </c>
+      <c r="G21" s="153">
+        <v>1</v>
+      </c>
+      <c r="H21" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C22" s="152" t="s">
+        <v>592</v>
+      </c>
+      <c r="D22" s="153">
+        <v>0</v>
+      </c>
+      <c r="E22" s="153">
+        <v>0</v>
+      </c>
+      <c r="F22" s="153">
+        <v>1</v>
+      </c>
+      <c r="G22" s="153">
+        <v>1</v>
+      </c>
+      <c r="H22" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C23" s="152" t="s">
+        <v>593</v>
+      </c>
+      <c r="D23" s="153">
+        <v>0</v>
+      </c>
+      <c r="E23" s="153">
+        <v>35</v>
+      </c>
+      <c r="F23" s="153">
+        <v>1</v>
+      </c>
+      <c r="G23" s="153">
+        <v>1</v>
+      </c>
+      <c r="H23" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C24" s="152" t="s">
         <v>425</v>
       </c>
-      <c r="F3" s="110" t="s">
+      <c r="D24" s="153">
+        <v>0</v>
+      </c>
+      <c r="E24" s="153">
+        <v>0</v>
+      </c>
+      <c r="F24" s="153">
+        <v>0.67</v>
+      </c>
+      <c r="G24" s="153">
+        <v>0.67</v>
+      </c>
+      <c r="H24" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C25" s="152" t="s">
+        <v>429</v>
+      </c>
+      <c r="D25" s="153">
+        <v>0</v>
+      </c>
+      <c r="E25" s="153">
+        <v>35</v>
+      </c>
+      <c r="F25" s="153">
+        <v>1</v>
+      </c>
+      <c r="G25" s="153">
+        <v>1</v>
+      </c>
+      <c r="H25" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C26" s="152" t="s">
+        <v>430</v>
+      </c>
+      <c r="D26" s="153">
+        <v>0</v>
+      </c>
+      <c r="E26" s="153">
+        <v>35</v>
+      </c>
+      <c r="F26" s="153">
+        <v>1</v>
+      </c>
+      <c r="G26" s="153">
+        <v>1</v>
+      </c>
+      <c r="H26" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C27" s="152" t="s">
+        <v>568</v>
+      </c>
+      <c r="D27" s="153">
+        <v>0</v>
+      </c>
+      <c r="E27" s="153">
+        <v>0</v>
+      </c>
+      <c r="F27" s="153">
+        <v>1</v>
+      </c>
+      <c r="G27" s="153">
+        <v>1</v>
+      </c>
+      <c r="H27" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C28" s="152" t="s">
+        <v>569</v>
+      </c>
+      <c r="D28" s="153">
+        <v>0</v>
+      </c>
+      <c r="E28" s="153">
+        <v>35</v>
+      </c>
+      <c r="F28" s="153">
+        <v>1</v>
+      </c>
+      <c r="G28" s="153">
+        <v>1</v>
+      </c>
+      <c r="H28" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C29" s="152" t="s">
+        <v>432</v>
+      </c>
+      <c r="D29" s="153">
+        <v>0</v>
+      </c>
+      <c r="E29" s="153">
+        <v>0</v>
+      </c>
+      <c r="F29" s="153">
+        <v>1</v>
+      </c>
+      <c r="G29" s="153">
+        <v>1</v>
+      </c>
+      <c r="H29" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C30" s="152" t="s">
+        <v>433</v>
+      </c>
+      <c r="D30" s="153">
+        <v>0</v>
+      </c>
+      <c r="E30" s="153">
+        <v>35</v>
+      </c>
+      <c r="F30" s="153">
+        <v>1</v>
+      </c>
+      <c r="G30" s="153">
+        <v>1</v>
+      </c>
+      <c r="H30" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C31" s="152" t="s">
+        <v>434</v>
+      </c>
+      <c r="D31" s="153">
+        <v>0</v>
+      </c>
+      <c r="E31" s="153">
+        <v>0</v>
+      </c>
+      <c r="F31" s="153">
+        <v>1</v>
+      </c>
+      <c r="G31" s="153">
+        <v>1</v>
+      </c>
+      <c r="H31" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C32" s="152" t="s">
+        <v>435</v>
+      </c>
+      <c r="D32" s="153">
+        <v>0</v>
+      </c>
+      <c r="E32" s="153">
+        <v>35</v>
+      </c>
+      <c r="F32" s="153">
+        <v>1</v>
+      </c>
+      <c r="G32" s="153">
+        <v>1</v>
+      </c>
+      <c r="H32" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C33" s="152" t="s">
+        <v>436</v>
+      </c>
+      <c r="D33" s="153">
+        <v>0</v>
+      </c>
+      <c r="E33" s="153">
+        <v>0</v>
+      </c>
+      <c r="F33" s="153">
+        <v>1</v>
+      </c>
+      <c r="G33" s="153">
+        <v>1</v>
+      </c>
+      <c r="H33" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C34" s="152" t="s">
+        <v>437</v>
+      </c>
+      <c r="D34" s="153">
+        <v>0</v>
+      </c>
+      <c r="E34" s="153">
+        <v>35</v>
+      </c>
+      <c r="F34" s="153">
+        <v>1</v>
+      </c>
+      <c r="G34" s="153">
+        <v>1</v>
+      </c>
+      <c r="H34" s="153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C35" s="152" t="s">
+        <v>522</v>
+      </c>
+      <c r="D35" s="153">
+        <v>0</v>
+      </c>
+      <c r="E35" s="153">
+        <v>2</v>
+      </c>
+      <c r="F35" s="153">
+        <v>1</v>
+      </c>
+      <c r="G35" s="153">
+        <v>1</v>
+      </c>
+      <c r="H35" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="36" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C36" s="152" t="s">
+        <v>523</v>
+      </c>
+      <c r="D36" s="153">
+        <v>0</v>
+      </c>
+      <c r="E36" s="153">
+        <v>35</v>
+      </c>
+      <c r="F36" s="153">
+        <v>1</v>
+      </c>
+      <c r="G36" s="153">
+        <v>1</v>
+      </c>
+      <c r="H36" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="37" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C37" s="152" t="s">
+        <v>524</v>
+      </c>
+      <c r="D37" s="153">
+        <v>0</v>
+      </c>
+      <c r="E37" s="153">
+        <v>2</v>
+      </c>
+      <c r="F37" s="153">
+        <v>1</v>
+      </c>
+      <c r="G37" s="153">
+        <v>1</v>
+      </c>
+      <c r="H37" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="38" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C38" s="152" t="s">
+        <v>525</v>
+      </c>
+      <c r="D38" s="153">
+        <v>0</v>
+      </c>
+      <c r="E38" s="153">
+        <v>35</v>
+      </c>
+      <c r="F38" s="153">
+        <v>1</v>
+      </c>
+      <c r="G38" s="153">
+        <v>1</v>
+      </c>
+      <c r="H38" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="39" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C39" s="152" t="s">
+        <v>566</v>
+      </c>
+      <c r="D39" s="153">
+        <v>0</v>
+      </c>
+      <c r="E39" s="153">
+        <v>2</v>
+      </c>
+      <c r="F39" s="153">
+        <v>1</v>
+      </c>
+      <c r="G39" s="153">
+        <v>1</v>
+      </c>
+      <c r="H39" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="40" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C40" s="152" t="s">
+        <v>567</v>
+      </c>
+      <c r="D40" s="153">
+        <v>0</v>
+      </c>
+      <c r="E40" s="153">
+        <v>35</v>
+      </c>
+      <c r="F40" s="153">
+        <v>1</v>
+      </c>
+      <c r="G40" s="153">
+        <v>1</v>
+      </c>
+      <c r="H40" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="41" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C41" s="152" t="s">
+        <v>613</v>
+      </c>
+      <c r="D41" s="153">
+        <v>0</v>
+      </c>
+      <c r="E41" s="153">
+        <v>2</v>
+      </c>
+      <c r="F41" s="153">
+        <v>1</v>
+      </c>
+      <c r="G41" s="153">
+        <v>1</v>
+      </c>
+      <c r="H41" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="42" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C42" s="152" t="s">
+        <v>614</v>
+      </c>
+      <c r="D42" s="153">
+        <v>0</v>
+      </c>
+      <c r="E42" s="153">
+        <v>35</v>
+      </c>
+      <c r="F42" s="153">
+        <v>1</v>
+      </c>
+      <c r="G42" s="153">
+        <v>1</v>
+      </c>
+      <c r="H42" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="43" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C43" s="152" t="s">
+        <v>615</v>
+      </c>
+      <c r="D43" s="153">
+        <v>0</v>
+      </c>
+      <c r="E43" s="153">
+        <v>2</v>
+      </c>
+      <c r="F43" s="153">
+        <v>1</v>
+      </c>
+      <c r="G43" s="153">
+        <v>1</v>
+      </c>
+      <c r="H43" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="44" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C44" s="152" t="s">
+        <v>616</v>
+      </c>
+      <c r="D44" s="153">
+        <v>0</v>
+      </c>
+      <c r="E44" s="153">
+        <v>35</v>
+      </c>
+      <c r="F44" s="153">
+        <v>1</v>
+      </c>
+      <c r="G44" s="153">
+        <v>1</v>
+      </c>
+      <c r="H44" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="45" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C45" s="152" t="s">
+        <v>617</v>
+      </c>
+      <c r="D45" s="153">
+        <v>0</v>
+      </c>
+      <c r="E45" s="153">
+        <v>2</v>
+      </c>
+      <c r="F45" s="153">
+        <v>1</v>
+      </c>
+      <c r="G45" s="153">
+        <v>1</v>
+      </c>
+      <c r="H45" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="46" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C46" s="152" t="s">
+        <v>618</v>
+      </c>
+      <c r="D46" s="153">
+        <v>0</v>
+      </c>
+      <c r="E46" s="153">
+        <v>35</v>
+      </c>
+      <c r="F46" s="153">
+        <v>1</v>
+      </c>
+      <c r="G46" s="153">
+        <v>1</v>
+      </c>
+      <c r="H46" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="47" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C47" s="152" t="s">
+        <v>619</v>
+      </c>
+      <c r="D47" s="153">
+        <v>0</v>
+      </c>
+      <c r="E47" s="153">
+        <v>2</v>
+      </c>
+      <c r="F47" s="153">
+        <v>1</v>
+      </c>
+      <c r="G47" s="153">
+        <v>1</v>
+      </c>
+      <c r="H47" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="48" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C48" s="152" t="s">
+        <v>620</v>
+      </c>
+      <c r="D48" s="153">
+        <v>0</v>
+      </c>
+      <c r="E48" s="153">
+        <v>35</v>
+      </c>
+      <c r="F48" s="153">
+        <v>1</v>
+      </c>
+      <c r="G48" s="153">
+        <v>1</v>
+      </c>
+      <c r="H48" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="49" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C49" s="152" t="s">
+        <v>621</v>
+      </c>
+      <c r="D49" s="153">
+        <v>0</v>
+      </c>
+      <c r="E49" s="153">
+        <v>2</v>
+      </c>
+      <c r="F49" s="153">
+        <v>1</v>
+      </c>
+      <c r="G49" s="153">
+        <v>1</v>
+      </c>
+      <c r="H49" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="50" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C50" s="152" t="s">
+        <v>622</v>
+      </c>
+      <c r="D50" s="153">
+        <v>0</v>
+      </c>
+      <c r="E50" s="153">
+        <v>35</v>
+      </c>
+      <c r="F50" s="153">
+        <v>1</v>
+      </c>
+      <c r="G50" s="153">
+        <v>1</v>
+      </c>
+      <c r="H50" s="153">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="51" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C51" s="152" t="s">
         <v>426</v>
       </c>
-      <c r="G3" s="110" t="s">
-        <v>427</v>
-      </c>
-      <c r="H3" s="110" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C4" s="154" t="s">
-        <v>429</v>
-      </c>
-      <c r="D4" s="155">
-        <v>0</v>
-      </c>
-      <c r="E4" s="155">
-        <v>0</v>
-      </c>
-      <c r="F4" s="155">
+      <c r="D51" s="153">
+        <v>0</v>
+      </c>
+      <c r="E51" s="153">
+        <v>0</v>
+      </c>
+      <c r="F51" s="153">
         <v>1</v>
       </c>
-      <c r="G4" s="155">
+      <c r="G51" s="153">
         <v>1</v>
       </c>
-      <c r="H4" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C5" s="154" t="s">
-        <v>433</v>
-      </c>
-      <c r="D5" s="155">
-        <v>0</v>
-      </c>
-      <c r="E5" s="155">
-        <v>35</v>
-      </c>
-      <c r="F5" s="155">
-        <v>1</v>
-      </c>
-      <c r="G5" s="155">
-        <v>1</v>
-      </c>
-      <c r="H5" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C6" s="154" t="s">
-        <v>603</v>
-      </c>
-      <c r="D6" s="155">
-        <v>0</v>
-      </c>
-      <c r="E6" s="155">
-        <v>0</v>
-      </c>
-      <c r="F6" s="155">
-        <v>1</v>
-      </c>
-      <c r="G6" s="155">
-        <v>1</v>
-      </c>
-      <c r="H6" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C7" s="154" t="s">
-        <v>604</v>
-      </c>
-      <c r="D7" s="155">
-        <v>0</v>
-      </c>
-      <c r="E7" s="155">
-        <v>35</v>
-      </c>
-      <c r="F7" s="155">
-        <v>1</v>
-      </c>
-      <c r="G7" s="155">
-        <v>1</v>
-      </c>
-      <c r="H7" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C8" s="154" t="s">
-        <v>565</v>
-      </c>
-      <c r="D8" s="155">
-        <v>0</v>
-      </c>
-      <c r="E8" s="155">
-        <v>0</v>
-      </c>
-      <c r="F8" s="155">
-        <v>1</v>
-      </c>
-      <c r="G8" s="155">
-        <v>1</v>
-      </c>
-      <c r="H8" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C9" s="154" t="s">
-        <v>566</v>
-      </c>
-      <c r="D9" s="155">
-        <v>0</v>
-      </c>
-      <c r="E9" s="155">
-        <v>35</v>
-      </c>
-      <c r="F9" s="155">
-        <v>1</v>
-      </c>
-      <c r="G9" s="155">
-        <v>1</v>
-      </c>
-      <c r="H9" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C10" s="154" t="s">
-        <v>605</v>
-      </c>
-      <c r="D10" s="155">
-        <v>0</v>
-      </c>
-      <c r="E10" s="155">
-        <v>0</v>
-      </c>
-      <c r="F10" s="155">
-        <v>1</v>
-      </c>
-      <c r="G10" s="155">
-        <v>1</v>
-      </c>
-      <c r="H10" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C11" s="154" t="s">
-        <v>606</v>
-      </c>
-      <c r="D11" s="155">
-        <v>0</v>
-      </c>
-      <c r="E11" s="155">
-        <v>35</v>
-      </c>
-      <c r="F11" s="155">
-        <v>1</v>
-      </c>
-      <c r="G11" s="155">
-        <v>1</v>
-      </c>
-      <c r="H11" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C12" s="154" t="s">
-        <v>569</v>
-      </c>
-      <c r="D12" s="155">
-        <v>0</v>
-      </c>
-      <c r="E12" s="155">
-        <v>0</v>
-      </c>
-      <c r="F12" s="155">
-        <v>1</v>
-      </c>
-      <c r="G12" s="155">
-        <v>1</v>
-      </c>
-      <c r="H12" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C13" s="154" t="s">
-        <v>570</v>
-      </c>
-      <c r="D13" s="155">
-        <v>0</v>
-      </c>
-      <c r="E13" s="155">
-        <v>35</v>
-      </c>
-      <c r="F13" s="155">
-        <v>1</v>
-      </c>
-      <c r="G13" s="155">
-        <v>1</v>
-      </c>
-      <c r="H13" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C14" s="154" t="s">
-        <v>607</v>
-      </c>
-      <c r="D14" s="155">
-        <v>0</v>
-      </c>
-      <c r="E14" s="155">
-        <v>0</v>
-      </c>
-      <c r="F14" s="155">
-        <v>1</v>
-      </c>
-      <c r="G14" s="155">
-        <v>1</v>
-      </c>
-      <c r="H14" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C15" s="154" t="s">
-        <v>608</v>
-      </c>
-      <c r="D15" s="155">
-        <v>0</v>
-      </c>
-      <c r="E15" s="155">
-        <v>35</v>
-      </c>
-      <c r="F15" s="155">
-        <v>1</v>
-      </c>
-      <c r="G15" s="155">
-        <v>1</v>
-      </c>
-      <c r="H15" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C16" s="154" t="s">
-        <v>609</v>
-      </c>
-      <c r="D16" s="155">
-        <v>0</v>
-      </c>
-      <c r="E16" s="155">
-        <v>0</v>
-      </c>
-      <c r="F16" s="155">
-        <v>1</v>
-      </c>
-      <c r="G16" s="155">
-        <v>1</v>
-      </c>
-      <c r="H16" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C17" s="154" t="s">
-        <v>610</v>
-      </c>
-      <c r="D17" s="155">
-        <v>0</v>
-      </c>
-      <c r="E17" s="155">
-        <v>35</v>
-      </c>
-      <c r="F17" s="155">
-        <v>1</v>
-      </c>
-      <c r="G17" s="155">
-        <v>1</v>
-      </c>
-      <c r="H17" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C18" s="154" t="s">
-        <v>567</v>
-      </c>
-      <c r="D18" s="155">
-        <v>0</v>
-      </c>
-      <c r="E18" s="155">
-        <v>0</v>
-      </c>
-      <c r="F18" s="155">
-        <v>1</v>
-      </c>
-      <c r="G18" s="155">
-        <v>1</v>
-      </c>
-      <c r="H18" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C19" s="154" t="s">
-        <v>568</v>
-      </c>
-      <c r="D19" s="155">
-        <v>0</v>
-      </c>
-      <c r="E19" s="155">
-        <v>35</v>
-      </c>
-      <c r="F19" s="155">
-        <v>1</v>
-      </c>
-      <c r="G19" s="155">
-        <v>1</v>
-      </c>
-      <c r="H19" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C20" s="154" t="s">
-        <v>575</v>
-      </c>
-      <c r="D20" s="155">
-        <v>0</v>
-      </c>
-      <c r="E20" s="155">
-        <v>0</v>
-      </c>
-      <c r="F20" s="155">
-        <v>1</v>
-      </c>
-      <c r="G20" s="155">
-        <v>1</v>
-      </c>
-      <c r="H20" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C21" s="154" t="s">
-        <v>576</v>
-      </c>
-      <c r="D21" s="155">
-        <v>0</v>
-      </c>
-      <c r="E21" s="155">
-        <v>35</v>
-      </c>
-      <c r="F21" s="155">
-        <v>1</v>
-      </c>
-      <c r="G21" s="155">
-        <v>1</v>
-      </c>
-      <c r="H21" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C22" s="154" t="s">
-        <v>597</v>
-      </c>
-      <c r="D22" s="155">
-        <v>0</v>
-      </c>
-      <c r="E22" s="155">
-        <v>0</v>
-      </c>
-      <c r="F22" s="155">
-        <v>1</v>
-      </c>
-      <c r="G22" s="155">
-        <v>1</v>
-      </c>
-      <c r="H22" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C23" s="154" t="s">
-        <v>598</v>
-      </c>
-      <c r="D23" s="155">
-        <v>0</v>
-      </c>
-      <c r="E23" s="155">
-        <v>35</v>
-      </c>
-      <c r="F23" s="155">
-        <v>1</v>
-      </c>
-      <c r="G23" s="155">
-        <v>1</v>
-      </c>
-      <c r="H23" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C24" s="154" t="s">
-        <v>430</v>
-      </c>
-      <c r="D24" s="155">
-        <v>0</v>
-      </c>
-      <c r="E24" s="155">
-        <v>0</v>
-      </c>
-      <c r="F24" s="155">
-        <v>0.67</v>
-      </c>
-      <c r="G24" s="155">
-        <v>0.67</v>
-      </c>
-      <c r="H24" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C25" s="154" t="s">
-        <v>434</v>
-      </c>
-      <c r="D25" s="155">
-        <v>0</v>
-      </c>
-      <c r="E25" s="155">
-        <v>35</v>
-      </c>
-      <c r="F25" s="155">
-        <v>1</v>
-      </c>
-      <c r="G25" s="155">
-        <v>1</v>
-      </c>
-      <c r="H25" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C26" s="154" t="s">
-        <v>435</v>
-      </c>
-      <c r="D26" s="155">
-        <v>0</v>
-      </c>
-      <c r="E26" s="155">
-        <v>35</v>
-      </c>
-      <c r="F26" s="155">
-        <v>1</v>
-      </c>
-      <c r="G26" s="155">
-        <v>1</v>
-      </c>
-      <c r="H26" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C27" s="154" t="s">
-        <v>573</v>
-      </c>
-      <c r="D27" s="155">
-        <v>0</v>
-      </c>
-      <c r="E27" s="155">
-        <v>0</v>
-      </c>
-      <c r="F27" s="155">
-        <v>1</v>
-      </c>
-      <c r="G27" s="155">
-        <v>1</v>
-      </c>
-      <c r="H27" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C28" s="154" t="s">
-        <v>574</v>
-      </c>
-      <c r="D28" s="155">
-        <v>0</v>
-      </c>
-      <c r="E28" s="155">
-        <v>35</v>
-      </c>
-      <c r="F28" s="155">
-        <v>1</v>
-      </c>
-      <c r="G28" s="155">
-        <v>1</v>
-      </c>
-      <c r="H28" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C29" s="154" t="s">
-        <v>437</v>
-      </c>
-      <c r="D29" s="155">
-        <v>0</v>
-      </c>
-      <c r="E29" s="155">
-        <v>0</v>
-      </c>
-      <c r="F29" s="155">
-        <v>1</v>
-      </c>
-      <c r="G29" s="155">
-        <v>1</v>
-      </c>
-      <c r="H29" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C30" s="154" t="s">
-        <v>438</v>
-      </c>
-      <c r="D30" s="155">
-        <v>0</v>
-      </c>
-      <c r="E30" s="155">
-        <v>35</v>
-      </c>
-      <c r="F30" s="155">
-        <v>1</v>
-      </c>
-      <c r="G30" s="155">
-        <v>1</v>
-      </c>
-      <c r="H30" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C31" s="154" t="s">
-        <v>439</v>
-      </c>
-      <c r="D31" s="155">
-        <v>0</v>
-      </c>
-      <c r="E31" s="155">
-        <v>0</v>
-      </c>
-      <c r="F31" s="155">
-        <v>1</v>
-      </c>
-      <c r="G31" s="155">
-        <v>1</v>
-      </c>
-      <c r="H31" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C32" s="154" t="s">
-        <v>440</v>
-      </c>
-      <c r="D32" s="155">
-        <v>0</v>
-      </c>
-      <c r="E32" s="155">
-        <v>35</v>
-      </c>
-      <c r="F32" s="155">
-        <v>1</v>
-      </c>
-      <c r="G32" s="155">
-        <v>1</v>
-      </c>
-      <c r="H32" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C33" s="154" t="s">
-        <v>441</v>
-      </c>
-      <c r="D33" s="155">
-        <v>0</v>
-      </c>
-      <c r="E33" s="155">
-        <v>0</v>
-      </c>
-      <c r="F33" s="155">
-        <v>1</v>
-      </c>
-      <c r="G33" s="155">
-        <v>1</v>
-      </c>
-      <c r="H33" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C34" s="154" t="s">
-        <v>442</v>
-      </c>
-      <c r="D34" s="155">
-        <v>0</v>
-      </c>
-      <c r="E34" s="155">
-        <v>35</v>
-      </c>
-      <c r="F34" s="155">
-        <v>1</v>
-      </c>
-      <c r="G34" s="155">
-        <v>1</v>
-      </c>
-      <c r="H34" s="155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C35" s="154" t="s">
-        <v>527</v>
-      </c>
-      <c r="D35" s="155">
-        <v>0</v>
-      </c>
-      <c r="E35" s="155">
-        <v>2</v>
-      </c>
-      <c r="F35" s="155">
-        <v>1</v>
-      </c>
-      <c r="G35" s="155">
-        <v>1</v>
-      </c>
-      <c r="H35" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="36" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C36" s="154" t="s">
-        <v>528</v>
-      </c>
-      <c r="D36" s="155">
-        <v>0</v>
-      </c>
-      <c r="E36" s="155">
-        <v>35</v>
-      </c>
-      <c r="F36" s="155">
-        <v>1</v>
-      </c>
-      <c r="G36" s="155">
-        <v>1</v>
-      </c>
-      <c r="H36" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="37" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C37" s="154" t="s">
-        <v>529</v>
-      </c>
-      <c r="D37" s="155">
-        <v>0</v>
-      </c>
-      <c r="E37" s="155">
-        <v>2</v>
-      </c>
-      <c r="F37" s="155">
-        <v>1</v>
-      </c>
-      <c r="G37" s="155">
-        <v>1</v>
-      </c>
-      <c r="H37" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="38" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C38" s="154" t="s">
-        <v>530</v>
-      </c>
-      <c r="D38" s="155">
-        <v>0</v>
-      </c>
-      <c r="E38" s="155">
-        <v>35</v>
-      </c>
-      <c r="F38" s="155">
-        <v>1</v>
-      </c>
-      <c r="G38" s="155">
-        <v>1</v>
-      </c>
-      <c r="H38" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="39" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C39" s="154" t="s">
-        <v>571</v>
-      </c>
-      <c r="D39" s="155">
-        <v>0</v>
-      </c>
-      <c r="E39" s="155">
-        <v>2</v>
-      </c>
-      <c r="F39" s="155">
-        <v>1</v>
-      </c>
-      <c r="G39" s="155">
-        <v>1</v>
-      </c>
-      <c r="H39" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="40" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C40" s="154" t="s">
-        <v>572</v>
-      </c>
-      <c r="D40" s="155">
-        <v>0</v>
-      </c>
-      <c r="E40" s="155">
-        <v>35</v>
-      </c>
-      <c r="F40" s="155">
-        <v>1</v>
-      </c>
-      <c r="G40" s="155">
-        <v>1</v>
-      </c>
-      <c r="H40" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="41" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C41" s="154" t="s">
-        <v>620</v>
-      </c>
-      <c r="D41" s="155">
-        <v>0</v>
-      </c>
-      <c r="E41" s="155">
-        <v>2</v>
-      </c>
-      <c r="F41" s="155">
-        <v>1</v>
-      </c>
-      <c r="G41" s="155">
-        <v>1</v>
-      </c>
-      <c r="H41" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="42" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C42" s="154" t="s">
-        <v>621</v>
-      </c>
-      <c r="D42" s="155">
-        <v>0</v>
-      </c>
-      <c r="E42" s="155">
-        <v>35</v>
-      </c>
-      <c r="F42" s="155">
-        <v>1</v>
-      </c>
-      <c r="G42" s="155">
-        <v>1</v>
-      </c>
-      <c r="H42" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="43" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C43" s="154" t="s">
-        <v>622</v>
-      </c>
-      <c r="D43" s="155">
-        <v>0</v>
-      </c>
-      <c r="E43" s="155">
-        <v>2</v>
-      </c>
-      <c r="F43" s="155">
-        <v>1</v>
-      </c>
-      <c r="G43" s="155">
-        <v>1</v>
-      </c>
-      <c r="H43" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="44" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C44" s="154" t="s">
-        <v>623</v>
-      </c>
-      <c r="D44" s="155">
-        <v>0</v>
-      </c>
-      <c r="E44" s="155">
-        <v>35</v>
-      </c>
-      <c r="F44" s="155">
-        <v>1</v>
-      </c>
-      <c r="G44" s="155">
-        <v>1</v>
-      </c>
-      <c r="H44" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="45" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C45" s="154" t="s">
-        <v>624</v>
-      </c>
-      <c r="D45" s="155">
-        <v>0</v>
-      </c>
-      <c r="E45" s="155">
-        <v>2</v>
-      </c>
-      <c r="F45" s="155">
-        <v>1</v>
-      </c>
-      <c r="G45" s="155">
-        <v>1</v>
-      </c>
-      <c r="H45" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="46" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C46" s="154" t="s">
-        <v>625</v>
-      </c>
-      <c r="D46" s="155">
-        <v>0</v>
-      </c>
-      <c r="E46" s="155">
-        <v>35</v>
-      </c>
-      <c r="F46" s="155">
-        <v>1</v>
-      </c>
-      <c r="G46" s="155">
-        <v>1</v>
-      </c>
-      <c r="H46" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="47" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C47" s="154" t="s">
-        <v>626</v>
-      </c>
-      <c r="D47" s="155">
-        <v>0</v>
-      </c>
-      <c r="E47" s="155">
-        <v>2</v>
-      </c>
-      <c r="F47" s="155">
-        <v>1</v>
-      </c>
-      <c r="G47" s="155">
-        <v>1</v>
-      </c>
-      <c r="H47" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="48" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C48" s="154" t="s">
-        <v>627</v>
-      </c>
-      <c r="D48" s="155">
-        <v>0</v>
-      </c>
-      <c r="E48" s="155">
-        <v>35</v>
-      </c>
-      <c r="F48" s="155">
-        <v>1</v>
-      </c>
-      <c r="G48" s="155">
-        <v>1</v>
-      </c>
-      <c r="H48" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="49" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C49" s="154" t="s">
-        <v>628</v>
-      </c>
-      <c r="D49" s="155">
-        <v>0</v>
-      </c>
-      <c r="E49" s="155">
-        <v>2</v>
-      </c>
-      <c r="F49" s="155">
-        <v>1</v>
-      </c>
-      <c r="G49" s="155">
-        <v>1</v>
-      </c>
-      <c r="H49" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="50" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C50" s="154" t="s">
-        <v>629</v>
-      </c>
-      <c r="D50" s="155">
-        <v>0</v>
-      </c>
-      <c r="E50" s="155">
-        <v>35</v>
-      </c>
-      <c r="F50" s="155">
-        <v>1</v>
-      </c>
-      <c r="G50" s="155">
-        <v>1</v>
-      </c>
-      <c r="H50" s="155">
-        <v>4.71</v>
-      </c>
-    </row>
-    <row r="51" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C51" s="154" t="s">
-        <v>431</v>
-      </c>
-      <c r="D51" s="155">
-        <v>0</v>
-      </c>
-      <c r="E51" s="155">
-        <v>0</v>
-      </c>
-      <c r="F51" s="155">
-        <v>1</v>
-      </c>
-      <c r="G51" s="155">
-        <v>1</v>
-      </c>
-      <c r="H51" s="155">
+      <c r="H51" s="153">
         <v>0</v>
       </c>
     </row>
@@ -20199,47 +20313,47 @@
         <v>361</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>362</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>364</v>
+        <v>646</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>366</v>
+        <v>647</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>368</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>372</v>
+        <v>645</v>
       </c>
     </row>
   </sheetData>
@@ -20260,7 +20374,7 @@
         <v>175</v>
       </c>
       <c r="B1" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -20329,137 +20443,137 @@
         <v>328</v>
       </c>
       <c r="I7" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I8" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="26" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I26" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="27" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I27" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="K27" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="28" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J28" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="K28" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="29" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J29" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="K29" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="30" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I30" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="K30" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="31" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J31" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="K31" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="32" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J32" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="K32" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="33" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J33" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="K33" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="34" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J34" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K34" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="35" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J35" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="K35" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="36" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I36" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="K36" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="37" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J37" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="K37" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="38" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J38" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="K38" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="39" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J39" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="K39" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="40" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J40" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K40" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="41" spans="9:11" x14ac:dyDescent="0.25">
       <c r="J41" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="K41" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -20469,9 +20583,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A1BDDE-60BA-44D5-BCC5-6893FF63103C}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="15.28515625" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -20487,16 +20602,32 @@
       <c r="A2" t="s">
         <v>171</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B2" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B4" t="str">
         <f>"&lt;zsetformulatocell toSheet=[BD]  toCell=[A2] formula=[SUM(B4:B5)]"</f>
         <v>&lt;zsetformulatocell toSheet=[BD]  toCell=[A2] formula=[SUM(B4:B5)]</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>172</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B5" t="s">
         <v>174</v>
       </c>
     </row>
@@ -20507,7 +20638,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5946069B-84EF-483E-B2A7-62FC8EF81A67}">
-  <dimension ref="A3:BP11"/>
+  <dimension ref="A3:BX11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -20534,35 +20665,35 @@
     <col min="33" max="33" width="3.7109375" customWidth="1"/>
     <col min="34" max="38" width="12.7109375" customWidth="1"/>
     <col min="39" max="39" width="3.7109375" customWidth="1"/>
-    <col min="40" max="42" width="12.7109375" customWidth="1"/>
-    <col min="43" max="51" width="14.140625" customWidth="1"/>
-    <col min="52" max="53" width="16" customWidth="1"/>
-    <col min="54" max="67" width="12.7109375" customWidth="1"/>
+    <col min="40" max="45" width="12.7109375" customWidth="1"/>
+    <col min="46" max="54" width="14.140625" customWidth="1"/>
+    <col min="55" max="56" width="16" customWidth="1"/>
+    <col min="57" max="75" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
-      <c r="D3" s="240" t="s">
+    <row r="3" spans="1:76" x14ac:dyDescent="0.25">
+      <c r="D3" s="289" t="s">
         <v>316</v>
       </c>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
-    </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="E3" s="289"/>
+      <c r="F3" s="289"/>
+    </row>
+    <row r="4" spans="1:76" x14ac:dyDescent="0.25">
       <c r="D4" s="63" t="s">
         <v>317</v>
       </c>
       <c r="E4" s="64"/>
-      <c r="F4" s="67" t="s">
+      <c r="F4" s="66" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>COLUMN(A7)-1</f>
         <v>0</v>
       </c>
       <c r="B7">
-        <f t="shared" ref="B7:BP7" si="0">COLUMN(B7)-1</f>
+        <f t="shared" ref="B7:BX7" si="0">COLUMN(B7)-1</f>
         <v>1</v>
       </c>
       <c r="C7">
@@ -20697,10 +20828,54 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
+      <c r="AJ7">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="AK7">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="AL7">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="AM7">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="AN7">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="AO7">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
       <c r="AQ7">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
+      <c r="AR7">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="AS7">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="AT7">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="AU7">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
       <c r="AV7">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -20733,19 +20908,19 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="BD7" s="79">
+      <c r="BD7">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="BE7" s="79">
+      <c r="BE7">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="BF7" s="79">
+      <c r="BF7">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="BG7" s="79">
+      <c r="BG7">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
@@ -20761,150 +20936,226 @@
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
+      <c r="BK7">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="BL7">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="BM7">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="BN7">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="BO7">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
       <c r="BP7">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-    </row>
-    <row r="8" spans="1:68" ht="135" x14ac:dyDescent="0.25">
-      <c r="B8" s="211"/>
-      <c r="C8" s="239" t="s">
+      <c r="BQ7">
+        <f t="shared" si="0"/>
+        <v>68</v>
+      </c>
+      <c r="BR7">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+      <c r="BS7">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="BT7">
+        <f t="shared" si="0"/>
+        <v>71</v>
+      </c>
+      <c r="BU7">
+        <f t="shared" si="0"/>
+        <v>72</v>
+      </c>
+      <c r="BV7">
+        <f t="shared" si="0"/>
+        <v>73</v>
+      </c>
+      <c r="BW7">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="BX7">
+        <f t="shared" si="0"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:76" ht="135" x14ac:dyDescent="0.25">
+      <c r="B8" s="209"/>
+      <c r="C8" s="288" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="239"/>
-      <c r="E8" s="239"/>
-      <c r="F8" s="241" t="s">
+      <c r="D8" s="288"/>
+      <c r="E8" s="288"/>
+      <c r="F8" s="290" t="s">
         <v>323</v>
       </c>
-      <c r="G8" s="241"/>
-      <c r="H8" s="241"/>
-      <c r="I8" s="239" t="s">
+      <c r="G8" s="290"/>
+      <c r="H8" s="290"/>
+      <c r="I8" s="288" t="s">
         <v>165</v>
       </c>
-      <c r="J8" s="239"/>
-      <c r="K8" s="239"/>
-      <c r="L8" s="239" t="s">
+      <c r="J8" s="288"/>
+      <c r="K8" s="288"/>
+      <c r="L8" s="288" t="s">
         <v>178</v>
       </c>
-      <c r="M8" s="239"/>
-      <c r="N8" s="239"/>
-      <c r="O8" s="239" t="s">
+      <c r="M8" s="288"/>
+      <c r="N8" s="288"/>
+      <c r="O8" s="288" t="s">
         <v>7</v>
       </c>
-      <c r="P8" s="239"/>
-      <c r="Q8" s="239"/>
-      <c r="R8" s="239" t="s">
+      <c r="P8" s="288"/>
+      <c r="Q8" s="288"/>
+      <c r="R8" s="288" t="s">
         <v>179</v>
       </c>
-      <c r="S8" s="239"/>
-      <c r="T8" s="239"/>
-      <c r="U8" s="239" t="s">
+      <c r="S8" s="288"/>
+      <c r="T8" s="288"/>
+      <c r="U8" s="288" t="s">
         <v>166</v>
       </c>
-      <c r="V8" s="239"/>
-      <c r="W8" s="239"/>
-      <c r="X8" s="239" t="s">
+      <c r="V8" s="288"/>
+      <c r="W8" s="288"/>
+      <c r="X8" s="288" t="s">
         <v>181</v>
       </c>
-      <c r="Y8" s="239"/>
-      <c r="Z8" s="239"/>
-      <c r="AA8" s="239" t="s">
+      <c r="Y8" s="288"/>
+      <c r="Z8" s="288"/>
+      <c r="AA8" s="288" t="s">
         <v>182</v>
       </c>
-      <c r="AB8" s="239"/>
-      <c r="AC8" s="239"/>
-      <c r="AD8" s="239" t="s">
+      <c r="AB8" s="288"/>
+      <c r="AC8" s="288"/>
+      <c r="AD8" s="288" t="s">
         <v>3</v>
       </c>
-      <c r="AE8" s="239"/>
-      <c r="AF8" s="239"/>
-      <c r="AG8" s="239" t="s">
+      <c r="AE8" s="288"/>
+      <c r="AF8" s="288"/>
+      <c r="AG8" s="288" t="s">
+        <v>375</v>
+      </c>
+      <c r="AH8" s="288"/>
+      <c r="AI8" s="288"/>
+      <c r="AJ8" s="288" t="s">
+        <v>594</v>
+      </c>
+      <c r="AK8" s="288"/>
+      <c r="AL8" s="288"/>
+      <c r="AM8" s="288" t="s">
+        <v>590</v>
+      </c>
+      <c r="AN8" s="288"/>
+      <c r="AO8" s="288"/>
+      <c r="AP8" s="99" t="s">
+        <v>414</v>
+      </c>
+      <c r="AQ8" s="288" t="s">
+        <v>632</v>
+      </c>
+      <c r="AR8" s="288"/>
+      <c r="AS8" s="288"/>
+      <c r="AT8" s="80" t="s">
+        <v>325</v>
+      </c>
+      <c r="AU8" s="80" t="s">
+        <v>465</v>
+      </c>
+      <c r="AV8" s="80" t="s">
+        <v>466</v>
+      </c>
+      <c r="AW8" s="80" t="s">
+        <v>467</v>
+      </c>
+      <c r="AX8" s="80" t="s">
+        <v>589</v>
+      </c>
+      <c r="AY8" s="83" t="s">
         <v>380</v>
       </c>
-      <c r="AH8" s="239"/>
-      <c r="AI8" s="239"/>
-      <c r="AJ8" s="239" t="s">
-        <v>599</v>
-      </c>
-      <c r="AK8" s="239"/>
-      <c r="AL8" s="239"/>
-      <c r="AM8" s="239" t="s">
-        <v>595</v>
-      </c>
-      <c r="AN8" s="239"/>
-      <c r="AO8" s="239"/>
-      <c r="AP8" s="101" t="s">
-        <v>419</v>
-      </c>
-      <c r="AQ8" s="82" t="s">
-        <v>325</v>
-      </c>
-      <c r="AR8" s="82" t="s">
-        <v>470</v>
-      </c>
-      <c r="AS8" s="82" t="s">
-        <v>471</v>
-      </c>
-      <c r="AT8" s="82" t="s">
-        <v>472</v>
-      </c>
-      <c r="AU8" s="82" t="s">
-        <v>594</v>
-      </c>
-      <c r="AV8" s="85" t="s">
-        <v>385</v>
-      </c>
-      <c r="AW8" s="85" t="s">
-        <v>386</v>
-      </c>
-      <c r="AX8" s="85" t="s">
+      <c r="AZ8" s="83" t="s">
+        <v>381</v>
+      </c>
+      <c r="BA8" s="83" t="s">
+        <v>382</v>
+      </c>
+      <c r="BB8" s="86" t="s">
+        <v>383</v>
+      </c>
+      <c r="BC8" s="80" t="s">
+        <v>326</v>
+      </c>
+      <c r="BD8" s="80" t="s">
+        <v>327</v>
+      </c>
+      <c r="BE8" s="78" t="s">
+        <v>185</v>
+      </c>
+      <c r="BF8" s="79" t="s">
+        <v>317</v>
+      </c>
+      <c r="BG8" s="93" t="s">
+        <v>389</v>
+      </c>
+      <c r="BH8" s="93" t="s">
+        <v>390</v>
+      </c>
+      <c r="BI8" s="86" t="s">
         <v>387</v>
       </c>
-      <c r="AY8" s="88" t="s">
+      <c r="BJ8" s="92" t="s">
         <v>388</v>
       </c>
-      <c r="AZ8" s="82" t="s">
-        <v>326</v>
-      </c>
-      <c r="BA8" s="82" t="s">
-        <v>327</v>
-      </c>
-      <c r="BB8" s="80" t="s">
-        <v>185</v>
-      </c>
-      <c r="BC8" s="81" t="s">
-        <v>317</v>
-      </c>
-      <c r="BD8" s="95" t="s">
-        <v>394</v>
-      </c>
-      <c r="BE8" s="95" t="s">
-        <v>395</v>
-      </c>
-      <c r="BF8" s="88" t="s">
-        <v>392</v>
-      </c>
-      <c r="BG8" s="94" t="s">
-        <v>393</v>
-      </c>
-      <c r="BH8" s="80" t="s">
+      <c r="BK8" s="78" t="s">
         <v>186</v>
       </c>
-      <c r="BI8" s="80" t="s">
+      <c r="BL8" s="78" t="s">
         <v>187</v>
       </c>
-      <c r="BJ8" s="80" t="s">
+      <c r="BM8" s="78" t="s">
         <v>188</v>
       </c>
-      <c r="BK8" s="80" t="s">
-        <v>381</v>
-      </c>
-      <c r="BL8" s="66"/>
-      <c r="BM8" s="66"/>
-      <c r="BN8" s="66"/>
-      <c r="BO8" s="66"/>
-    </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BN8" s="78" t="s">
+        <v>376</v>
+      </c>
+      <c r="BO8" s="217" t="s">
+        <v>633</v>
+      </c>
+      <c r="BP8" s="93" t="s">
+        <v>634</v>
+      </c>
+      <c r="BQ8" s="218"/>
+      <c r="BR8" s="218"/>
+      <c r="BS8" s="220" t="s">
+        <v>639</v>
+      </c>
+      <c r="BT8" s="220" t="s">
+        <v>640</v>
+      </c>
+      <c r="BU8" s="220" t="s">
+        <v>641</v>
+      </c>
+      <c r="BV8" s="220" t="s">
+        <v>642</v>
+      </c>
+      <c r="BW8" s="220" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="9" spans="1:76" x14ac:dyDescent="0.25">
       <c r="B9" s="47"/>
       <c r="C9" s="47" t="s">
         <v>164</v>
@@ -20912,7 +21163,7 @@
       <c r="D9" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="E9" s="90" t="s">
+      <c r="E9" s="88" t="s">
         <v>163</v>
       </c>
       <c r="F9" s="47" t="s">
@@ -20930,7 +21181,7 @@
       <c r="J9" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="K9" s="90" t="s">
+      <c r="K9" s="88" t="s">
         <v>163</v>
       </c>
       <c r="L9" s="47" t="s">
@@ -20939,7 +21190,7 @@
       <c r="M9" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="N9" s="90" t="s">
+      <c r="N9" s="88" t="s">
         <v>163</v>
       </c>
       <c r="O9" s="47" t="s">
@@ -20957,7 +21208,7 @@
       <c r="S9" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="T9" s="90" t="s">
+      <c r="T9" s="88" t="s">
         <v>163</v>
       </c>
       <c r="U9" s="47" t="s">
@@ -21020,60 +21271,74 @@
       <c r="AN9" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="AO9" s="90" t="s">
+      <c r="AO9" s="88" t="s">
         <v>163</v>
       </c>
       <c r="AP9" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="AQ9" s="68"/>
-      <c r="AR9" s="68"/>
-      <c r="AS9" s="68"/>
-      <c r="AT9" s="68"/>
-      <c r="AU9" s="68"/>
-      <c r="AV9" s="86"/>
-      <c r="AW9" s="86"/>
-      <c r="AX9" s="86"/>
-      <c r="AY9" s="86"/>
-      <c r="AZ9" s="68"/>
-      <c r="BA9" s="68"/>
-      <c r="BB9" s="51"/>
-      <c r="BC9" s="65"/>
-      <c r="BD9" s="78"/>
-      <c r="BE9" s="78"/>
-      <c r="BF9" s="86"/>
-      <c r="BG9" s="86"/>
-      <c r="BH9" s="51"/>
-      <c r="BI9" s="51"/>
-      <c r="BJ9" s="51"/>
+      <c r="AQ9" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="AR9" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="AS9" s="88" t="s">
+        <v>163</v>
+      </c>
+      <c r="AT9" s="67"/>
+      <c r="AU9" s="67"/>
+      <c r="AV9" s="67"/>
+      <c r="AW9" s="67"/>
+      <c r="AX9" s="67"/>
+      <c r="AY9" s="84"/>
+      <c r="AZ9" s="84"/>
+      <c r="BA9" s="84"/>
+      <c r="BB9" s="84"/>
+      <c r="BC9" s="67"/>
+      <c r="BD9" s="67"/>
+      <c r="BE9" s="51"/>
+      <c r="BF9" s="65"/>
+      <c r="BG9" s="77"/>
+      <c r="BH9" s="77"/>
+      <c r="BI9" s="84"/>
+      <c r="BJ9" s="84"/>
       <c r="BK9" s="51"/>
-      <c r="BL9" s="66"/>
-      <c r="BM9" s="66"/>
-      <c r="BN9" s="66"/>
-      <c r="BO9" s="66"/>
-    </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BL9" s="51"/>
+      <c r="BM9" s="51"/>
+      <c r="BN9" s="51"/>
+      <c r="BO9" s="219"/>
+      <c r="BP9" s="93"/>
+      <c r="BQ9" s="218"/>
+      <c r="BR9" s="218"/>
+      <c r="BS9" s="218"/>
+      <c r="BT9" s="218"/>
+      <c r="BU9" s="218"/>
+      <c r="BV9" s="218"/>
+      <c r="BW9" s="218"/>
+    </row>
+    <row r="10" spans="1:76" x14ac:dyDescent="0.25">
       <c r="B10" s="47" t="s">
         <v>2</v>
       </c>
       <c r="C10" s="47"/>
       <c r="D10" s="48"/>
-      <c r="E10" s="90"/>
+      <c r="E10" s="88"/>
       <c r="F10" s="47"/>
       <c r="G10" s="48"/>
       <c r="H10" s="49"/>
       <c r="I10" s="47"/>
       <c r="J10" s="48"/>
-      <c r="K10" s="90"/>
+      <c r="K10" s="88"/>
       <c r="L10" s="47"/>
       <c r="M10" s="48"/>
-      <c r="N10" s="90"/>
+      <c r="N10" s="88"/>
       <c r="O10" s="47"/>
       <c r="P10" s="48"/>
       <c r="Q10" s="49"/>
       <c r="R10" s="47"/>
       <c r="S10" s="48"/>
-      <c r="T10" s="90"/>
+      <c r="T10" s="88"/>
       <c r="U10" s="47"/>
       <c r="V10" s="48"/>
       <c r="W10" s="49"/>
@@ -21094,35 +21359,43 @@
       <c r="AL10" s="49"/>
       <c r="AM10" s="47"/>
       <c r="AN10" s="48"/>
-      <c r="AO10" s="90"/>
+      <c r="AO10" s="88"/>
       <c r="AP10" s="48"/>
-      <c r="AQ10" s="69"/>
-      <c r="AR10" s="69"/>
-      <c r="AS10" s="69"/>
-      <c r="AT10" s="69"/>
-      <c r="AU10" s="69"/>
-      <c r="AV10" s="87"/>
-      <c r="AW10" s="87"/>
-      <c r="AX10" s="87"/>
-      <c r="AY10" s="87"/>
-      <c r="AZ10" s="69"/>
-      <c r="BA10" s="69"/>
-      <c r="BB10" s="51"/>
-      <c r="BC10" s="65"/>
-      <c r="BD10" s="78"/>
-      <c r="BE10" s="78"/>
-      <c r="BF10" s="87"/>
-      <c r="BG10" s="87"/>
-      <c r="BH10" s="51"/>
-      <c r="BI10" s="51"/>
-      <c r="BJ10" s="51"/>
+      <c r="AQ10" s="48"/>
+      <c r="AR10" s="48"/>
+      <c r="AS10" s="48"/>
+      <c r="AT10" s="68"/>
+      <c r="AU10" s="68"/>
+      <c r="AV10" s="68"/>
+      <c r="AW10" s="68"/>
+      <c r="AX10" s="68"/>
+      <c r="AY10" s="85"/>
+      <c r="AZ10" s="85"/>
+      <c r="BA10" s="85"/>
+      <c r="BB10" s="85"/>
+      <c r="BC10" s="68"/>
+      <c r="BD10" s="68"/>
+      <c r="BE10" s="51"/>
+      <c r="BF10" s="65"/>
+      <c r="BG10" s="77"/>
+      <c r="BH10" s="77"/>
+      <c r="BI10" s="85"/>
+      <c r="BJ10" s="85"/>
       <c r="BK10" s="51"/>
-      <c r="BL10" s="66"/>
-      <c r="BM10" s="66"/>
-      <c r="BN10" s="66"/>
-      <c r="BO10" s="66"/>
-    </row>
-    <row r="11" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BL10" s="51"/>
+      <c r="BM10" s="51"/>
+      <c r="BN10" s="51"/>
+      <c r="BO10" s="219"/>
+      <c r="BP10" s="93"/>
+      <c r="BQ10" s="218"/>
+      <c r="BR10" s="218"/>
+      <c r="BS10" s="218"/>
+      <c r="BT10" s="218"/>
+      <c r="BU10" s="218"/>
+      <c r="BV10" s="218"/>
+      <c r="BW10" s="218"/>
+    </row>
+    <row r="11" spans="1:76" x14ac:dyDescent="0.25">
       <c r="B11" s="47" t="s">
         <v>160</v>
       </c>
@@ -21130,7 +21403,7 @@
         <v>168</v>
       </c>
       <c r="D11" s="48"/>
-      <c r="E11" s="90"/>
+      <c r="E11" s="88"/>
       <c r="F11" s="50" t="s">
         <v>320</v>
       </c>
@@ -21140,12 +21413,12 @@
         <v>321</v>
       </c>
       <c r="J11" s="48"/>
-      <c r="K11" s="90"/>
+      <c r="K11" s="88"/>
       <c r="L11" s="50" t="s">
         <v>322</v>
       </c>
       <c r="M11" s="48"/>
-      <c r="N11" s="90"/>
+      <c r="N11" s="88"/>
       <c r="O11" s="50" t="s">
         <v>167</v>
       </c>
@@ -21155,7 +21428,7 @@
         <v>324</v>
       </c>
       <c r="S11" s="48"/>
-      <c r="T11" s="90"/>
+      <c r="T11" s="88"/>
       <c r="U11" s="50" t="s">
         <v>169</v>
       </c>
@@ -21177,116 +21450,154 @@
       <c r="AE11" s="48"/>
       <c r="AF11" s="49"/>
       <c r="AG11" s="50" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="AH11" s="48"/>
       <c r="AI11" s="49"/>
       <c r="AJ11" s="50" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="AK11" s="48"/>
       <c r="AL11" s="49"/>
       <c r="AM11" s="50" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="AN11" s="48"/>
-      <c r="AO11" s="90"/>
+      <c r="AO11" s="88"/>
       <c r="AP11" s="48" t="s">
-        <v>420</v>
-      </c>
-      <c r="AQ11" s="68" t="str">
+        <v>415</v>
+      </c>
+      <c r="AQ11" s="50" t="s">
+        <v>631</v>
+      </c>
+      <c r="AR11" s="48"/>
+      <c r="AS11" s="88"/>
+      <c r="AT11" s="67" t="str">
         <f>J11&amp;"-"&amp;M11&amp;"-"&amp;S11</f>
         <v>--</v>
       </c>
-      <c r="AR11" s="68">
+      <c r="AU11" s="67">
         <f>IF(S11="XPS",1,0)</f>
         <v>0</v>
       </c>
-      <c r="AS11" s="68">
+      <c r="AV11" s="67">
         <f>IF(S11="XT",1,0)</f>
         <v>0</v>
       </c>
-      <c r="AT11" s="68">
+      <c r="AW11" s="67">
         <f>IF(S11="Вкл",1,0)</f>
         <v>0</v>
       </c>
-      <c r="AU11" s="68">
+      <c r="AX11" s="67">
         <f>IF(AN11="",0,1)</f>
         <v>0</v>
       </c>
-      <c r="AV11" s="86">
-        <f>IFERROR(IF(AU11=1,0,IF(SUM(AR11:AT11)&gt;0,0,IF(INDEX($AH$11:AH11,MATCH(J11,$D$11:D11,0))="True",1,0))),-1)</f>
+      <c r="AY11" s="84">
+        <f>IFERROR(IF(AX11=1,0,IF(SUM(AU11:AW11)&gt;0,0,IF(INDEX($AH$11:AH11,MATCH(J11,$D$11:D11,0))="True",1,0))),-1)</f>
         <v>-1</v>
       </c>
-      <c r="AW11" s="86" t="str">
-        <f>IF(AV11=-1,IF(SUM(AR11:AT11)&gt;0,INDEX($AW$11:AW11,COUNT($BB$11:BB11)-1),"-1"),IF(AV11=1,J11,INDEX($AW$11:AW11,COUNT($BB$11:BB11)-1)))</f>
+      <c r="AZ11" s="84" t="str">
+        <f>IF(AY11=-1,IF(SUM(AU11:AW11)&gt;0,INDEX($AZ$11:AZ11,COUNT($BE$11:BE11)-1),"-1"),IF(AY11=1,J11,INDEX($AZ$11:AZ11,COUNT($BE$11:BE11)-1)))</f>
         <v>-1</v>
       </c>
-      <c r="AX11" s="86">
-        <f>IF(AV11=-1,-1,IF(AV11=1,M11,INDEX($AX$11:AX11,COUNT($BB$11:BB11)-1)))</f>
+      <c r="BA11" s="84">
+        <f>IF(AY11=-1,-1,IF(AY11=1,M11,INDEX($BA$11:BA11,COUNT($BE$11:BE11)-1)))</f>
         <v>-1</v>
       </c>
-      <c r="AY11" s="86" t="str">
-        <f>IF(AW11="-1","-1",IF(AW11&lt;&gt;J11,1,0))</f>
+      <c r="BB11" s="84" t="str">
+        <f>IF(AZ11="-1","-1",IF(AZ11&lt;&gt;J11,1,0))</f>
         <v>-1</v>
       </c>
-      <c r="AZ11" s="68">
-        <f>IF(COUNT($BB$11:BB11)=MATCH(AQ11,$AQ$11:AQ11,0),1,0)</f>
+      <c r="BC11" s="67">
+        <f>IF(COUNT($BE$11:BE11)=MATCH(AT11,$AT$11:AT11,0),1,0)</f>
         <v>1</v>
       </c>
-      <c r="BA11" s="68">
-        <f>SUMIFS($BB$11:$BB$700000,$AQ$11:$AQ$700000,AQ11)</f>
+      <c r="BD11" s="67">
+        <f>SUMIFS($BE$11:$BE$700000,$AT$11:$AT$700000,AT11)</f>
         <v>1</v>
       </c>
-      <c r="BB11" s="51">
+      <c r="BE11" s="51">
         <v>1</v>
       </c>
-      <c r="BC11" s="65" t="str">
+      <c r="BF11" s="65" t="str">
         <f>$F$4</f>
         <v>-</v>
       </c>
-      <c r="BD11" s="78">
-        <f>IF(AK11="True",IF(BC11=AW11,IF(AZ11=1,IF(AU11=1,0,IF(SUM(AR11:AT11)&gt;0,0,1)),0),0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BE11" s="78">
-        <f>IF(AK11="True",IF(BC11=D11,1,0),0)</f>
-        <v>0</v>
-      </c>
-      <c r="BF11" s="86">
-        <f>SUMIF(J11:$J$700000,D11,BB11:$BB$700000)</f>
-        <v>0</v>
-      </c>
-      <c r="BG11" s="86" t="str">
-        <f>IF(AV11=-1,"0",1+INDEX($BG$11:$BG$700000,MATCH(J11,$D$11:$D$700000,0)))</f>
-        <v>0</v>
-      </c>
-      <c r="BH11" s="51">
-        <f>SUMIFS($BB$11:$BB$700000,$S$11:$S$700000,S11,$M$11:$M$700000,M11)</f>
-        <v>0</v>
-      </c>
-      <c r="BI11" s="51">
-        <f>IF(SUMIFS($BB$11:BB11,$S$11:S11,S11,$M$11:M11,M11)=1,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="BJ11" s="51">
-        <f>IF(BI11=1,1,0)</f>
+      <c r="BG11" s="77">
+        <f>IF(AK11="True",IF(BF11=AZ11,IF(BC11=1,IF(AX11=1,0,IF(SUM(AU11:AW11)&gt;0,0,1)),0),0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BH11" s="77">
+        <f>IF(AK11="True",IF(BF11=D11,1,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="BI11" s="84">
+        <f>SUMIF(J11:$J$700000,D11,BE11:$BE$700000)</f>
+        <v>0</v>
+      </c>
+      <c r="BJ11" s="84" t="str">
+        <f>IF(AY11=-1,"0",1+INDEX($BJ$11:$BJ$700000,MATCH(J11,$D$11:$D$700000,0)))</f>
         <v>0</v>
       </c>
       <c r="BK11" s="51">
+        <f>SUMIFS($BE$11:$BE$700000,$S$11:$S$700000,S11,$M$11:$M$700000,M11)</f>
+        <v>0</v>
+      </c>
+      <c r="BL11" s="51">
+        <f>IF(SUMIFS($BE$11:BE11,$S$11:S11,S11,$M$11:M11,M11)=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BM11" s="51">
+        <f>IF(BL11=1,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="BN11" s="51">
         <f>M11</f>
         <v>0</v>
       </c>
-      <c r="BL11" s="66"/>
-      <c r="BM11" s="66"/>
-      <c r="BN11" s="66"/>
-      <c r="BO11" s="66"/>
-      <c r="BP11" t="s">
+      <c r="BO11" s="219" t="str">
+        <f>J11&amp;"-"&amp;M11&amp;"-"&amp;D11&amp;"-"&amp;AR11</f>
+        <v>---</v>
+      </c>
+      <c r="BP11" s="93">
+        <f>IFERROR(IF(MATCH(BR11,$BR12:BR$777777,0)&gt;0,0,1),1)</f>
+        <v>1</v>
+      </c>
+      <c r="BQ11" s="218">
+        <f>COUNTIF($BO$11:$BO$777777,"&lt;"&amp;BO11)+COUNTIF($BO$11:BO11,BO11)</f>
+        <v>1</v>
+      </c>
+      <c r="BR11" s="218" t="str">
+        <f>INDEX($BO$11:$BO$777777, MATCH(ROW(BO11)-10, $BQ$11:$BQ$777777, 0))</f>
+        <v>---</v>
+      </c>
+      <c r="BS11" s="218" t="str">
+        <f>INDEX($BO$11:$BO$777777,MATCH(ROW(BP11)-10,$BQ$11:$BQ$777777,0))</f>
+        <v>---</v>
+      </c>
+      <c r="BT11" s="218">
+        <f>INDEX($J$11:$J$777777,MATCH(ROW(BP11)-10,$BQ$11:$BQ$777777,0))</f>
+        <v>0</v>
+      </c>
+      <c r="BU11" s="218">
+        <f>INDEX($M$11:$M$777777,MATCH(ROW(BP11)-10,$BQ$11:$BQ$777777,0))</f>
+        <v>0</v>
+      </c>
+      <c r="BV11" s="218">
+        <f>INDEX($D$11:$D$777777,MATCH(ROW(BP11)-10,$BQ$11:$BQ$777777,0))</f>
+        <v>0</v>
+      </c>
+      <c r="BW11" s="218">
+        <f>INDEX($AR$11:$AR$777777,MATCH(ROW(BP11)-10,$BQ$11:$BQ$777777,0))</f>
+        <v>0</v>
+      </c>
+      <c r="BX11" t="s">
         <v>161</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="AQ8:AS8"/>
     <mergeCell ref="AM8:AO8"/>
     <mergeCell ref="AG8:AI8"/>
     <mergeCell ref="D3:F3"/>
@@ -21307,40 +21618,134 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019AE8B5-0D80-438F-9CBA-ADEC7CDF9F04}">
-  <dimension ref="A1:B3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AAC30AF-53EA-49C7-84D1-3A4FC5AA4D11}">
+  <dimension ref="B1:X7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
+    <col min="7" max="14" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B2" t="str">
-        <f>"&lt;zsetformulatocell toSheet=[BD]  toCell=[A2] formula=[SUM(B4:B5)]"</f>
-        <v>&lt;zsetformulatocell toSheet=[BD]  toCell=[A2] formula=[SUM(B4:B5)]</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>172</v>
-      </c>
-      <c r="B3" t="s">
-        <v>174</v>
-      </c>
+    <row r="1" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="C1" s="241" t="s">
+        <v>431</v>
+      </c>
+      <c r="D1" s="241"/>
+    </row>
+    <row r="2" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="C2" s="97" t="s">
+        <v>419</v>
+      </c>
+      <c r="D2" s="97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="C3" s="97" t="s">
+        <v>420</v>
+      </c>
+      <c r="D3" s="97">
+        <f>D2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="C6" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>636</v>
+      </c>
+      <c r="C7" s="1">
+        <f>'&lt;zalldev&gt;EXPORT'!BT11</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <f>'&lt;zalldev&gt;EXPORT'!BU11</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <f>'&lt;zalldev&gt;EXPORT'!BV11</f>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f>'&lt;zalldev&gt;EXPORT'!BW11</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="221" t="str">
+        <f>C7&amp;"."&amp;D7&amp;"."&amp;E7</f>
+        <v>0.0.0</v>
+      </c>
+      <c r="H7" s="131" t="str">
+        <f>IF(MATCH(G7,$G$7:G7,0)=I7,G7,0)</f>
+        <v>0.0.0</v>
+      </c>
+      <c r="I7" s="131">
+        <f>COUNT($K$7:K7)</f>
+        <v>1</v>
+      </c>
+      <c r="J7" s="131" t="str">
+        <f>ADDRESS(ROW(Q7),COLUMN(Q7))</f>
+        <v>$Q$7</v>
+      </c>
+      <c r="K7" s="131">
+        <v>1</v>
+      </c>
+      <c r="L7" s="132" t="str">
+        <f>IF(SUMIF($G7:G$777777,G7,$K7:K$777777)=1,G7,0)</f>
+        <v>0.0.0</v>
+      </c>
+      <c r="M7" s="133">
+        <f>MATCH(G7,$H$7:H7,0)</f>
+        <v>1</v>
+      </c>
+      <c r="N7" s="133">
+        <f>MATCH(G7,$L$7:$L$777777,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O7" s="132" t="str">
+        <f>INDEX($J$7:J7,M7)</f>
+        <v>$Q$7</v>
+      </c>
+      <c r="P7" s="132" t="str">
+        <f>INDEX($J$7:$J$777777,N7)</f>
+        <v>$Q$7</v>
+      </c>
+      <c r="Q7" t="str">
+        <f>SUBSTITUTE(F7,",",".")</f>
+        <v>0</v>
+      </c>
+      <c r="R7" t="str">
+        <f t="shared" ref="R7" ca="1" si="0">_xlfn.TEXTJOIN(", ",TRUE,INDIRECT(O7&amp;":"&amp;P7))</f>
+        <v>0</v>
+      </c>
+      <c r="T7" t="s">
+        <v>189</v>
+      </c>
+      <c r="X7" s="138"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:D1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>